--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -10038,32 +10038,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130068636</v>
+        <v>130068604</v>
       </c>
       <c r="B96" t="n">
-        <v>78853</v>
+        <v>80229</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10073,10 +10073,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>490401</v>
+        <v>491011</v>
       </c>
       <c r="R96" t="n">
-        <v>6821355</v>
+        <v>6820779</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10145,10 +10145,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130068758</v>
+        <v>130068662</v>
       </c>
       <c r="B97" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10156,21 +10156,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10180,10 +10180,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>490678</v>
+        <v>490444</v>
       </c>
       <c r="R97" t="n">
-        <v>6821049</v>
+        <v>6821223</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10252,7 +10252,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130068841</v>
+        <v>130068698</v>
       </c>
       <c r="B98" t="n">
         <v>79095</v>
@@ -10287,10 +10287,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>490928</v>
+        <v>490411</v>
       </c>
       <c r="R98" t="n">
-        <v>6820734</v>
+        <v>6821237</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10359,7 +10359,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130068750</v>
+        <v>130068754</v>
       </c>
       <c r="B99" t="n">
         <v>79095</v>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>490627</v>
+        <v>490649</v>
       </c>
       <c r="R99" t="n">
-        <v>6821135</v>
+        <v>6821056</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10466,7 +10466,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130068698</v>
+        <v>130068736</v>
       </c>
       <c r="B100" t="n">
         <v>79095</v>
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>490411</v>
+        <v>490549</v>
       </c>
       <c r="R100" t="n">
-        <v>6821237</v>
+        <v>6821209</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10573,7 +10573,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130068754</v>
+        <v>130068876</v>
       </c>
       <c r="B101" t="n">
         <v>79095</v>
@@ -10608,10 +10608,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>490649</v>
+        <v>490680</v>
       </c>
       <c r="R101" t="n">
-        <v>6821056</v>
+        <v>6821006</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10643,7 +10643,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10680,7 +10680,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130068736</v>
+        <v>130068697</v>
       </c>
       <c r="B102" t="n">
         <v>79095</v>
@@ -10715,10 +10715,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490549</v>
+        <v>490390</v>
       </c>
       <c r="R102" t="n">
-        <v>6821209</v>
+        <v>6821282</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10787,7 +10787,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130068876</v>
+        <v>130068740</v>
       </c>
       <c r="B103" t="n">
         <v>79095</v>
@@ -10822,10 +10822,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490680</v>
+        <v>490573</v>
       </c>
       <c r="R103" t="n">
-        <v>6821006</v>
+        <v>6821208</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10894,7 +10894,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130068697</v>
+        <v>130068694</v>
       </c>
       <c r="B104" t="n">
         <v>79095</v>
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490390</v>
+        <v>490377</v>
       </c>
       <c r="R104" t="n">
-        <v>6821282</v>
+        <v>6821296</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11001,32 +11001,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130068618</v>
+        <v>130068742</v>
       </c>
       <c r="B105" t="n">
-        <v>97708</v>
+        <v>79095</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11036,10 +11036,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491025</v>
+        <v>490601</v>
       </c>
       <c r="R105" t="n">
-        <v>6820835</v>
+        <v>6821185</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11108,7 +11108,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130068740</v>
+        <v>130068726</v>
       </c>
       <c r="B106" t="n">
         <v>79095</v>
@@ -11143,10 +11143,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>490573</v>
+        <v>490525</v>
       </c>
       <c r="R106" t="n">
-        <v>6821208</v>
+        <v>6821257</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11178,7 +11178,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11215,10 +11215,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130068694</v>
+        <v>130068655</v>
       </c>
       <c r="B107" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11226,21 +11226,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11250,10 +11250,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>490377</v>
+        <v>490577</v>
       </c>
       <c r="R107" t="n">
-        <v>6821296</v>
+        <v>6821216</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11285,7 +11285,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11322,7 +11322,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130068742</v>
+        <v>130068758</v>
       </c>
       <c r="B108" t="n">
         <v>79095</v>
@@ -11357,10 +11357,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>490601</v>
+        <v>490678</v>
       </c>
       <c r="R108" t="n">
-        <v>6821185</v>
+        <v>6821049</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11392,7 +11392,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11429,7 +11429,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130068726</v>
+        <v>130068841</v>
       </c>
       <c r="B109" t="n">
         <v>79095</v>
@@ -11464,10 +11464,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>490525</v>
+        <v>490928</v>
       </c>
       <c r="R109" t="n">
-        <v>6821257</v>
+        <v>6820734</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11536,32 +11536,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130068604</v>
+        <v>130068750</v>
       </c>
       <c r="B110" t="n">
-        <v>80229</v>
+        <v>79095</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11571,10 +11571,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491011</v>
+        <v>490627</v>
       </c>
       <c r="R110" t="n">
-        <v>6820779</v>
+        <v>6821135</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11643,32 +11643,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130068662</v>
+        <v>130068618</v>
       </c>
       <c r="B111" t="n">
-        <v>78852</v>
+        <v>97708</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11678,10 +11678,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>490444</v>
+        <v>491025</v>
       </c>
       <c r="R111" t="n">
-        <v>6821223</v>
+        <v>6820835</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11750,10 +11750,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130068655</v>
+        <v>130068636</v>
       </c>
       <c r="B112" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11761,21 +11761,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11785,10 +11785,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>490577</v>
+        <v>490401</v>
       </c>
       <c r="R112" t="n">
-        <v>6821216</v>
+        <v>6821355</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14211,45 +14211,50 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130068797</v>
+        <v>130068633</v>
       </c>
       <c r="B135" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>491182</v>
+        <v>491186</v>
       </c>
       <c r="R135" t="n">
-        <v>6820616</v>
+        <v>6820622</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14318,45 +14323,54 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130068885</v>
+        <v>130068667</v>
       </c>
       <c r="B136" t="n">
-        <v>79095</v>
+        <v>98831</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>490562</v>
+        <v>490666</v>
       </c>
       <c r="R136" t="n">
-        <v>6821132</v>
+        <v>6821043</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14388,7 +14402,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14398,7 +14412,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14425,7 +14439,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130068867</v>
+        <v>130068797</v>
       </c>
       <c r="B137" t="n">
         <v>79095</v>
@@ -14460,10 +14474,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>490726</v>
+        <v>491182</v>
       </c>
       <c r="R137" t="n">
-        <v>6820965</v>
+        <v>6820616</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14495,7 +14509,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14505,7 +14519,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14532,7 +14546,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130068781</v>
+        <v>130068885</v>
       </c>
       <c r="B138" t="n">
         <v>79095</v>
@@ -14567,10 +14581,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>491160</v>
+        <v>490562</v>
       </c>
       <c r="R138" t="n">
-        <v>6820813</v>
+        <v>6821132</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14602,7 +14616,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14612,7 +14626,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14639,7 +14653,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130068836</v>
+        <v>130068867</v>
       </c>
       <c r="B139" t="n">
         <v>79095</v>
@@ -14674,10 +14688,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>490945</v>
+        <v>490726</v>
       </c>
       <c r="R139" t="n">
-        <v>6820623</v>
+        <v>6820965</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14709,7 +14723,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14719,7 +14733,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14746,7 +14760,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130068902</v>
+        <v>130068781</v>
       </c>
       <c r="B140" t="n">
         <v>79095</v>
@@ -14781,10 +14795,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>490481</v>
+        <v>491160</v>
       </c>
       <c r="R140" t="n">
-        <v>6821182</v>
+        <v>6820813</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14816,7 +14830,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14826,7 +14840,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14853,7 +14867,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130068718</v>
+        <v>130068836</v>
       </c>
       <c r="B141" t="n">
         <v>79095</v>
@@ -14888,10 +14902,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>490492</v>
+        <v>490945</v>
       </c>
       <c r="R141" t="n">
-        <v>6821351</v>
+        <v>6820623</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14923,7 +14937,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14933,7 +14947,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14960,7 +14974,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130068840</v>
+        <v>130068902</v>
       </c>
       <c r="B142" t="n">
         <v>79095</v>
@@ -14995,10 +15009,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>490857</v>
+        <v>490481</v>
       </c>
       <c r="R142" t="n">
-        <v>6820652</v>
+        <v>6821182</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15030,7 +15044,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15040,7 +15054,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15067,7 +15081,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130068873</v>
+        <v>130068718</v>
       </c>
       <c r="B143" t="n">
         <v>79095</v>
@@ -15102,10 +15116,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>490656</v>
+        <v>490492</v>
       </c>
       <c r="R143" t="n">
-        <v>6820985</v>
+        <v>6821351</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15137,7 +15151,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15147,7 +15161,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15174,7 +15188,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130068833</v>
+        <v>130068840</v>
       </c>
       <c r="B144" t="n">
         <v>79095</v>
@@ -15209,10 +15223,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>490971</v>
+        <v>490857</v>
       </c>
       <c r="R144" t="n">
-        <v>6820633</v>
+        <v>6820652</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15244,7 +15258,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15254,7 +15268,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15281,7 +15295,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130068776</v>
+        <v>130068873</v>
       </c>
       <c r="B145" t="n">
         <v>79095</v>
@@ -15316,10 +15330,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>491154</v>
+        <v>490656</v>
       </c>
       <c r="R145" t="n">
-        <v>6820794</v>
+        <v>6820985</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15351,7 +15365,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15361,7 +15375,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15388,10 +15402,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130068660</v>
+        <v>130068833</v>
       </c>
       <c r="B146" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15399,21 +15413,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15423,10 +15437,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>490550</v>
+        <v>490971</v>
       </c>
       <c r="R146" t="n">
-        <v>6821160</v>
+        <v>6820633</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15458,7 +15472,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15468,7 +15482,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15495,10 +15509,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130068657</v>
+        <v>130068776</v>
       </c>
       <c r="B147" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15506,21 +15520,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15530,10 +15544,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>490961</v>
+        <v>491154</v>
       </c>
       <c r="R147" t="n">
-        <v>6820600</v>
+        <v>6820794</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15565,7 +15579,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15575,7 +15589,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15602,32 +15616,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130068623</v>
+        <v>130068660</v>
       </c>
       <c r="B148" t="n">
-        <v>80228</v>
+        <v>78852</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15637,10 +15651,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>490594</v>
+        <v>490550</v>
       </c>
       <c r="R148" t="n">
-        <v>6821177</v>
+        <v>6821160</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15672,7 +15686,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15682,7 +15696,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15709,10 +15723,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130068563</v>
+        <v>130068657</v>
       </c>
       <c r="B149" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15720,21 +15734,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15744,10 +15758,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>490629</v>
+        <v>490961</v>
       </c>
       <c r="R149" t="n">
-        <v>6821073</v>
+        <v>6820600</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15779,7 +15793,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15789,7 +15803,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15816,10 +15830,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130068594</v>
+        <v>130068623</v>
       </c>
       <c r="B150" t="n">
-        <v>56931</v>
+        <v>80228</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15827,39 +15841,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>490601</v>
+        <v>490594</v>
       </c>
       <c r="R150" t="n">
-        <v>6821175</v>
+        <v>6821177</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15928,10 +15937,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130068926</v>
+        <v>130068563</v>
       </c>
       <c r="B151" t="n">
-        <v>78761</v>
+        <v>79714</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15939,21 +15948,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15963,10 +15972,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>491190</v>
+        <v>490629</v>
       </c>
       <c r="R151" t="n">
-        <v>6820607</v>
+        <v>6821073</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15998,7 +16007,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16008,7 +16017,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16035,45 +16044,50 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130068587</v>
+        <v>130068594</v>
       </c>
       <c r="B152" t="n">
-        <v>79127</v>
+        <v>56931</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>491161</v>
+        <v>490601</v>
       </c>
       <c r="R152" t="n">
-        <v>6820628</v>
+        <v>6821175</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16105,7 +16119,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16115,7 +16129,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16142,10 +16156,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130068605</v>
+        <v>130068926</v>
       </c>
       <c r="B153" t="n">
-        <v>91590</v>
+        <v>78761</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16153,21 +16167,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16177,10 +16191,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>490521</v>
+        <v>491190</v>
       </c>
       <c r="R153" t="n">
-        <v>6821298</v>
+        <v>6820607</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16212,7 +16226,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16222,7 +16236,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16249,50 +16263,45 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130068633</v>
+        <v>130068587</v>
       </c>
       <c r="B154" t="n">
-        <v>8451</v>
+        <v>79127</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>491186</v>
+        <v>491161</v>
       </c>
       <c r="R154" t="n">
-        <v>6820622</v>
+        <v>6820628</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16324,7 +16333,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16334,7 +16343,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16361,54 +16370,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130068667</v>
+        <v>130068605</v>
       </c>
       <c r="B155" t="n">
-        <v>98831</v>
+        <v>91590</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>490666</v>
+        <v>490521</v>
       </c>
       <c r="R155" t="n">
-        <v>6821043</v>
+        <v>6821298</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16477,10 +16477,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130068653</v>
+        <v>130068895</v>
       </c>
       <c r="B156" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16488,21 +16488,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16512,10 +16512,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>490522</v>
+        <v>490488</v>
       </c>
       <c r="R156" t="n">
-        <v>6821366</v>
+        <v>6821089</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16547,7 +16547,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16584,10 +16584,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130068914</v>
+        <v>130068753</v>
       </c>
       <c r="B157" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16595,39 +16595,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>490384</v>
+        <v>490636</v>
       </c>
       <c r="R157" t="n">
-        <v>6821397</v>
+        <v>6821100</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16659,7 +16654,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16669,7 +16664,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16696,32 +16691,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130068617</v>
+        <v>130068848</v>
       </c>
       <c r="B158" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16731,10 +16726,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>490994</v>
+        <v>490995</v>
       </c>
       <c r="R158" t="n">
-        <v>6820825</v>
+        <v>6820786</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16766,7 +16761,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16776,7 +16771,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16803,7 +16798,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130068895</v>
+        <v>130068845</v>
       </c>
       <c r="B159" t="n">
         <v>79095</v>
@@ -16838,10 +16833,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>490488</v>
+        <v>490996</v>
       </c>
       <c r="R159" t="n">
-        <v>6821089</v>
+        <v>6820767</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16873,7 +16868,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -16883,7 +16878,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16910,7 +16905,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130068753</v>
+        <v>130068877</v>
       </c>
       <c r="B160" t="n">
         <v>79095</v>
@@ -16945,10 +16940,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>490636</v>
+        <v>490683</v>
       </c>
       <c r="R160" t="n">
-        <v>6821100</v>
+        <v>6821011</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16980,7 +16975,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -16990,7 +16985,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17017,7 +17012,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130068848</v>
+        <v>130068701</v>
       </c>
       <c r="B161" t="n">
         <v>79095</v>
@@ -17052,10 +17047,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>490995</v>
+        <v>490427</v>
       </c>
       <c r="R161" t="n">
-        <v>6820786</v>
+        <v>6821240</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17087,7 +17082,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17097,7 +17092,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17124,10 +17119,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130068845</v>
+        <v>130068627</v>
       </c>
       <c r="B162" t="n">
-        <v>79095</v>
+        <v>92959</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17135,21 +17130,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17159,10 +17154,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>490996</v>
+        <v>491012</v>
       </c>
       <c r="R162" t="n">
-        <v>6820767</v>
+        <v>6820821</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17194,7 +17189,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17204,7 +17199,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17231,7 +17226,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>130068877</v>
+        <v>130068716</v>
       </c>
       <c r="B163" t="n">
         <v>79095</v>
@@ -17266,10 +17261,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>490683</v>
+        <v>490456</v>
       </c>
       <c r="R163" t="n">
-        <v>6821011</v>
+        <v>6821350</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17301,7 +17296,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17311,7 +17306,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17338,32 +17333,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130068701</v>
+        <v>130068617</v>
       </c>
       <c r="B164" t="n">
-        <v>79095</v>
+        <v>97702</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17373,10 +17368,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>490427</v>
+        <v>490994</v>
       </c>
       <c r="R164" t="n">
-        <v>6821240</v>
+        <v>6820825</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17408,7 +17403,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17418,7 +17413,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17445,10 +17440,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130068627</v>
+        <v>130068653</v>
       </c>
       <c r="B165" t="n">
-        <v>92959</v>
+        <v>78852</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17456,21 +17451,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17480,10 +17475,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>491012</v>
+        <v>490522</v>
       </c>
       <c r="R165" t="n">
-        <v>6820821</v>
+        <v>6821366</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17515,7 +17510,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17525,7 +17520,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17552,10 +17547,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>130068716</v>
+        <v>130068914</v>
       </c>
       <c r="B166" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17563,34 +17558,39 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>490456</v>
+        <v>490384</v>
       </c>
       <c r="R166" t="n">
-        <v>6821350</v>
+        <v>6821397</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17632,7 +17632,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20129,10 +20129,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>130068642</v>
+        <v>130068930</v>
       </c>
       <c r="B190" t="n">
-        <v>80200</v>
+        <v>78761</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20140,21 +20140,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20164,10 +20164,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>491110</v>
+        <v>490563</v>
       </c>
       <c r="R190" t="n">
-        <v>6820801</v>
+        <v>6821133</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20209,7 +20209,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20236,10 +20236,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>130068561</v>
+        <v>130068741</v>
       </c>
       <c r="B191" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20247,21 +20247,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20271,10 +20271,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>490380</v>
+        <v>490578</v>
       </c>
       <c r="R191" t="n">
-        <v>6821325</v>
+        <v>6821202</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20343,10 +20343,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>130068930</v>
+        <v>130068785</v>
       </c>
       <c r="B192" t="n">
-        <v>78761</v>
+        <v>79095</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20354,21 +20354,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20378,10 +20378,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>490563</v>
+        <v>491178</v>
       </c>
       <c r="R192" t="n">
-        <v>6821133</v>
+        <v>6820798</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20413,7 +20413,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20450,7 +20450,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>130068741</v>
+        <v>130068806</v>
       </c>
       <c r="B193" t="n">
         <v>79095</v>
@@ -20485,10 +20485,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>490578</v>
+        <v>491242</v>
       </c>
       <c r="R193" t="n">
-        <v>6821202</v>
+        <v>6820579</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20520,7 +20520,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20530,7 +20530,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20557,10 +20557,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>130068785</v>
+        <v>130068607</v>
       </c>
       <c r="B194" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20568,34 +20568,39 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>491178</v>
+        <v>490376</v>
       </c>
       <c r="R194" t="n">
-        <v>6820798</v>
+        <v>6821479</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20627,7 +20632,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20637,7 +20642,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20664,10 +20669,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>130068806</v>
+        <v>130068561</v>
       </c>
       <c r="B195" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20675,21 +20680,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20699,10 +20704,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>491242</v>
+        <v>490380</v>
       </c>
       <c r="R195" t="n">
-        <v>6820579</v>
+        <v>6821325</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20734,7 +20739,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20744,7 +20749,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20771,10 +20776,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>130068607</v>
+        <v>130068570</v>
       </c>
       <c r="B196" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20782,39 +20787,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>490376</v>
+        <v>490731</v>
       </c>
       <c r="R196" t="n">
-        <v>6821479</v>
+        <v>6820976</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20846,7 +20846,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20856,7 +20856,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20883,10 +20883,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>130068570</v>
+        <v>130068658</v>
       </c>
       <c r="B197" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20894,21 +20894,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20918,10 +20918,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>490731</v>
+        <v>490643</v>
       </c>
       <c r="R197" t="n">
-        <v>6820976</v>
+        <v>6821043</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20990,10 +20990,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>130068658</v>
+        <v>130068898</v>
       </c>
       <c r="B198" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21001,21 +21001,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21025,10 +21025,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>490643</v>
+        <v>490480</v>
       </c>
       <c r="R198" t="n">
-        <v>6821043</v>
+        <v>6821113</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21070,7 +21070,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21097,7 +21097,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>130068898</v>
+        <v>130068748</v>
       </c>
       <c r="B199" t="n">
         <v>79095</v>
@@ -21132,10 +21132,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>490480</v>
+        <v>490584</v>
       </c>
       <c r="R199" t="n">
-        <v>6821113</v>
+        <v>6821145</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21167,7 +21167,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21177,7 +21177,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21204,7 +21204,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>130068748</v>
+        <v>130068719</v>
       </c>
       <c r="B200" t="n">
         <v>79095</v>
@@ -21239,10 +21239,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>490584</v>
+        <v>490534</v>
       </c>
       <c r="R200" t="n">
-        <v>6821145</v>
+        <v>6821348</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21274,7 +21274,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21311,7 +21311,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>130068719</v>
+        <v>130068771</v>
       </c>
       <c r="B201" t="n">
         <v>79095</v>
@@ -21346,10 +21346,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>490534</v>
+        <v>490799</v>
       </c>
       <c r="R201" t="n">
-        <v>6821348</v>
+        <v>6820989</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21418,7 +21418,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>130068771</v>
+        <v>130068837</v>
       </c>
       <c r="B202" t="n">
         <v>79095</v>
@@ -21453,10 +21453,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>490799</v>
+        <v>490932</v>
       </c>
       <c r="R202" t="n">
-        <v>6820989</v>
+        <v>6820625</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21498,7 +21498,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21525,7 +21525,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>130068837</v>
+        <v>130068712</v>
       </c>
       <c r="B203" t="n">
         <v>79095</v>
@@ -21560,10 +21560,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>490932</v>
+        <v>490440</v>
       </c>
       <c r="R203" t="n">
-        <v>6820625</v>
+        <v>6821320</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21595,7 +21595,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -21605,7 +21605,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21632,10 +21632,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>130068712</v>
+        <v>130068596</v>
       </c>
       <c r="B204" t="n">
-        <v>79095</v>
+        <v>57900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21643,34 +21643,50 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>490440</v>
+        <v>490604</v>
       </c>
       <c r="R204" t="n">
-        <v>6821320</v>
+        <v>6821185</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21702,7 +21718,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -21712,7 +21728,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21739,10 +21755,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>130068596</v>
+        <v>130068642</v>
       </c>
       <c r="B205" t="n">
-        <v>57900</v>
+        <v>80200</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21750,50 +21766,34 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N205" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>490604</v>
+        <v>491110</v>
       </c>
       <c r="R205" t="n">
-        <v>6821185</v>
+        <v>6820801</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21825,7 +21825,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -21835,7 +21835,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -28627,10 +28627,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>130068924</v>
+        <v>130068832</v>
       </c>
       <c r="B269" t="n">
-        <v>78761</v>
+        <v>79095</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -28638,21 +28638,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -28662,10 +28662,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>490633</v>
+        <v>490961</v>
       </c>
       <c r="R269" t="n">
-        <v>6821099</v>
+        <v>6820628</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28697,7 +28697,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -28734,32 +28734,32 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>130068918</v>
+        <v>130068924</v>
       </c>
       <c r="B270" t="n">
-        <v>92921</v>
+        <v>78761</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -28769,10 +28769,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>490996</v>
+        <v>490633</v>
       </c>
       <c r="R270" t="n">
-        <v>6820534</v>
+        <v>6821099</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28804,7 +28804,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -28814,7 +28814,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -28948,7 +28948,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>130068832</v>
+        <v>130068826</v>
       </c>
       <c r="B272" t="n">
         <v>79095</v>
@@ -28983,10 +28983,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>490961</v>
+        <v>490946</v>
       </c>
       <c r="R272" t="n">
-        <v>6820628</v>
+        <v>6820553</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -29018,7 +29018,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -29028,7 +29028,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -29055,7 +29055,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>130068826</v>
+        <v>130068828</v>
       </c>
       <c r="B273" t="n">
         <v>79095</v>
@@ -29093,7 +29093,7 @@
         <v>490946</v>
       </c>
       <c r="R273" t="n">
-        <v>6820553</v>
+        <v>6820572</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -29125,7 +29125,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -29135,7 +29135,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -29162,10 +29162,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>130068828</v>
+        <v>130068565</v>
       </c>
       <c r="B274" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -29173,21 +29173,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -29197,10 +29197,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>490946</v>
+        <v>490634</v>
       </c>
       <c r="R274" t="n">
-        <v>6820572</v>
+        <v>6821064</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -29232,7 +29232,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -29242,7 +29242,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -29269,10 +29269,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>130068565</v>
+        <v>130068648</v>
       </c>
       <c r="B275" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -29280,21 +29280,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -29304,10 +29304,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>490634</v>
+        <v>490376</v>
       </c>
       <c r="R275" t="n">
-        <v>6821064</v>
+        <v>6821407</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -29339,7 +29339,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -29349,7 +29349,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -29376,10 +29376,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>130068648</v>
+        <v>130068793</v>
       </c>
       <c r="B276" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -29387,21 +29387,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -29411,10 +29411,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>490376</v>
+        <v>491162</v>
       </c>
       <c r="R276" t="n">
-        <v>6821407</v>
+        <v>6820645</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -29446,7 +29446,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -29456,7 +29456,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -29483,7 +29483,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>130068793</v>
+        <v>130068730</v>
       </c>
       <c r="B277" t="n">
         <v>79095</v>
@@ -29518,10 +29518,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>491162</v>
+        <v>490555</v>
       </c>
       <c r="R277" t="n">
-        <v>6820645</v>
+        <v>6821236</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -29553,7 +29553,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -29563,7 +29563,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -29590,7 +29590,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>130068730</v>
+        <v>130068720</v>
       </c>
       <c r="B278" t="n">
         <v>79095</v>
@@ -29625,10 +29625,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>490555</v>
+        <v>490558</v>
       </c>
       <c r="R278" t="n">
-        <v>6821236</v>
+        <v>6821331</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -29660,7 +29660,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -29670,7 +29670,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -29697,7 +29697,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>130068720</v>
+        <v>130068827</v>
       </c>
       <c r="B279" t="n">
         <v>79095</v>
@@ -29732,10 +29732,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>490558</v>
+        <v>490946</v>
       </c>
       <c r="R279" t="n">
-        <v>6821331</v>
+        <v>6820565</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -29767,7 +29767,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -29777,7 +29777,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -29804,7 +29804,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>130068827</v>
+        <v>130068843</v>
       </c>
       <c r="B280" t="n">
         <v>79095</v>
@@ -29839,10 +29839,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>490946</v>
+        <v>490983</v>
       </c>
       <c r="R280" t="n">
-        <v>6820565</v>
+        <v>6820765</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29874,7 +29874,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -29884,7 +29884,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -29911,7 +29911,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>130068843</v>
+        <v>130068817</v>
       </c>
       <c r="B281" t="n">
         <v>79095</v>
@@ -29946,10 +29946,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>490983</v>
+        <v>491139</v>
       </c>
       <c r="R281" t="n">
-        <v>6820765</v>
+        <v>6820498</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -29981,7 +29981,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -29991,7 +29991,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -30018,7 +30018,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>130068817</v>
+        <v>130068691</v>
       </c>
       <c r="B282" t="n">
         <v>79095</v>
@@ -30053,10 +30053,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>491139</v>
+        <v>490386</v>
       </c>
       <c r="R282" t="n">
-        <v>6820498</v>
+        <v>6821339</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -30088,7 +30088,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -30098,7 +30098,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -30125,32 +30125,32 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>130068691</v>
+        <v>130068918</v>
       </c>
       <c r="B283" t="n">
-        <v>79095</v>
+        <v>92921</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -30160,10 +30160,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>490386</v>
+        <v>490996</v>
       </c>
       <c r="R283" t="n">
-        <v>6821339</v>
+        <v>6820534</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -30195,7 +30195,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -30205,7 +30205,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -33772,32 +33772,32 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>130068591</v>
+        <v>130068650</v>
       </c>
       <c r="B317" t="n">
-        <v>91603</v>
+        <v>78852</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
@@ -33807,10 +33807,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>490750</v>
+        <v>490380</v>
       </c>
       <c r="R317" t="n">
-        <v>6820956</v>
+        <v>6821325</v>
       </c>
       <c r="S317" t="n">
         <v>10</v>
@@ -33842,7 +33842,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -33852,7 +33852,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD317" t="b">
@@ -33879,32 +33879,32 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>130068808</v>
+        <v>130068591</v>
       </c>
       <c r="B318" t="n">
-        <v>79095</v>
+        <v>91603</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I318" t="inlineStr"/>
@@ -33914,10 +33914,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>491244</v>
+        <v>490750</v>
       </c>
       <c r="R318" t="n">
-        <v>6820561</v>
+        <v>6820956</v>
       </c>
       <c r="S318" t="n">
         <v>10</v>
@@ -33949,7 +33949,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -33959,7 +33959,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD318" t="b">
@@ -33986,10 +33986,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>130068584</v>
+        <v>130068739</v>
       </c>
       <c r="B319" t="n">
-        <v>79127</v>
+        <v>79095</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -33997,21 +33997,21 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I319" t="inlineStr"/>
@@ -34021,10 +34021,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>490537</v>
+        <v>490569</v>
       </c>
       <c r="R319" t="n">
-        <v>6821254</v>
+        <v>6821203</v>
       </c>
       <c r="S319" t="n">
         <v>10</v>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -34066,7 +34066,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD319" t="b">
@@ -34093,10 +34093,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>130068929</v>
+        <v>130068717</v>
       </c>
       <c r="B320" t="n">
-        <v>78761</v>
+        <v>79095</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -34104,21 +34104,21 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
@@ -34128,10 +34128,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>490662</v>
+        <v>490489</v>
       </c>
       <c r="R320" t="n">
-        <v>6820980</v>
+        <v>6821341</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -34163,7 +34163,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD320" t="b">
@@ -34200,7 +34200,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>130068911</v>
+        <v>130068842</v>
       </c>
       <c r="B321" t="n">
         <v>79095</v>
@@ -34235,10 +34235,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>490465</v>
+        <v>490953</v>
       </c>
       <c r="R321" t="n">
-        <v>6821283</v>
+        <v>6820764</v>
       </c>
       <c r="S321" t="n">
         <v>10</v>
@@ -34270,7 +34270,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -34280,7 +34280,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -34307,10 +34307,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>130068650</v>
+        <v>130068822</v>
       </c>
       <c r="B322" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -34318,21 +34318,21 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
@@ -34342,10 +34342,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>490380</v>
+        <v>491047</v>
       </c>
       <c r="R322" t="n">
-        <v>6821325</v>
+        <v>6820558</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -34377,7 +34377,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -34387,7 +34387,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -34414,7 +34414,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>130068739</v>
+        <v>130068879</v>
       </c>
       <c r="B323" t="n">
         <v>79095</v>
@@ -34449,10 +34449,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>490569</v>
+        <v>490669</v>
       </c>
       <c r="R323" t="n">
-        <v>6821203</v>
+        <v>6821033</v>
       </c>
       <c r="S323" t="n">
         <v>10</v>
@@ -34484,7 +34484,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -34494,7 +34494,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -34521,7 +34521,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>130068717</v>
+        <v>130068892</v>
       </c>
       <c r="B324" t="n">
         <v>79095</v>
@@ -34556,10 +34556,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>490489</v>
+        <v>490511</v>
       </c>
       <c r="R324" t="n">
-        <v>6821341</v>
+        <v>6821122</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -34591,7 +34591,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -34628,10 +34628,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>130068842</v>
+        <v>130068584</v>
       </c>
       <c r="B325" t="n">
-        <v>79095</v>
+        <v>79127</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -34639,21 +34639,21 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
@@ -34663,10 +34663,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>490953</v>
+        <v>490537</v>
       </c>
       <c r="R325" t="n">
-        <v>6820764</v>
+        <v>6821254</v>
       </c>
       <c r="S325" t="n">
         <v>10</v>
@@ -34698,7 +34698,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -34708,7 +34708,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD325" t="b">
@@ -34735,10 +34735,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>130068822</v>
+        <v>130068929</v>
       </c>
       <c r="B326" t="n">
-        <v>79095</v>
+        <v>78761</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -34746,21 +34746,21 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
@@ -34770,10 +34770,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>491047</v>
+        <v>490662</v>
       </c>
       <c r="R326" t="n">
-        <v>6820558</v>
+        <v>6820980</v>
       </c>
       <c r="S326" t="n">
         <v>10</v>
@@ -34805,7 +34805,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -34815,7 +34815,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD326" t="b">
@@ -34842,7 +34842,7 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>130068879</v>
+        <v>130068808</v>
       </c>
       <c r="B327" t="n">
         <v>79095</v>
@@ -34877,10 +34877,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>490669</v>
+        <v>491244</v>
       </c>
       <c r="R327" t="n">
-        <v>6821033</v>
+        <v>6820561</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -34912,7 +34912,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -34922,7 +34922,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD327" t="b">
@@ -34949,7 +34949,7 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>130068892</v>
+        <v>130068911</v>
       </c>
       <c r="B328" t="n">
         <v>79095</v>
@@ -34984,10 +34984,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>490511</v>
+        <v>490465</v>
       </c>
       <c r="R328" t="n">
-        <v>6821122</v>
+        <v>6821283</v>
       </c>
       <c r="S328" t="n">
         <v>10</v>
@@ -35019,7 +35019,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -35029,7 +35029,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD328" t="b">

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -11857,10 +11857,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130068625</v>
+        <v>130068576</v>
       </c>
       <c r="B113" t="n">
-        <v>91692</v>
+        <v>79714</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11868,21 +11868,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11892,10 +11892,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>490368</v>
+        <v>490574</v>
       </c>
       <c r="R113" t="n">
-        <v>6821331</v>
+        <v>6821123</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11964,10 +11964,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130068899</v>
+        <v>130068560</v>
       </c>
       <c r="B114" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11975,21 +11975,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11999,10 +11999,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>490483</v>
+        <v>490330</v>
       </c>
       <c r="R114" t="n">
-        <v>6821119</v>
+        <v>6821427</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12071,32 +12071,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130068620</v>
+        <v>130068574</v>
       </c>
       <c r="B115" t="n">
-        <v>79119</v>
+        <v>79714</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12106,10 +12106,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>490403</v>
+        <v>490884</v>
       </c>
       <c r="R115" t="n">
-        <v>6821241</v>
+        <v>6820910</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12178,10 +12178,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130068721</v>
+        <v>130068659</v>
       </c>
       <c r="B116" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12189,21 +12189,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>490529</v>
+        <v>490573</v>
       </c>
       <c r="R116" t="n">
-        <v>6821302</v>
+        <v>6821128</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12285,10 +12285,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130068904</v>
+        <v>130068567</v>
       </c>
       <c r="B117" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12296,21 +12296,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12320,10 +12320,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>490473</v>
+        <v>490688</v>
       </c>
       <c r="R117" t="n">
-        <v>6821203</v>
+        <v>6821009</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12392,7 +12392,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130068912</v>
+        <v>130068768</v>
       </c>
       <c r="B118" t="n">
         <v>79095</v>
@@ -12427,10 +12427,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490458</v>
+        <v>490712</v>
       </c>
       <c r="R118" t="n">
-        <v>6821315</v>
+        <v>6820983</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12462,7 +12462,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12499,10 +12499,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130068576</v>
+        <v>130068907</v>
       </c>
       <c r="B119" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12510,21 +12510,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12534,10 +12534,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>490574</v>
+        <v>490441</v>
       </c>
       <c r="R119" t="n">
-        <v>6821123</v>
+        <v>6821216</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12606,10 +12606,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130068560</v>
+        <v>130068729</v>
       </c>
       <c r="B120" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12617,21 +12617,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12641,10 +12641,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>490330</v>
+        <v>490543</v>
       </c>
       <c r="R120" t="n">
-        <v>6821427</v>
+        <v>6821249</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12676,7 +12676,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12713,10 +12713,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130068574</v>
+        <v>130068814</v>
       </c>
       <c r="B121" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12724,21 +12724,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490884</v>
+        <v>491167</v>
       </c>
       <c r="R121" t="n">
-        <v>6820910</v>
+        <v>6820511</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12820,10 +12820,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130068659</v>
+        <v>130068800</v>
       </c>
       <c r="B122" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12831,21 +12831,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12855,10 +12855,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>490573</v>
+        <v>491225</v>
       </c>
       <c r="R122" t="n">
-        <v>6821128</v>
+        <v>6820604</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12927,10 +12927,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130068567</v>
+        <v>130068693</v>
       </c>
       <c r="B123" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12938,21 +12938,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12962,10 +12962,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>490688</v>
+        <v>490375</v>
       </c>
       <c r="R123" t="n">
-        <v>6821009</v>
+        <v>6821308</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13034,10 +13034,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130068585</v>
+        <v>130068878</v>
       </c>
       <c r="B124" t="n">
-        <v>79127</v>
+        <v>79095</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13045,21 +13045,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13069,10 +13069,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490543</v>
+        <v>490675</v>
       </c>
       <c r="R124" t="n">
-        <v>6821250</v>
+        <v>6821023</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13141,7 +13141,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130068768</v>
+        <v>130068713</v>
       </c>
       <c r="B125" t="n">
         <v>79095</v>
@@ -13176,10 +13176,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>490712</v>
+        <v>490449</v>
       </c>
       <c r="R125" t="n">
-        <v>6820983</v>
+        <v>6821335</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13211,7 +13211,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13248,10 +13248,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130068907</v>
+        <v>130068625</v>
       </c>
       <c r="B126" t="n">
-        <v>79095</v>
+        <v>91692</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13259,21 +13259,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13283,10 +13283,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>490441</v>
+        <v>490368</v>
       </c>
       <c r="R126" t="n">
-        <v>6821216</v>
+        <v>6821331</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13355,10 +13355,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130068729</v>
+        <v>130068585</v>
       </c>
       <c r="B127" t="n">
-        <v>79095</v>
+        <v>79127</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13366,21 +13366,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13393,7 +13393,7 @@
         <v>490543</v>
       </c>
       <c r="R127" t="n">
-        <v>6821249</v>
+        <v>6821250</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13462,7 +13462,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130068814</v>
+        <v>130068899</v>
       </c>
       <c r="B128" t="n">
         <v>79095</v>
@@ -13497,10 +13497,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>491167</v>
+        <v>490483</v>
       </c>
       <c r="R128" t="n">
-        <v>6820511</v>
+        <v>6821119</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13569,32 +13569,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130068800</v>
+        <v>130068620</v>
       </c>
       <c r="B129" t="n">
-        <v>79095</v>
+        <v>79119</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13604,10 +13604,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>491225</v>
+        <v>490403</v>
       </c>
       <c r="R129" t="n">
-        <v>6820604</v>
+        <v>6821241</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13676,32 +13676,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130068693</v>
+        <v>130068919</v>
       </c>
       <c r="B130" t="n">
-        <v>79095</v>
+        <v>92921</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13711,10 +13711,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>490375</v>
+        <v>490993</v>
       </c>
       <c r="R130" t="n">
-        <v>6821308</v>
+        <v>6820630</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13746,7 +13746,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13783,7 +13783,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130068878</v>
+        <v>130068721</v>
       </c>
       <c r="B131" t="n">
         <v>79095</v>
@@ -13818,10 +13818,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>490675</v>
+        <v>490529</v>
       </c>
       <c r="R131" t="n">
-        <v>6821023</v>
+        <v>6821302</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13890,7 +13890,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130068713</v>
+        <v>130068904</v>
       </c>
       <c r="B132" t="n">
         <v>79095</v>
@@ -13925,10 +13925,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>490449</v>
+        <v>490473</v>
       </c>
       <c r="R132" t="n">
-        <v>6821335</v>
+        <v>6821203</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13997,32 +13997,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130068919</v>
+        <v>130068912</v>
       </c>
       <c r="B133" t="n">
-        <v>92921</v>
+        <v>79095</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>490993</v>
+        <v>490458</v>
       </c>
       <c r="R133" t="n">
-        <v>6820630</v>
+        <v>6821315</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14077,7 +14077,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14211,10 +14211,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130068633</v>
+        <v>130068594</v>
       </c>
       <c r="B135" t="n">
-        <v>8451</v>
+        <v>56931</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14222,27 +14222,27 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>491186</v>
+        <v>490601</v>
       </c>
       <c r="R135" t="n">
-        <v>6820622</v>
+        <v>6821175</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14286,7 +14286,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14323,42 +14323,38 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130068667</v>
+        <v>130068633</v>
       </c>
       <c r="B136" t="n">
-        <v>98831</v>
+        <v>8451</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -14367,10 +14363,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>490666</v>
+        <v>491186</v>
       </c>
       <c r="R136" t="n">
-        <v>6821043</v>
+        <v>6820622</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14402,7 +14398,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14412,7 +14408,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14439,10 +14435,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130068797</v>
+        <v>130068926</v>
       </c>
       <c r="B137" t="n">
-        <v>79095</v>
+        <v>78761</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14450,21 +14446,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14474,10 +14470,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>491182</v>
+        <v>491190</v>
       </c>
       <c r="R137" t="n">
-        <v>6820616</v>
+        <v>6820607</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14509,7 +14505,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14519,7 +14515,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14546,10 +14542,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130068885</v>
+        <v>130068587</v>
       </c>
       <c r="B138" t="n">
-        <v>79095</v>
+        <v>79127</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14557,21 +14553,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14581,10 +14577,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>490562</v>
+        <v>491161</v>
       </c>
       <c r="R138" t="n">
-        <v>6821132</v>
+        <v>6820628</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14616,7 +14612,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14626,7 +14622,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14653,10 +14649,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130068867</v>
+        <v>130068605</v>
       </c>
       <c r="B139" t="n">
-        <v>79095</v>
+        <v>91590</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14664,21 +14660,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14688,10 +14684,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>490726</v>
+        <v>490521</v>
       </c>
       <c r="R139" t="n">
-        <v>6820965</v>
+        <v>6821298</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14723,7 +14719,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14733,7 +14729,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14760,7 +14756,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130068781</v>
+        <v>130068840</v>
       </c>
       <c r="B140" t="n">
         <v>79095</v>
@@ -14795,10 +14791,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>491160</v>
+        <v>490857</v>
       </c>
       <c r="R140" t="n">
-        <v>6820813</v>
+        <v>6820652</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14830,7 +14826,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14840,7 +14836,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14867,7 +14863,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130068836</v>
+        <v>130068873</v>
       </c>
       <c r="B141" t="n">
         <v>79095</v>
@@ -14902,10 +14898,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>490945</v>
+        <v>490656</v>
       </c>
       <c r="R141" t="n">
-        <v>6820623</v>
+        <v>6820985</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14937,7 +14933,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14947,7 +14943,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14974,7 +14970,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130068902</v>
+        <v>130068833</v>
       </c>
       <c r="B142" t="n">
         <v>79095</v>
@@ -15009,10 +15005,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>490481</v>
+        <v>490971</v>
       </c>
       <c r="R142" t="n">
-        <v>6821182</v>
+        <v>6820633</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15044,7 +15040,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15054,7 +15050,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15081,7 +15077,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130068718</v>
+        <v>130068776</v>
       </c>
       <c r="B143" t="n">
         <v>79095</v>
@@ -15116,10 +15112,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>490492</v>
+        <v>491154</v>
       </c>
       <c r="R143" t="n">
-        <v>6821351</v>
+        <v>6820794</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15151,7 +15147,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15161,7 +15157,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15188,10 +15184,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130068840</v>
+        <v>130068660</v>
       </c>
       <c r="B144" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15199,21 +15195,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15223,10 +15219,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>490857</v>
+        <v>490550</v>
       </c>
       <c r="R144" t="n">
-        <v>6820652</v>
+        <v>6821160</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15258,7 +15254,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15268,7 +15264,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15295,10 +15291,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130068873</v>
+        <v>130068657</v>
       </c>
       <c r="B145" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15306,21 +15302,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15330,10 +15326,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>490656</v>
+        <v>490961</v>
       </c>
       <c r="R145" t="n">
-        <v>6820985</v>
+        <v>6820600</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15365,7 +15361,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15375,7 +15371,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15402,32 +15398,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130068833</v>
+        <v>130068623</v>
       </c>
       <c r="B146" t="n">
-        <v>79095</v>
+        <v>80228</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15437,10 +15433,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>490971</v>
+        <v>490594</v>
       </c>
       <c r="R146" t="n">
-        <v>6820633</v>
+        <v>6821177</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15472,7 +15468,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15482,7 +15478,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15509,10 +15505,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130068776</v>
+        <v>130068563</v>
       </c>
       <c r="B147" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15520,21 +15516,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15544,10 +15540,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>491154</v>
+        <v>490629</v>
       </c>
       <c r="R147" t="n">
-        <v>6820794</v>
+        <v>6821073</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15579,7 +15575,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15589,7 +15585,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15616,10 +15612,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130068660</v>
+        <v>130068797</v>
       </c>
       <c r="B148" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15627,21 +15623,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15651,10 +15647,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>490550</v>
+        <v>491182</v>
       </c>
       <c r="R148" t="n">
-        <v>6821160</v>
+        <v>6820616</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15686,7 +15682,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15696,7 +15692,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15723,10 +15719,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130068657</v>
+        <v>130068885</v>
       </c>
       <c r="B149" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15734,21 +15730,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15758,10 +15754,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>490961</v>
+        <v>490562</v>
       </c>
       <c r="R149" t="n">
-        <v>6820600</v>
+        <v>6821132</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15793,7 +15789,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15803,7 +15799,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15830,32 +15826,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130068623</v>
+        <v>130068867</v>
       </c>
       <c r="B150" t="n">
-        <v>80228</v>
+        <v>79095</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15865,10 +15861,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>490594</v>
+        <v>490726</v>
       </c>
       <c r="R150" t="n">
-        <v>6821177</v>
+        <v>6820965</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15900,7 +15896,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -15910,7 +15906,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15937,10 +15933,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130068563</v>
+        <v>130068781</v>
       </c>
       <c r="B151" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15948,21 +15944,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15972,10 +15968,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>490629</v>
+        <v>491160</v>
       </c>
       <c r="R151" t="n">
-        <v>6821073</v>
+        <v>6820813</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16007,7 +16003,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16017,7 +16013,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16044,50 +16040,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130068594</v>
+        <v>130068836</v>
       </c>
       <c r="B152" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>490601</v>
+        <v>490945</v>
       </c>
       <c r="R152" t="n">
-        <v>6821175</v>
+        <v>6820623</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16119,7 +16110,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16129,7 +16120,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16156,10 +16147,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130068926</v>
+        <v>130068902</v>
       </c>
       <c r="B153" t="n">
-        <v>78761</v>
+        <v>79095</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16167,21 +16158,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16191,10 +16182,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>491190</v>
+        <v>490481</v>
       </c>
       <c r="R153" t="n">
-        <v>6820607</v>
+        <v>6821182</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16226,7 +16217,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16236,7 +16227,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16263,10 +16254,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130068587</v>
+        <v>130068718</v>
       </c>
       <c r="B154" t="n">
-        <v>79127</v>
+        <v>79095</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16274,21 +16265,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16298,10 +16289,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>491161</v>
+        <v>490492</v>
       </c>
       <c r="R154" t="n">
-        <v>6820628</v>
+        <v>6821351</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16333,7 +16324,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16343,7 +16334,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16370,45 +16361,54 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130068605</v>
+        <v>130068667</v>
       </c>
       <c r="B155" t="n">
-        <v>91590</v>
+        <v>98831</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>490521</v>
+        <v>490666</v>
       </c>
       <c r="R155" t="n">
-        <v>6821298</v>
+        <v>6821043</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16477,10 +16477,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130068895</v>
+        <v>130068653</v>
       </c>
       <c r="B156" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16488,21 +16488,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16512,10 +16512,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>490488</v>
+        <v>490522</v>
       </c>
       <c r="R156" t="n">
-        <v>6821089</v>
+        <v>6821366</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16547,7 +16547,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16584,10 +16584,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130068753</v>
+        <v>130068914</v>
       </c>
       <c r="B157" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16595,34 +16595,39 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>490636</v>
+        <v>490384</v>
       </c>
       <c r="R157" t="n">
-        <v>6821100</v>
+        <v>6821397</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16654,7 +16659,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16664,7 +16669,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16691,32 +16696,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130068848</v>
+        <v>130068617</v>
       </c>
       <c r="B158" t="n">
-        <v>79095</v>
+        <v>97702</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16726,10 +16731,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>490995</v>
+        <v>490994</v>
       </c>
       <c r="R158" t="n">
-        <v>6820786</v>
+        <v>6820825</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16761,7 +16766,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16771,7 +16776,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16798,7 +16803,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130068845</v>
+        <v>130068895</v>
       </c>
       <c r="B159" t="n">
         <v>79095</v>
@@ -16833,10 +16838,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>490996</v>
+        <v>490488</v>
       </c>
       <c r="R159" t="n">
-        <v>6820767</v>
+        <v>6821089</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16868,7 +16873,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -16878,7 +16883,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16905,7 +16910,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130068877</v>
+        <v>130068753</v>
       </c>
       <c r="B160" t="n">
         <v>79095</v>
@@ -16940,10 +16945,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>490683</v>
+        <v>490636</v>
       </c>
       <c r="R160" t="n">
-        <v>6821011</v>
+        <v>6821100</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16975,7 +16980,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -16985,7 +16990,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17012,7 +17017,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130068701</v>
+        <v>130068848</v>
       </c>
       <c r="B161" t="n">
         <v>79095</v>
@@ -17047,10 +17052,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>490427</v>
+        <v>490995</v>
       </c>
       <c r="R161" t="n">
-        <v>6821240</v>
+        <v>6820786</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17082,7 +17087,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17092,7 +17097,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17119,10 +17124,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130068627</v>
+        <v>130068845</v>
       </c>
       <c r="B162" t="n">
-        <v>92959</v>
+        <v>79095</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17130,21 +17135,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17154,10 +17159,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>491012</v>
+        <v>490996</v>
       </c>
       <c r="R162" t="n">
-        <v>6820821</v>
+        <v>6820767</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17189,7 +17194,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17199,7 +17204,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17226,7 +17231,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>130068716</v>
+        <v>130068877</v>
       </c>
       <c r="B163" t="n">
         <v>79095</v>
@@ -17261,10 +17266,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>490456</v>
+        <v>490683</v>
       </c>
       <c r="R163" t="n">
-        <v>6821350</v>
+        <v>6821011</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17296,7 +17301,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17306,7 +17311,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17333,32 +17338,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130068617</v>
+        <v>130068701</v>
       </c>
       <c r="B164" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17368,10 +17373,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>490994</v>
+        <v>490427</v>
       </c>
       <c r="R164" t="n">
-        <v>6820825</v>
+        <v>6821240</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17403,7 +17408,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17413,7 +17418,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17440,10 +17445,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130068653</v>
+        <v>130068627</v>
       </c>
       <c r="B165" t="n">
-        <v>78852</v>
+        <v>92959</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17451,21 +17456,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17475,10 +17480,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>490522</v>
+        <v>491012</v>
       </c>
       <c r="R165" t="n">
-        <v>6821366</v>
+        <v>6820821</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17510,7 +17515,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17520,7 +17525,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17547,10 +17552,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>130068914</v>
+        <v>130068716</v>
       </c>
       <c r="B166" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17558,39 +17563,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>490384</v>
+        <v>490456</v>
       </c>
       <c r="R166" t="n">
-        <v>6821397</v>
+        <v>6821350</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17632,7 +17632,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20129,10 +20129,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>130068930</v>
+        <v>130068642</v>
       </c>
       <c r="B190" t="n">
-        <v>78761</v>
+        <v>80200</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20140,21 +20140,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20164,10 +20164,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>490563</v>
+        <v>491110</v>
       </c>
       <c r="R190" t="n">
-        <v>6821133</v>
+        <v>6820801</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20209,7 +20209,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20236,10 +20236,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>130068741</v>
+        <v>130068561</v>
       </c>
       <c r="B191" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20247,21 +20247,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20271,10 +20271,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>490578</v>
+        <v>490380</v>
       </c>
       <c r="R191" t="n">
-        <v>6821202</v>
+        <v>6821325</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20343,10 +20343,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>130068785</v>
+        <v>130068930</v>
       </c>
       <c r="B192" t="n">
-        <v>79095</v>
+        <v>78761</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20354,21 +20354,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20378,10 +20378,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>491178</v>
+        <v>490563</v>
       </c>
       <c r="R192" t="n">
-        <v>6820798</v>
+        <v>6821133</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20413,7 +20413,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20450,7 +20450,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>130068806</v>
+        <v>130068741</v>
       </c>
       <c r="B193" t="n">
         <v>79095</v>
@@ -20485,10 +20485,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>491242</v>
+        <v>490578</v>
       </c>
       <c r="R193" t="n">
-        <v>6820579</v>
+        <v>6821202</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20520,7 +20520,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20530,7 +20530,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20557,10 +20557,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>130068607</v>
+        <v>130068785</v>
       </c>
       <c r="B194" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20568,39 +20568,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>490376</v>
+        <v>491178</v>
       </c>
       <c r="R194" t="n">
-        <v>6821479</v>
+        <v>6820798</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20632,7 +20627,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20642,7 +20637,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20669,10 +20664,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>130068561</v>
+        <v>130068806</v>
       </c>
       <c r="B195" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20680,21 +20675,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20704,10 +20699,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>490380</v>
+        <v>491242</v>
       </c>
       <c r="R195" t="n">
-        <v>6821325</v>
+        <v>6820579</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20739,7 +20734,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20749,7 +20744,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20776,10 +20771,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>130068570</v>
+        <v>130068607</v>
       </c>
       <c r="B196" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20787,34 +20782,39 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>490731</v>
+        <v>490376</v>
       </c>
       <c r="R196" t="n">
-        <v>6820976</v>
+        <v>6821479</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20846,7 +20846,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20856,7 +20856,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20883,10 +20883,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>130068658</v>
+        <v>130068570</v>
       </c>
       <c r="B197" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20894,21 +20894,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20918,10 +20918,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>490643</v>
+        <v>490731</v>
       </c>
       <c r="R197" t="n">
-        <v>6821043</v>
+        <v>6820976</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20990,10 +20990,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>130068898</v>
+        <v>130068658</v>
       </c>
       <c r="B198" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21001,21 +21001,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21025,10 +21025,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>490480</v>
+        <v>490643</v>
       </c>
       <c r="R198" t="n">
-        <v>6821113</v>
+        <v>6821043</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21070,7 +21070,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21097,7 +21097,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>130068748</v>
+        <v>130068898</v>
       </c>
       <c r="B199" t="n">
         <v>79095</v>
@@ -21132,10 +21132,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>490584</v>
+        <v>490480</v>
       </c>
       <c r="R199" t="n">
-        <v>6821145</v>
+        <v>6821113</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21167,7 +21167,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21177,7 +21177,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21204,7 +21204,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>130068719</v>
+        <v>130068748</v>
       </c>
       <c r="B200" t="n">
         <v>79095</v>
@@ -21239,10 +21239,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>490534</v>
+        <v>490584</v>
       </c>
       <c r="R200" t="n">
-        <v>6821348</v>
+        <v>6821145</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21274,7 +21274,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21311,7 +21311,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>130068771</v>
+        <v>130068719</v>
       </c>
       <c r="B201" t="n">
         <v>79095</v>
@@ -21346,10 +21346,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>490799</v>
+        <v>490534</v>
       </c>
       <c r="R201" t="n">
-        <v>6820989</v>
+        <v>6821348</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21418,7 +21418,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>130068837</v>
+        <v>130068771</v>
       </c>
       <c r="B202" t="n">
         <v>79095</v>
@@ -21453,10 +21453,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>490932</v>
+        <v>490799</v>
       </c>
       <c r="R202" t="n">
-        <v>6820625</v>
+        <v>6820989</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21498,7 +21498,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21525,7 +21525,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>130068712</v>
+        <v>130068837</v>
       </c>
       <c r="B203" t="n">
         <v>79095</v>
@@ -21560,10 +21560,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>490440</v>
+        <v>490932</v>
       </c>
       <c r="R203" t="n">
-        <v>6821320</v>
+        <v>6820625</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21595,7 +21595,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -21605,7 +21605,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21632,10 +21632,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>130068596</v>
+        <v>130068712</v>
       </c>
       <c r="B204" t="n">
-        <v>57900</v>
+        <v>79095</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21643,50 +21643,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>490604</v>
+        <v>490440</v>
       </c>
       <c r="R204" t="n">
-        <v>6821185</v>
+        <v>6821320</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21718,7 +21702,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -21728,7 +21712,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21755,10 +21739,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>130068642</v>
+        <v>130068596</v>
       </c>
       <c r="B205" t="n">
-        <v>80200</v>
+        <v>57900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21766,34 +21750,50 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>491110</v>
+        <v>490604</v>
       </c>
       <c r="R205" t="n">
-        <v>6820801</v>
+        <v>6821185</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21825,7 +21825,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -21835,7 +21835,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21862,10 +21862,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>130068757</v>
+        <v>130068610</v>
       </c>
       <c r="B206" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21873,21 +21873,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21897,10 +21897,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>490676</v>
+        <v>490684</v>
       </c>
       <c r="R206" t="n">
-        <v>6821055</v>
+        <v>6820964</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21932,7 +21932,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -21942,7 +21942,12 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -21969,50 +21974,45 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>130068630</v>
+        <v>130068638</v>
       </c>
       <c r="B207" t="n">
-        <v>8451</v>
+        <v>78853</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>490672</v>
+        <v>490380</v>
       </c>
       <c r="R207" t="n">
-        <v>6821014</v>
+        <v>6821325</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22044,7 +22044,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22054,7 +22054,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22081,10 +22081,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>130068638</v>
+        <v>130068757</v>
       </c>
       <c r="B208" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22092,21 +22092,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -22116,10 +22116,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>490380</v>
+        <v>490676</v>
       </c>
       <c r="R208" t="n">
-        <v>6821325</v>
+        <v>6821055</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22151,7 +22151,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23472,45 +23472,50 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>130068610</v>
+        <v>130068630</v>
       </c>
       <c r="B221" t="n">
-        <v>57741</v>
+        <v>8451</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>490684</v>
+        <v>490672</v>
       </c>
       <c r="R221" t="n">
-        <v>6820964</v>
+        <v>6821014</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23542,7 +23547,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -23552,12 +23557,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -32809,32 +32809,32 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>130068622</v>
+        <v>130068634</v>
       </c>
       <c r="B308" t="n">
-        <v>80228</v>
+        <v>78853</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -32844,10 +32844,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>490534</v>
+        <v>490332</v>
       </c>
       <c r="R308" t="n">
-        <v>6821209</v>
+        <v>6821426</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -32879,7 +32879,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -32889,7 +32889,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -32916,32 +32916,32 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>130068603</v>
+        <v>130068639</v>
       </c>
       <c r="B309" t="n">
-        <v>80229</v>
+        <v>78853</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -32951,10 +32951,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>491182</v>
+        <v>490401</v>
       </c>
       <c r="R309" t="n">
-        <v>6820747</v>
+        <v>6821264</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -32986,7 +32986,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -32996,7 +32996,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -33023,32 +33023,32 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>130068702</v>
+        <v>130068622</v>
       </c>
       <c r="B310" t="n">
-        <v>79095</v>
+        <v>80228</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -33058,10 +33058,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>490438</v>
+        <v>490534</v>
       </c>
       <c r="R310" t="n">
-        <v>6821252</v>
+        <v>6821209</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -33093,7 +33093,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -33103,7 +33103,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -33130,32 +33130,32 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>130068686</v>
+        <v>130068603</v>
       </c>
       <c r="B311" t="n">
-        <v>79095</v>
+        <v>80229</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -33165,10 +33165,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>490393</v>
+        <v>491182</v>
       </c>
       <c r="R311" t="n">
-        <v>6821358</v>
+        <v>6820747</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -33200,7 +33200,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -33210,7 +33210,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -33237,7 +33237,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>130068749</v>
+        <v>130068702</v>
       </c>
       <c r="B312" t="n">
         <v>79095</v>
@@ -33272,10 +33272,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>490607</v>
+        <v>490438</v>
       </c>
       <c r="R312" t="n">
-        <v>6821129</v>
+        <v>6821252</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -33307,7 +33307,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -33317,7 +33317,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -33344,7 +33344,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>130068901</v>
+        <v>130068686</v>
       </c>
       <c r="B313" t="n">
         <v>79095</v>
@@ -33379,10 +33379,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>490479</v>
+        <v>490393</v>
       </c>
       <c r="R313" t="n">
-        <v>6821177</v>
+        <v>6821358</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -33414,7 +33414,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -33424,7 +33424,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -33451,7 +33451,7 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>130068875</v>
+        <v>130068749</v>
       </c>
       <c r="B314" t="n">
         <v>79095</v>
@@ -33486,10 +33486,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>490675</v>
+        <v>490607</v>
       </c>
       <c r="R314" t="n">
-        <v>6821007</v>
+        <v>6821129</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -33521,7 +33521,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -33531,7 +33531,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD314" t="b">
@@ -33558,10 +33558,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>130068634</v>
+        <v>130068901</v>
       </c>
       <c r="B315" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -33569,21 +33569,21 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -33593,10 +33593,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>490332</v>
+        <v>490479</v>
       </c>
       <c r="R315" t="n">
-        <v>6821426</v>
+        <v>6821177</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>
@@ -33628,7 +33628,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -33638,7 +33638,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD315" t="b">
@@ -33665,10 +33665,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>130068639</v>
+        <v>130068875</v>
       </c>
       <c r="B316" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -33676,21 +33676,21 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
@@ -33700,10 +33700,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>490401</v>
+        <v>490675</v>
       </c>
       <c r="R316" t="n">
-        <v>6821264</v>
+        <v>6821007</v>
       </c>
       <c r="S316" t="n">
         <v>10</v>
@@ -33735,7 +33735,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -33745,7 +33745,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD316" t="b">
@@ -33772,32 +33772,32 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>130068650</v>
+        <v>130068591</v>
       </c>
       <c r="B317" t="n">
-        <v>78852</v>
+        <v>91603</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
@@ -33807,10 +33807,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>490380</v>
+        <v>490750</v>
       </c>
       <c r="R317" t="n">
-        <v>6821325</v>
+        <v>6820956</v>
       </c>
       <c r="S317" t="n">
         <v>10</v>
@@ -33842,7 +33842,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -33852,7 +33852,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD317" t="b">
@@ -33879,32 +33879,32 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>130068591</v>
+        <v>130068808</v>
       </c>
       <c r="B318" t="n">
-        <v>91603</v>
+        <v>79095</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I318" t="inlineStr"/>
@@ -33914,10 +33914,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>490750</v>
+        <v>491244</v>
       </c>
       <c r="R318" t="n">
-        <v>6820956</v>
+        <v>6820561</v>
       </c>
       <c r="S318" t="n">
         <v>10</v>
@@ -33949,7 +33949,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -33959,7 +33959,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD318" t="b">
@@ -33986,10 +33986,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>130068739</v>
+        <v>130068584</v>
       </c>
       <c r="B319" t="n">
-        <v>79095</v>
+        <v>79127</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -33997,21 +33997,21 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I319" t="inlineStr"/>
@@ -34021,10 +34021,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>490569</v>
+        <v>490537</v>
       </c>
       <c r="R319" t="n">
-        <v>6821203</v>
+        <v>6821254</v>
       </c>
       <c r="S319" t="n">
         <v>10</v>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -34066,7 +34066,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD319" t="b">
@@ -34093,10 +34093,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>130068717</v>
+        <v>130068929</v>
       </c>
       <c r="B320" t="n">
-        <v>79095</v>
+        <v>78761</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -34104,21 +34104,21 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
@@ -34128,10 +34128,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>490489</v>
+        <v>490662</v>
       </c>
       <c r="R320" t="n">
-        <v>6821341</v>
+        <v>6820980</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -34163,7 +34163,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD320" t="b">
@@ -34200,7 +34200,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>130068842</v>
+        <v>130068911</v>
       </c>
       <c r="B321" t="n">
         <v>79095</v>
@@ -34235,10 +34235,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>490953</v>
+        <v>490465</v>
       </c>
       <c r="R321" t="n">
-        <v>6820764</v>
+        <v>6821283</v>
       </c>
       <c r="S321" t="n">
         <v>10</v>
@@ -34270,7 +34270,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -34280,7 +34280,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -34307,10 +34307,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>130068822</v>
+        <v>130068650</v>
       </c>
       <c r="B322" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -34318,21 +34318,21 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
@@ -34342,10 +34342,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>491047</v>
+        <v>490380</v>
       </c>
       <c r="R322" t="n">
-        <v>6820558</v>
+        <v>6821325</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -34377,7 +34377,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -34387,7 +34387,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -34414,7 +34414,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>130068879</v>
+        <v>130068739</v>
       </c>
       <c r="B323" t="n">
         <v>79095</v>
@@ -34449,10 +34449,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>490669</v>
+        <v>490569</v>
       </c>
       <c r="R323" t="n">
-        <v>6821033</v>
+        <v>6821203</v>
       </c>
       <c r="S323" t="n">
         <v>10</v>
@@ -34484,7 +34484,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -34494,7 +34494,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -34521,7 +34521,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>130068892</v>
+        <v>130068717</v>
       </c>
       <c r="B324" t="n">
         <v>79095</v>
@@ -34556,10 +34556,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>490511</v>
+        <v>490489</v>
       </c>
       <c r="R324" t="n">
-        <v>6821122</v>
+        <v>6821341</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -34591,7 +34591,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -34628,10 +34628,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>130068584</v>
+        <v>130068842</v>
       </c>
       <c r="B325" t="n">
-        <v>79127</v>
+        <v>79095</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -34639,21 +34639,21 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
@@ -34663,10 +34663,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>490537</v>
+        <v>490953</v>
       </c>
       <c r="R325" t="n">
-        <v>6821254</v>
+        <v>6820764</v>
       </c>
       <c r="S325" t="n">
         <v>10</v>
@@ -34698,7 +34698,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -34708,7 +34708,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD325" t="b">
@@ -34735,10 +34735,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>130068929</v>
+        <v>130068822</v>
       </c>
       <c r="B326" t="n">
-        <v>78761</v>
+        <v>79095</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -34746,21 +34746,21 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
@@ -34770,10 +34770,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>490662</v>
+        <v>491047</v>
       </c>
       <c r="R326" t="n">
-        <v>6820980</v>
+        <v>6820558</v>
       </c>
       <c r="S326" t="n">
         <v>10</v>
@@ -34805,7 +34805,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -34815,7 +34815,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD326" t="b">
@@ -34842,7 +34842,7 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>130068808</v>
+        <v>130068879</v>
       </c>
       <c r="B327" t="n">
         <v>79095</v>
@@ -34877,10 +34877,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>491244</v>
+        <v>490669</v>
       </c>
       <c r="R327" t="n">
-        <v>6820561</v>
+        <v>6821033</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -34912,7 +34912,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -34922,7 +34922,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD327" t="b">
@@ -34949,7 +34949,7 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>130068911</v>
+        <v>130068892</v>
       </c>
       <c r="B328" t="n">
         <v>79095</v>
@@ -34984,10 +34984,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>490465</v>
+        <v>490511</v>
       </c>
       <c r="R328" t="n">
-        <v>6821283</v>
+        <v>6821122</v>
       </c>
       <c r="S328" t="n">
         <v>10</v>
@@ -35019,7 +35019,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -35029,7 +35029,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD328" t="b">
@@ -40122,45 +40122,50 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>130068572</v>
+        <v>130068595</v>
       </c>
       <c r="B376" t="n">
-        <v>79714</v>
+        <v>56931</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I376" t="inlineStr"/>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P376" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>490961</v>
+        <v>490535</v>
       </c>
       <c r="R376" t="n">
-        <v>6820600</v>
+        <v>6821122</v>
       </c>
       <c r="S376" t="n">
         <v>10</v>
@@ -40192,7 +40197,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -40202,7 +40207,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD376" t="b">
@@ -40229,10 +40234,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>130068568</v>
+        <v>130068925</v>
       </c>
       <c r="B377" t="n">
-        <v>79714</v>
+        <v>78761</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -40240,21 +40245,21 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I377" t="inlineStr"/>
@@ -40264,10 +40269,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>490698</v>
+        <v>490731</v>
       </c>
       <c r="R377" t="n">
-        <v>6821013</v>
+        <v>6820976</v>
       </c>
       <c r="S377" t="n">
         <v>10</v>
@@ -40299,7 +40304,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -40309,7 +40314,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD377" t="b">
@@ -40336,7 +40341,7 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>130068703</v>
+        <v>130068690</v>
       </c>
       <c r="B378" t="n">
         <v>79095</v>
@@ -40371,10 +40376,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>490436</v>
+        <v>490406</v>
       </c>
       <c r="R378" t="n">
-        <v>6821261</v>
+        <v>6821345</v>
       </c>
       <c r="S378" t="n">
         <v>10</v>
@@ -40406,7 +40411,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -40416,7 +40421,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD378" t="b">
@@ -40443,10 +40448,10 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>130068628</v>
+        <v>130068762</v>
       </c>
       <c r="B379" t="n">
-        <v>92959</v>
+        <v>79095</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -40454,21 +40459,21 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I379" t="inlineStr"/>
@@ -40478,10 +40483,10 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>490896</v>
+        <v>490687</v>
       </c>
       <c r="R379" t="n">
-        <v>6820806</v>
+        <v>6821018</v>
       </c>
       <c r="S379" t="n">
         <v>10</v>
@@ -40513,7 +40518,7 @@
       </c>
       <c r="Z379" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
@@ -40523,7 +40528,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD379" t="b">
@@ -40550,10 +40555,10 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>130068733</v>
+        <v>130068572</v>
       </c>
       <c r="B380" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -40561,21 +40566,21 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I380" t="inlineStr"/>
@@ -40585,10 +40590,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>490539</v>
+        <v>490961</v>
       </c>
       <c r="R380" t="n">
-        <v>6821218</v>
+        <v>6820600</v>
       </c>
       <c r="S380" t="n">
         <v>10</v>
@@ -40620,7 +40625,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -40630,7 +40635,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD380" t="b">
@@ -40657,10 +40662,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>130068761</v>
+        <v>130068568</v>
       </c>
       <c r="B381" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -40668,21 +40673,21 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I381" t="inlineStr"/>
@@ -40695,7 +40700,7 @@
         <v>490698</v>
       </c>
       <c r="R381" t="n">
-        <v>6821021</v>
+        <v>6821013</v>
       </c>
       <c r="S381" t="n">
         <v>10</v>
@@ -40727,7 +40732,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -40737,7 +40742,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD381" t="b">
@@ -40764,7 +40769,7 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>130068882</v>
+        <v>130068703</v>
       </c>
       <c r="B382" t="n">
         <v>79095</v>
@@ -40799,10 +40804,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>490609</v>
+        <v>490436</v>
       </c>
       <c r="R382" t="n">
-        <v>6821100</v>
+        <v>6821261</v>
       </c>
       <c r="S382" t="n">
         <v>10</v>
@@ -40834,7 +40839,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -40844,7 +40849,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD382" t="b">
@@ -40871,10 +40876,10 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>130068732</v>
+        <v>130068628</v>
       </c>
       <c r="B383" t="n">
-        <v>79095</v>
+        <v>92959</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -40882,21 +40887,21 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I383" t="inlineStr"/>
@@ -40906,10 +40911,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>490542</v>
+        <v>490896</v>
       </c>
       <c r="R383" t="n">
-        <v>6821224</v>
+        <v>6820806</v>
       </c>
       <c r="S383" t="n">
         <v>10</v>
@@ -40941,7 +40946,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -40951,7 +40956,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD383" t="b">
@@ -40978,10 +40983,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>130068925</v>
+        <v>130068733</v>
       </c>
       <c r="B384" t="n">
-        <v>78761</v>
+        <v>79095</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -40989,21 +40994,21 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I384" t="inlineStr"/>
@@ -41013,10 +41018,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>490731</v>
+        <v>490539</v>
       </c>
       <c r="R384" t="n">
-        <v>6820976</v>
+        <v>6821218</v>
       </c>
       <c r="S384" t="n">
         <v>10</v>
@@ -41048,7 +41053,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -41058,7 +41063,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD384" t="b">
@@ -41085,7 +41090,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>130068690</v>
+        <v>130068761</v>
       </c>
       <c r="B385" t="n">
         <v>79095</v>
@@ -41120,10 +41125,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>490406</v>
+        <v>490698</v>
       </c>
       <c r="R385" t="n">
-        <v>6821345</v>
+        <v>6821021</v>
       </c>
       <c r="S385" t="n">
         <v>10</v>
@@ -41155,7 +41160,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -41165,7 +41170,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD385" t="b">
@@ -41192,7 +41197,7 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>130068762</v>
+        <v>130068882</v>
       </c>
       <c r="B386" t="n">
         <v>79095</v>
@@ -41227,10 +41232,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>490687</v>
+        <v>490609</v>
       </c>
       <c r="R386" t="n">
-        <v>6821018</v>
+        <v>6821100</v>
       </c>
       <c r="S386" t="n">
         <v>10</v>
@@ -41262,7 +41267,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -41272,7 +41277,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD386" t="b">
@@ -41299,50 +41304,45 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>130068595</v>
+        <v>130068732</v>
       </c>
       <c r="B387" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I387" t="inlineStr"/>
-      <c r="M387" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P387" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>490535</v>
+        <v>490542</v>
       </c>
       <c r="R387" t="n">
-        <v>6821122</v>
+        <v>6821224</v>
       </c>
       <c r="S387" t="n">
         <v>10</v>
@@ -41374,7 +41374,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -41384,7 +41384,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD387" t="b">
@@ -41411,45 +41411,50 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>130068928</v>
+        <v>130068631</v>
       </c>
       <c r="B388" t="n">
-        <v>78761</v>
+        <v>8451</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr"/>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P388" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>490893</v>
+        <v>490558</v>
       </c>
       <c r="R388" t="n">
-        <v>6820651</v>
+        <v>6821203</v>
       </c>
       <c r="S388" t="n">
         <v>10</v>
@@ -41481,7 +41486,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -41491,7 +41496,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD388" t="b">
@@ -41518,10 +41523,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>130068644</v>
+        <v>130068928</v>
       </c>
       <c r="B389" t="n">
-        <v>81080</v>
+        <v>78761</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -41529,21 +41534,21 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I389" t="inlineStr"/>
@@ -41553,10 +41558,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>490352</v>
+        <v>490893</v>
       </c>
       <c r="R389" t="n">
-        <v>6821426</v>
+        <v>6820651</v>
       </c>
       <c r="S389" t="n">
         <v>10</v>
@@ -41588,7 +41593,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -41598,7 +41603,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD389" t="b">
@@ -41625,10 +41630,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>130068656</v>
+        <v>130068644</v>
       </c>
       <c r="B390" t="n">
-        <v>78852</v>
+        <v>81080</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -41636,21 +41641,21 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I390" t="inlineStr"/>
@@ -41660,10 +41665,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>490731</v>
+        <v>490352</v>
       </c>
       <c r="R390" t="n">
-        <v>6820976</v>
+        <v>6821426</v>
       </c>
       <c r="S390" t="n">
         <v>10</v>
@@ -41695,7 +41700,7 @@
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -41705,7 +41710,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD390" t="b">
@@ -41732,32 +41737,32 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>130068612</v>
+        <v>130068774</v>
       </c>
       <c r="B391" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I391" t="inlineStr"/>
@@ -41767,10 +41772,10 @@
         </is>
       </c>
       <c r="Q391" t="n">
-        <v>490645</v>
+        <v>491119</v>
       </c>
       <c r="R391" t="n">
-        <v>6821063</v>
+        <v>6820790</v>
       </c>
       <c r="S391" t="n">
         <v>10</v>
@@ -41802,7 +41807,7 @@
       </c>
       <c r="Z391" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA391" t="inlineStr">
@@ -41812,7 +41817,7 @@
       </c>
       <c r="AB391" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD391" t="b">
@@ -41839,32 +41844,32 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>130068616</v>
+        <v>130068715</v>
       </c>
       <c r="B392" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I392" t="inlineStr"/>
@@ -41874,10 +41879,10 @@
         </is>
       </c>
       <c r="Q392" t="n">
-        <v>491184</v>
+        <v>490454</v>
       </c>
       <c r="R392" t="n">
-        <v>6820708</v>
+        <v>6821354</v>
       </c>
       <c r="S392" t="n">
         <v>10</v>
@@ -41909,7 +41914,7 @@
       </c>
       <c r="Z392" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA392" t="inlineStr">
@@ -41919,7 +41924,7 @@
       </c>
       <c r="AB392" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD392" t="b">
@@ -41946,10 +41951,10 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>130068774</v>
+        <v>130068656</v>
       </c>
       <c r="B393" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -41957,21 +41962,21 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I393" t="inlineStr"/>
@@ -41981,10 +41986,10 @@
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>491119</v>
+        <v>490731</v>
       </c>
       <c r="R393" t="n">
-        <v>6820790</v>
+        <v>6820976</v>
       </c>
       <c r="S393" t="n">
         <v>10</v>
@@ -42016,7 +42021,7 @@
       </c>
       <c r="Z393" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA393" t="inlineStr">
@@ -42026,7 +42031,7 @@
       </c>
       <c r="AB393" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD393" t="b">
@@ -42053,7 +42058,7 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>130068715</v>
+        <v>130068685</v>
       </c>
       <c r="B394" t="n">
         <v>79095</v>
@@ -42088,10 +42093,10 @@
         </is>
       </c>
       <c r="Q394" t="n">
-        <v>490454</v>
+        <v>490423</v>
       </c>
       <c r="R394" t="n">
-        <v>6821354</v>
+        <v>6821356</v>
       </c>
       <c r="S394" t="n">
         <v>10</v>
@@ -42123,7 +42128,7 @@
       </c>
       <c r="Z394" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA394" t="inlineStr">
@@ -42133,7 +42138,7 @@
       </c>
       <c r="AB394" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD394" t="b">
@@ -42160,7 +42165,7 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>130068685</v>
+        <v>130068769</v>
       </c>
       <c r="B395" t="n">
         <v>79095</v>
@@ -42195,10 +42200,10 @@
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>490423</v>
+        <v>490786</v>
       </c>
       <c r="R395" t="n">
-        <v>6821356</v>
+        <v>6820988</v>
       </c>
       <c r="S395" t="n">
         <v>10</v>
@@ -42230,7 +42235,7 @@
       </c>
       <c r="Z395" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA395" t="inlineStr">
@@ -42240,7 +42245,7 @@
       </c>
       <c r="AB395" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD395" t="b">
@@ -42267,7 +42272,7 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>130068769</v>
+        <v>130068752</v>
       </c>
       <c r="B396" t="n">
         <v>79095</v>
@@ -42302,10 +42307,10 @@
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>490786</v>
+        <v>490624</v>
       </c>
       <c r="R396" t="n">
-        <v>6820988</v>
+        <v>6821125</v>
       </c>
       <c r="S396" t="n">
         <v>10</v>
@@ -42337,7 +42342,7 @@
       </c>
       <c r="Z396" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA396" t="inlineStr">
@@ -42347,7 +42352,7 @@
       </c>
       <c r="AB396" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD396" t="b">
@@ -42374,32 +42379,32 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>130068752</v>
+        <v>130068612</v>
       </c>
       <c r="B397" t="n">
-        <v>79095</v>
+        <v>97702</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I397" t="inlineStr"/>
@@ -42409,10 +42414,10 @@
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>490624</v>
+        <v>490645</v>
       </c>
       <c r="R397" t="n">
-        <v>6821125</v>
+        <v>6821063</v>
       </c>
       <c r="S397" t="n">
         <v>10</v>
@@ -42444,7 +42449,7 @@
       </c>
       <c r="Z397" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA397" t="inlineStr">
@@ -42454,7 +42459,7 @@
       </c>
       <c r="AB397" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD397" t="b">
@@ -42481,10 +42486,10 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>130068631</v>
+        <v>130068616</v>
       </c>
       <c r="B398" t="n">
-        <v>8451</v>
+        <v>97702</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -42492,39 +42497,34 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I398" t="inlineStr"/>
-      <c r="M398" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P398" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>490558</v>
+        <v>491184</v>
       </c>
       <c r="R398" t="n">
-        <v>6821203</v>
+        <v>6820708</v>
       </c>
       <c r="S398" t="n">
         <v>10</v>
@@ -42556,7 +42556,7 @@
       </c>
       <c r="Z398" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA398" t="inlineStr">
@@ -42566,7 +42566,7 @@
       </c>
       <c r="AB398" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD398" t="b">

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -11857,10 +11857,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130068585</v>
+        <v>130068625</v>
       </c>
       <c r="B113" t="n">
-        <v>79212</v>
+        <v>91781</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11868,21 +11868,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>185</v>
+        <v>2079</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11892,10 +11892,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>490543</v>
+        <v>490368</v>
       </c>
       <c r="R113" t="n">
-        <v>6821250</v>
+        <v>6821331</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11964,32 +11964,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130068625</v>
+        <v>130068919</v>
       </c>
       <c r="B114" t="n">
-        <v>91781</v>
+        <v>93010</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11999,10 +11999,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>490368</v>
+        <v>490993</v>
       </c>
       <c r="R114" t="n">
-        <v>6821331</v>
+        <v>6820630</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12071,32 +12071,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130068919</v>
+        <v>130068768</v>
       </c>
       <c r="B115" t="n">
-        <v>93010</v>
+        <v>79180</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12106,10 +12106,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>490993</v>
+        <v>490712</v>
       </c>
       <c r="R115" t="n">
-        <v>6820630</v>
+        <v>6820983</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12178,7 +12178,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130068768</v>
+        <v>130068814</v>
       </c>
       <c r="B116" t="n">
         <v>79180</v>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>490712</v>
+        <v>491167</v>
       </c>
       <c r="R116" t="n">
-        <v>6820983</v>
+        <v>6820511</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12285,7 +12285,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130068814</v>
+        <v>130068721</v>
       </c>
       <c r="B117" t="n">
         <v>79180</v>
@@ -12320,10 +12320,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>491167</v>
+        <v>490529</v>
       </c>
       <c r="R117" t="n">
-        <v>6820511</v>
+        <v>6821302</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12392,7 +12392,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130068721</v>
+        <v>130068904</v>
       </c>
       <c r="B118" t="n">
         <v>79180</v>
@@ -12427,10 +12427,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>490529</v>
+        <v>490473</v>
       </c>
       <c r="R118" t="n">
-        <v>6821302</v>
+        <v>6821203</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12462,7 +12462,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12499,7 +12499,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130068904</v>
+        <v>130068693</v>
       </c>
       <c r="B119" t="n">
         <v>79180</v>
@@ -12534,10 +12534,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>490473</v>
+        <v>490375</v>
       </c>
       <c r="R119" t="n">
-        <v>6821203</v>
+        <v>6821308</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12606,7 +12606,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130068693</v>
+        <v>130068907</v>
       </c>
       <c r="B120" t="n">
         <v>79180</v>
@@ -12641,10 +12641,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>490375</v>
+        <v>490441</v>
       </c>
       <c r="R120" t="n">
-        <v>6821308</v>
+        <v>6821216</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12676,7 +12676,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12713,7 +12713,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130068907</v>
+        <v>130068729</v>
       </c>
       <c r="B121" t="n">
         <v>79180</v>
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>490441</v>
+        <v>490543</v>
       </c>
       <c r="R121" t="n">
-        <v>6821216</v>
+        <v>6821249</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12820,7 +12820,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130068729</v>
+        <v>130068800</v>
       </c>
       <c r="B122" t="n">
         <v>79180</v>
@@ -12855,10 +12855,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>490543</v>
+        <v>491225</v>
       </c>
       <c r="R122" t="n">
-        <v>6821249</v>
+        <v>6820604</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12927,7 +12927,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130068800</v>
+        <v>130068912</v>
       </c>
       <c r="B123" t="n">
         <v>79180</v>
@@ -12962,10 +12962,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>491225</v>
+        <v>490458</v>
       </c>
       <c r="R123" t="n">
-        <v>6820604</v>
+        <v>6821315</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13034,7 +13034,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130068912</v>
+        <v>130068899</v>
       </c>
       <c r="B124" t="n">
         <v>79180</v>
@@ -13069,10 +13069,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>490458</v>
+        <v>490483</v>
       </c>
       <c r="R124" t="n">
-        <v>6821315</v>
+        <v>6821119</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13141,10 +13141,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130068899</v>
+        <v>130068585</v>
       </c>
       <c r="B125" t="n">
-        <v>79180</v>
+        <v>79212</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13152,21 +13152,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13176,10 +13176,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>490483</v>
+        <v>490543</v>
       </c>
       <c r="R125" t="n">
-        <v>6821119</v>
+        <v>6821250</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13211,7 +13211,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13462,10 +13462,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130068637</v>
+        <v>130068576</v>
       </c>
       <c r="B128" t="n">
-        <v>78938</v>
+        <v>79799</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13473,21 +13473,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13497,10 +13497,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>490393</v>
+        <v>490574</v>
       </c>
       <c r="R128" t="n">
-        <v>6821367</v>
+        <v>6821123</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13569,7 +13569,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130068576</v>
+        <v>130068567</v>
       </c>
       <c r="B129" t="n">
         <v>79799</v>
@@ -13604,10 +13604,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>490574</v>
+        <v>490688</v>
       </c>
       <c r="R129" t="n">
-        <v>6821123</v>
+        <v>6821009</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13676,7 +13676,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130068567</v>
+        <v>130068574</v>
       </c>
       <c r="B130" t="n">
         <v>79799</v>
@@ -13711,10 +13711,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>490688</v>
+        <v>490884</v>
       </c>
       <c r="R130" t="n">
-        <v>6821009</v>
+        <v>6820910</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13746,7 +13746,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13783,7 +13783,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130068574</v>
+        <v>130068560</v>
       </c>
       <c r="B131" t="n">
         <v>79799</v>
@@ -13818,10 +13818,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>490884</v>
+        <v>490330</v>
       </c>
       <c r="R131" t="n">
-        <v>6820910</v>
+        <v>6821427</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13890,32 +13890,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130068560</v>
+        <v>130068620</v>
       </c>
       <c r="B132" t="n">
-        <v>79799</v>
+        <v>79204</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13925,10 +13925,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>490330</v>
+        <v>490403</v>
       </c>
       <c r="R132" t="n">
-        <v>6821427</v>
+        <v>6821241</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13997,32 +13997,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130068620</v>
+        <v>130068659</v>
       </c>
       <c r="B133" t="n">
-        <v>79204</v>
+        <v>78937</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>490403</v>
+        <v>490573</v>
       </c>
       <c r="R133" t="n">
-        <v>6821241</v>
+        <v>6821128</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14077,7 +14077,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14104,10 +14104,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130068659</v>
+        <v>130068637</v>
       </c>
       <c r="B134" t="n">
-        <v>78937</v>
+        <v>78938</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14115,21 +14115,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14139,10 +14139,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>490573</v>
+        <v>490393</v>
       </c>
       <c r="R134" t="n">
-        <v>6821128</v>
+        <v>6821367</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14211,50 +14211,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130068594</v>
+        <v>130068926</v>
       </c>
       <c r="B135" t="n">
-        <v>57016</v>
+        <v>78846</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>490601</v>
+        <v>491190</v>
       </c>
       <c r="R135" t="n">
-        <v>6821175</v>
+        <v>6820607</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14286,7 +14281,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14296,7 +14291,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14323,10 +14318,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130068926</v>
+        <v>130068587</v>
       </c>
       <c r="B136" t="n">
-        <v>78846</v>
+        <v>79212</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14334,21 +14329,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14358,10 +14353,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>491190</v>
+        <v>491161</v>
       </c>
       <c r="R136" t="n">
-        <v>6820607</v>
+        <v>6820628</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14393,7 +14388,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14403,7 +14398,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14430,10 +14425,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130068587</v>
+        <v>130068605</v>
       </c>
       <c r="B137" t="n">
-        <v>79212</v>
+        <v>91679</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14441,21 +14436,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14465,10 +14460,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>491161</v>
+        <v>490521</v>
       </c>
       <c r="R137" t="n">
-        <v>6820628</v>
+        <v>6821298</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14500,7 +14495,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14510,7 +14505,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14537,10 +14532,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130068605</v>
+        <v>130068885</v>
       </c>
       <c r="B138" t="n">
-        <v>91679</v>
+        <v>79180</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14548,21 +14543,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14572,10 +14567,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>490521</v>
+        <v>490562</v>
       </c>
       <c r="R138" t="n">
-        <v>6821298</v>
+        <v>6821132</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14607,7 +14602,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14617,7 +14612,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14644,10 +14639,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130068657</v>
+        <v>130068867</v>
       </c>
       <c r="B139" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14655,21 +14650,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14679,10 +14674,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>490961</v>
+        <v>490726</v>
       </c>
       <c r="R139" t="n">
-        <v>6820600</v>
+        <v>6820965</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14714,7 +14709,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14724,7 +14719,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14751,10 +14746,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130068660</v>
+        <v>130068836</v>
       </c>
       <c r="B140" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14762,21 +14757,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14786,10 +14781,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>490550</v>
+        <v>490945</v>
       </c>
       <c r="R140" t="n">
-        <v>6821160</v>
+        <v>6820623</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14821,7 +14816,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -14831,7 +14826,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14858,7 +14853,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130068718</v>
+        <v>130068902</v>
       </c>
       <c r="B141" t="n">
         <v>79180</v>
@@ -14893,10 +14888,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>490492</v>
+        <v>490481</v>
       </c>
       <c r="R141" t="n">
-        <v>6821351</v>
+        <v>6821182</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14928,7 +14923,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -14938,7 +14933,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14965,7 +14960,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130068885</v>
+        <v>130068797</v>
       </c>
       <c r="B142" t="n">
         <v>79180</v>
@@ -15000,10 +14995,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>490562</v>
+        <v>491182</v>
       </c>
       <c r="R142" t="n">
-        <v>6821132</v>
+        <v>6820616</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15035,7 +15030,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15045,7 +15040,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15072,7 +15067,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130068867</v>
+        <v>130068833</v>
       </c>
       <c r="B143" t="n">
         <v>79180</v>
@@ -15107,10 +15102,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>490726</v>
+        <v>490971</v>
       </c>
       <c r="R143" t="n">
-        <v>6820965</v>
+        <v>6820633</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15142,7 +15137,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15152,7 +15147,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15179,7 +15174,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130068836</v>
+        <v>130068781</v>
       </c>
       <c r="B144" t="n">
         <v>79180</v>
@@ -15214,10 +15209,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>490945</v>
+        <v>491160</v>
       </c>
       <c r="R144" t="n">
-        <v>6820623</v>
+        <v>6820813</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15249,7 +15244,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15259,7 +15254,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15286,7 +15281,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130068902</v>
+        <v>130068776</v>
       </c>
       <c r="B145" t="n">
         <v>79180</v>
@@ -15321,10 +15316,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>490481</v>
+        <v>491154</v>
       </c>
       <c r="R145" t="n">
-        <v>6821182</v>
+        <v>6820794</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15356,7 +15351,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15366,7 +15361,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15393,32 +15388,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130068797</v>
+        <v>130068623</v>
       </c>
       <c r="B146" t="n">
-        <v>79180</v>
+        <v>80313</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15428,10 +15423,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>491182</v>
+        <v>490594</v>
       </c>
       <c r="R146" t="n">
-        <v>6820616</v>
+        <v>6821177</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15463,7 +15458,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15473,7 +15468,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15500,10 +15495,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130068833</v>
+        <v>130068660</v>
       </c>
       <c r="B147" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15511,21 +15506,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15535,10 +15530,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>490971</v>
+        <v>490550</v>
       </c>
       <c r="R147" t="n">
-        <v>6820633</v>
+        <v>6821160</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15570,7 +15565,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15580,7 +15575,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15607,7 +15602,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130068781</v>
+        <v>130068718</v>
       </c>
       <c r="B148" t="n">
         <v>79180</v>
@@ -15642,10 +15637,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>491160</v>
+        <v>490492</v>
       </c>
       <c r="R148" t="n">
-        <v>6820813</v>
+        <v>6821351</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15677,7 +15672,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15687,7 +15682,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15714,7 +15709,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130068776</v>
+        <v>130068840</v>
       </c>
       <c r="B149" t="n">
         <v>79180</v>
@@ -15749,10 +15744,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>491154</v>
+        <v>490857</v>
       </c>
       <c r="R149" t="n">
-        <v>6820794</v>
+        <v>6820652</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15784,7 +15779,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15794,7 +15789,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15821,7 +15816,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130068840</v>
+        <v>130068873</v>
       </c>
       <c r="B150" t="n">
         <v>79180</v>
@@ -15856,10 +15851,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>490857</v>
+        <v>490656</v>
       </c>
       <c r="R150" t="n">
-        <v>6820652</v>
+        <v>6820985</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15891,7 +15886,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -15901,7 +15896,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15928,10 +15923,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130068873</v>
+        <v>130068563</v>
       </c>
       <c r="B151" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15939,21 +15934,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15963,10 +15958,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>490656</v>
+        <v>490629</v>
       </c>
       <c r="R151" t="n">
-        <v>6820985</v>
+        <v>6821073</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15998,7 +15993,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16008,7 +16003,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16035,32 +16030,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130068623</v>
+        <v>130068657</v>
       </c>
       <c r="B152" t="n">
-        <v>80313</v>
+        <v>78937</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16070,10 +16065,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>490594</v>
+        <v>490961</v>
       </c>
       <c r="R152" t="n">
-        <v>6821177</v>
+        <v>6820600</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16105,7 +16100,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16115,7 +16110,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16142,45 +16137,50 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130068563</v>
+        <v>130068594</v>
       </c>
       <c r="B153" t="n">
-        <v>79799</v>
+        <v>57016</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>490629</v>
+        <v>490601</v>
       </c>
       <c r="R153" t="n">
-        <v>6821073</v>
+        <v>6821175</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16222,7 +16222,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -23584,10 +23584,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>130068646</v>
+        <v>130068583</v>
       </c>
       <c r="B222" t="n">
-        <v>81165</v>
+        <v>79212</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23595,21 +23595,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23619,10 +23619,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>490550</v>
+        <v>491003</v>
       </c>
       <c r="R222" t="n">
-        <v>6821161</v>
+        <v>6820778</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -23664,7 +23664,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23691,10 +23691,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>130068913</v>
+        <v>130068646</v>
       </c>
       <c r="B223" t="n">
-        <v>79180</v>
+        <v>81165</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23702,21 +23702,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23726,10 +23726,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>490410</v>
+        <v>490550</v>
       </c>
       <c r="R223" t="n">
-        <v>6821329</v>
+        <v>6821161</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23761,7 +23761,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23798,7 +23798,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>130068743</v>
+        <v>130068766</v>
       </c>
       <c r="B224" t="n">
         <v>79180</v>
@@ -23833,10 +23833,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>490593</v>
+        <v>490705</v>
       </c>
       <c r="R224" t="n">
-        <v>6821181</v>
+        <v>6821005</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23868,7 +23868,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -23878,7 +23878,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23905,7 +23905,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>130068747</v>
+        <v>130068727</v>
       </c>
       <c r="B225" t="n">
         <v>79180</v>
@@ -23940,10 +23940,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>490598</v>
+        <v>490537</v>
       </c>
       <c r="R225" t="n">
-        <v>6821145</v>
+        <v>6821254</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23975,7 +23975,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -23985,7 +23985,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24012,7 +24012,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>130068725</v>
+        <v>130068744</v>
       </c>
       <c r="B226" t="n">
         <v>79180</v>
@@ -24047,10 +24047,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>490522</v>
+        <v>490605</v>
       </c>
       <c r="R226" t="n">
-        <v>6821261</v>
+        <v>6821175</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24082,7 +24082,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24092,7 +24092,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24119,7 +24119,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>130068735</v>
+        <v>130068913</v>
       </c>
       <c r="B227" t="n">
         <v>79180</v>
@@ -24154,10 +24154,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>490544</v>
+        <v>490410</v>
       </c>
       <c r="R227" t="n">
-        <v>6821205</v>
+        <v>6821329</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24189,7 +24189,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -24199,7 +24199,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24226,7 +24226,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>130068816</v>
+        <v>130068743</v>
       </c>
       <c r="B228" t="n">
         <v>79180</v>
@@ -24261,10 +24261,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>491141</v>
+        <v>490593</v>
       </c>
       <c r="R228" t="n">
-        <v>6820499</v>
+        <v>6821181</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24296,7 +24296,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24333,7 +24333,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>130068809</v>
+        <v>130068747</v>
       </c>
       <c r="B229" t="n">
         <v>79180</v>
@@ -24368,10 +24368,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>491230</v>
+        <v>490598</v>
       </c>
       <c r="R229" t="n">
-        <v>6820560</v>
+        <v>6821145</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24403,7 +24403,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -24413,7 +24413,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24440,7 +24440,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>130068767</v>
+        <v>130068725</v>
       </c>
       <c r="B230" t="n">
         <v>79180</v>
@@ -24475,10 +24475,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>490711</v>
+        <v>490522</v>
       </c>
       <c r="R230" t="n">
-        <v>6820988</v>
+        <v>6821261</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24510,7 +24510,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -24520,7 +24520,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24547,7 +24547,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>130068820</v>
+        <v>130068735</v>
       </c>
       <c r="B231" t="n">
         <v>79180</v>
@@ -24582,10 +24582,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>491083</v>
+        <v>490544</v>
       </c>
       <c r="R231" t="n">
-        <v>6820517</v>
+        <v>6821205</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24617,7 +24617,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24654,7 +24654,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>130068813</v>
+        <v>130068816</v>
       </c>
       <c r="B232" t="n">
         <v>79180</v>
@@ -24689,10 +24689,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>491226</v>
+        <v>491141</v>
       </c>
       <c r="R232" t="n">
-        <v>6820480</v>
+        <v>6820499</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24724,7 +24724,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -24734,7 +24734,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24761,7 +24761,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>130068704</v>
+        <v>130068809</v>
       </c>
       <c r="B233" t="n">
         <v>79180</v>
@@ -24796,10 +24796,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>490432</v>
+        <v>491230</v>
       </c>
       <c r="R233" t="n">
-        <v>6821264</v>
+        <v>6820560</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24831,7 +24831,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -24841,7 +24841,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24868,7 +24868,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>130068745</v>
+        <v>130068767</v>
       </c>
       <c r="B234" t="n">
         <v>79180</v>
@@ -24903,10 +24903,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>490627</v>
+        <v>490711</v>
       </c>
       <c r="R234" t="n">
-        <v>6821161</v>
+        <v>6820988</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24938,7 +24938,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -24948,7 +24948,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -24975,7 +24975,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>130068905</v>
+        <v>130068820</v>
       </c>
       <c r="B235" t="n">
         <v>79180</v>
@@ -25010,10 +25010,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>490465</v>
+        <v>491083</v>
       </c>
       <c r="R235" t="n">
-        <v>6821218</v>
+        <v>6820517</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25045,7 +25045,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -25055,7 +25055,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -25082,7 +25082,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>130068906</v>
+        <v>130068813</v>
       </c>
       <c r="B236" t="n">
         <v>79180</v>
@@ -25117,10 +25117,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>490456</v>
+        <v>491226</v>
       </c>
       <c r="R236" t="n">
-        <v>6821215</v>
+        <v>6820480</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -25162,7 +25162,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25189,7 +25189,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>130068766</v>
+        <v>130068704</v>
       </c>
       <c r="B237" t="n">
         <v>79180</v>
@@ -25224,10 +25224,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>490705</v>
+        <v>490432</v>
       </c>
       <c r="R237" t="n">
-        <v>6821005</v>
+        <v>6821264</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25259,7 +25259,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25296,7 +25296,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>130068727</v>
+        <v>130068745</v>
       </c>
       <c r="B238" t="n">
         <v>79180</v>
@@ -25331,10 +25331,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>490537</v>
+        <v>490627</v>
       </c>
       <c r="R238" t="n">
-        <v>6821254</v>
+        <v>6821161</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25366,7 +25366,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -25403,7 +25403,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>130068744</v>
+        <v>130068905</v>
       </c>
       <c r="B239" t="n">
         <v>79180</v>
@@ -25438,10 +25438,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>490605</v>
+        <v>490465</v>
       </c>
       <c r="R239" t="n">
-        <v>6821175</v>
+        <v>6821218</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25473,7 +25473,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -25510,10 +25510,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>130068583</v>
+        <v>130068906</v>
       </c>
       <c r="B240" t="n">
-        <v>79212</v>
+        <v>79180</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -25521,21 +25521,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -25545,10 +25545,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>491003</v>
+        <v>490456</v>
       </c>
       <c r="R240" t="n">
-        <v>6820778</v>
+        <v>6821215</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25580,7 +25580,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -25590,7 +25590,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -25617,7 +25617,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>130068751</v>
+        <v>130068872</v>
       </c>
       <c r="B241" t="n">
         <v>79180</v>
@@ -25652,10 +25652,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>490626</v>
+        <v>490677</v>
       </c>
       <c r="R241" t="n">
-        <v>6821133</v>
+        <v>6820976</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25687,7 +25687,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -25697,7 +25697,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -25724,10 +25724,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>130068807</v>
+        <v>130068663</v>
       </c>
       <c r="B242" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25735,21 +25735,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25759,10 +25759,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>491248</v>
+        <v>490449</v>
       </c>
       <c r="R242" t="n">
-        <v>6820566</v>
+        <v>6821237</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -25804,7 +25804,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25831,10 +25831,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>130068794</v>
+        <v>130068927</v>
       </c>
       <c r="B243" t="n">
-        <v>79180</v>
+        <v>78846</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25842,21 +25842,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25866,10 +25866,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>491171</v>
+        <v>490948</v>
       </c>
       <c r="R243" t="n">
-        <v>6820628</v>
+        <v>6820619</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25901,7 +25901,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -25911,7 +25911,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25938,10 +25938,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>130068788</v>
+        <v>130068931</v>
       </c>
       <c r="B244" t="n">
-        <v>79180</v>
+        <v>78846</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25949,21 +25949,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25973,10 +25973,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>491152</v>
+        <v>490510</v>
       </c>
       <c r="R244" t="n">
-        <v>6820778</v>
+        <v>6821122</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -26008,7 +26008,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -26018,7 +26018,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -26045,7 +26045,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>130068709</v>
+        <v>130068834</v>
       </c>
       <c r="B245" t="n">
         <v>79180</v>
@@ -26080,10 +26080,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>490438</v>
+        <v>490981</v>
       </c>
       <c r="R245" t="n">
-        <v>6821306</v>
+        <v>6820625</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -26115,7 +26115,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -26125,7 +26125,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -26152,7 +26152,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>130068862</v>
+        <v>130068824</v>
       </c>
       <c r="B246" t="n">
         <v>79180</v>
@@ -26187,10 +26187,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>490788</v>
+        <v>491021</v>
       </c>
       <c r="R246" t="n">
-        <v>6820868</v>
+        <v>6820562</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -26232,7 +26232,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26259,7 +26259,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>130068773</v>
+        <v>130068751</v>
       </c>
       <c r="B247" t="n">
         <v>79180</v>
@@ -26294,10 +26294,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>491101</v>
+        <v>490626</v>
       </c>
       <c r="R247" t="n">
-        <v>6820784</v>
+        <v>6821133</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26329,7 +26329,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -26339,7 +26339,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -26366,7 +26366,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>130068872</v>
+        <v>130068807</v>
       </c>
       <c r="B248" t="n">
         <v>79180</v>
@@ -26401,10 +26401,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>490677</v>
+        <v>491248</v>
       </c>
       <c r="R248" t="n">
-        <v>6820976</v>
+        <v>6820566</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26436,7 +26436,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26473,10 +26473,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>130068663</v>
+        <v>130068794</v>
       </c>
       <c r="B249" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26484,21 +26484,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -26508,10 +26508,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>490449</v>
+        <v>491171</v>
       </c>
       <c r="R249" t="n">
-        <v>6821237</v>
+        <v>6820628</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26543,7 +26543,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -26553,7 +26553,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26580,10 +26580,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>130068931</v>
+        <v>130068788</v>
       </c>
       <c r="B250" t="n">
-        <v>78846</v>
+        <v>79180</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26591,21 +26591,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -26615,10 +26615,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>490510</v>
+        <v>491152</v>
       </c>
       <c r="R250" t="n">
-        <v>6821122</v>
+        <v>6820778</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -26660,7 +26660,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26687,7 +26687,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>130068834</v>
+        <v>130068709</v>
       </c>
       <c r="B251" t="n">
         <v>79180</v>
@@ -26722,10 +26722,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>490981</v>
+        <v>490438</v>
       </c>
       <c r="R251" t="n">
-        <v>6820625</v>
+        <v>6821306</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -26767,7 +26767,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26794,7 +26794,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>130068824</v>
+        <v>130068862</v>
       </c>
       <c r="B252" t="n">
         <v>79180</v>
@@ -26829,10 +26829,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>491021</v>
+        <v>490788</v>
       </c>
       <c r="R252" t="n">
-        <v>6820562</v>
+        <v>6820868</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26864,7 +26864,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -26874,7 +26874,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -26901,10 +26901,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>130068927</v>
+        <v>130068773</v>
       </c>
       <c r="B253" t="n">
-        <v>78846</v>
+        <v>79180</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26912,21 +26912,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -26936,10 +26936,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>490948</v>
+        <v>491101</v>
       </c>
       <c r="R253" t="n">
-        <v>6820619</v>
+        <v>6820784</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26971,7 +26971,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -27008,10 +27008,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>130068677</v>
+        <v>130068674</v>
       </c>
       <c r="B254" t="n">
-        <v>91901</v>
+        <v>98920</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -27019,34 +27019,43 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P254" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>490384</v>
+        <v>490606</v>
       </c>
       <c r="R254" t="n">
-        <v>6821360</v>
+        <v>6821108</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -27078,7 +27087,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -27088,7 +27097,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27115,32 +27124,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>130068590</v>
+        <v>130068645</v>
       </c>
       <c r="B255" t="n">
-        <v>91692</v>
+        <v>81165</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -27150,10 +27159,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>490670</v>
+        <v>490554</v>
       </c>
       <c r="R255" t="n">
-        <v>6821056</v>
+        <v>6821209</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -27185,7 +27194,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -27195,7 +27204,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -27222,7 +27231,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>130068909</v>
+        <v>130068708</v>
       </c>
       <c r="B256" t="n">
         <v>79180</v>
@@ -27257,10 +27266,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>490479</v>
+        <v>490439</v>
       </c>
       <c r="R256" t="n">
-        <v>6821264</v>
+        <v>6821301</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -27292,7 +27301,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -27302,7 +27311,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27329,7 +27338,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>130068746</v>
+        <v>130068705</v>
       </c>
       <c r="B257" t="n">
         <v>79180</v>
@@ -27364,10 +27373,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>490617</v>
+        <v>490431</v>
       </c>
       <c r="R257" t="n">
-        <v>6821148</v>
+        <v>6821274</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27399,7 +27408,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -27409,7 +27418,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27436,32 +27445,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>130068723</v>
+        <v>130068677</v>
       </c>
       <c r="B258" t="n">
-        <v>79180</v>
+        <v>91901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -27471,10 +27480,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>490527</v>
+        <v>490384</v>
       </c>
       <c r="R258" t="n">
-        <v>6821279</v>
+        <v>6821360</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27506,7 +27515,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -27516,7 +27525,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -27543,32 +27552,32 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>130068708</v>
+        <v>130068590</v>
       </c>
       <c r="B259" t="n">
-        <v>79180</v>
+        <v>91692</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -27578,10 +27587,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>490439</v>
+        <v>490670</v>
       </c>
       <c r="R259" t="n">
-        <v>6821301</v>
+        <v>6821056</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27613,7 +27622,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -27623,7 +27632,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -27650,10 +27659,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>130068571</v>
+        <v>130068909</v>
       </c>
       <c r="B260" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -27661,21 +27670,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -27685,10 +27694,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>491234</v>
+        <v>490479</v>
       </c>
       <c r="R260" t="n">
-        <v>6820562</v>
+        <v>6821264</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27720,7 +27729,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -27730,7 +27739,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -27757,10 +27766,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>130068566</v>
+        <v>130068746</v>
       </c>
       <c r="B261" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -27768,21 +27777,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -27792,10 +27801,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>490653</v>
+        <v>490617</v>
       </c>
       <c r="R261" t="n">
-        <v>6821056</v>
+        <v>6821148</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27827,7 +27836,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -27837,7 +27846,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -27864,10 +27873,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>130068577</v>
+        <v>130068723</v>
       </c>
       <c r="B262" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -27875,21 +27884,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -27899,10 +27908,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>490510</v>
+        <v>490527</v>
       </c>
       <c r="R262" t="n">
-        <v>6821122</v>
+        <v>6821279</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27934,7 +27943,7 @@
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -27944,7 +27953,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -27971,10 +27980,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>130068645</v>
+        <v>130068571</v>
       </c>
       <c r="B263" t="n">
-        <v>81165</v>
+        <v>79799</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -27982,21 +27991,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -28006,10 +28015,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>490554</v>
+        <v>491234</v>
       </c>
       <c r="R263" t="n">
-        <v>6821209</v>
+        <v>6820562</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -28041,7 +28050,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -28051,7 +28060,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -28078,10 +28087,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>130068705</v>
+        <v>130068566</v>
       </c>
       <c r="B264" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -28089,21 +28098,21 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -28113,10 +28122,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>490431</v>
+        <v>490653</v>
       </c>
       <c r="R264" t="n">
-        <v>6821274</v>
+        <v>6821056</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -28148,7 +28157,7 @@
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -28158,7 +28167,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -28185,10 +28194,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>130068647</v>
+        <v>130068577</v>
       </c>
       <c r="B265" t="n">
-        <v>78937</v>
+        <v>79799</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -28196,21 +28205,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -28220,10 +28229,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>490333</v>
+        <v>490510</v>
       </c>
       <c r="R265" t="n">
-        <v>6821419</v>
+        <v>6821122</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -28255,7 +28264,7 @@
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
@@ -28265,7 +28274,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -28292,7 +28301,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>130068649</v>
+        <v>130068647</v>
       </c>
       <c r="B266" t="n">
         <v>78937</v>
@@ -28327,10 +28336,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>490404</v>
+        <v>490333</v>
       </c>
       <c r="R266" t="n">
-        <v>6821355</v>
+        <v>6821419</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28362,7 +28371,7 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -28372,7 +28381,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28399,10 +28408,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>130068676</v>
+        <v>130068649</v>
       </c>
       <c r="B267" t="n">
-        <v>5176</v>
+        <v>78937</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -28410,39 +28419,34 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>102204</v>
+        <v>6446</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P267" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>490599</v>
+        <v>490404</v>
       </c>
       <c r="R267" t="n">
-        <v>6821131</v>
+        <v>6821355</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28474,7 +28478,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -28484,7 +28488,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28511,42 +28515,38 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>130068674</v>
+        <v>130068676</v>
       </c>
       <c r="B268" t="n">
-        <v>98920</v>
+        <v>5176</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>220787</v>
+        <v>102204</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr"/>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
@@ -28555,10 +28555,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>490606</v>
+        <v>490599</v>
       </c>
       <c r="R268" t="n">
-        <v>6821108</v>
+        <v>6821131</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28590,7 +28590,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -28600,7 +28600,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -32488,32 +32488,32 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>130068921</v>
+        <v>130068634</v>
       </c>
       <c r="B305" t="n">
-        <v>93010</v>
+        <v>78938</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -32523,10 +32523,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>490679</v>
+        <v>490332</v>
       </c>
       <c r="R305" t="n">
-        <v>6820958</v>
+        <v>6821426</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -32558,7 +32558,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -32568,7 +32568,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -32595,10 +32595,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>130068702</v>
+        <v>130068639</v>
       </c>
       <c r="B306" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -32606,21 +32606,21 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
@@ -32630,10 +32630,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>490438</v>
+        <v>490401</v>
       </c>
       <c r="R306" t="n">
-        <v>6821252</v>
+        <v>6821264</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -32675,7 +32675,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -32702,32 +32702,32 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>130068603</v>
+        <v>130068686</v>
       </c>
       <c r="B307" t="n">
-        <v>80314</v>
+        <v>79180</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -32737,10 +32737,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>491182</v>
+        <v>490393</v>
       </c>
       <c r="R307" t="n">
-        <v>6820747</v>
+        <v>6821358</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -32772,7 +32772,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -32782,7 +32782,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -32809,32 +32809,32 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>130068622</v>
+        <v>130068901</v>
       </c>
       <c r="B308" t="n">
-        <v>80313</v>
+        <v>79180</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -32844,10 +32844,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>490534</v>
+        <v>490479</v>
       </c>
       <c r="R308" t="n">
-        <v>6821209</v>
+        <v>6821177</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -32879,7 +32879,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -32889,7 +32889,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -32916,10 +32916,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>130068634</v>
+        <v>130068875</v>
       </c>
       <c r="B309" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -32927,21 +32927,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -32951,10 +32951,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>490332</v>
+        <v>490675</v>
       </c>
       <c r="R309" t="n">
-        <v>6821426</v>
+        <v>6821007</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -32986,7 +32986,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -32996,7 +32996,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -33023,10 +33023,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>130068639</v>
+        <v>130068891</v>
       </c>
       <c r="B310" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -33034,21 +33034,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -33058,10 +33058,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>490401</v>
+        <v>490526</v>
       </c>
       <c r="R310" t="n">
-        <v>6821264</v>
+        <v>6821120</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -33093,7 +33093,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -33103,7 +33103,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -33130,7 +33130,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>130068686</v>
+        <v>130068749</v>
       </c>
       <c r="B311" t="n">
         <v>79180</v>
@@ -33165,10 +33165,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>490393</v>
+        <v>490607</v>
       </c>
       <c r="R311" t="n">
-        <v>6821358</v>
+        <v>6821129</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -33200,7 +33200,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -33210,7 +33210,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -33237,7 +33237,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>130068901</v>
+        <v>130068714</v>
       </c>
       <c r="B312" t="n">
         <v>79180</v>
@@ -33272,10 +33272,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>490479</v>
+        <v>490444</v>
       </c>
       <c r="R312" t="n">
-        <v>6821177</v>
+        <v>6821345</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -33307,7 +33307,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -33317,7 +33317,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -33344,7 +33344,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>130068875</v>
+        <v>130068702</v>
       </c>
       <c r="B313" t="n">
         <v>79180</v>
@@ -33379,10 +33379,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>490675</v>
+        <v>490438</v>
       </c>
       <c r="R313" t="n">
-        <v>6821007</v>
+        <v>6821252</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -33414,7 +33414,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -33424,7 +33424,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -33451,32 +33451,32 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>130068891</v>
+        <v>130068603</v>
       </c>
       <c r="B314" t="n">
-        <v>79180</v>
+        <v>80314</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
@@ -33486,10 +33486,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>490526</v>
+        <v>491182</v>
       </c>
       <c r="R314" t="n">
-        <v>6821120</v>
+        <v>6820747</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -33521,7 +33521,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -33531,7 +33531,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD314" t="b">
@@ -33558,32 +33558,32 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>130068749</v>
+        <v>130068622</v>
       </c>
       <c r="B315" t="n">
-        <v>79180</v>
+        <v>80313</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -33593,10 +33593,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>490607</v>
+        <v>490534</v>
       </c>
       <c r="R315" t="n">
-        <v>6821129</v>
+        <v>6821209</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>
@@ -33628,7 +33628,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -33638,7 +33638,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD315" t="b">
@@ -33665,32 +33665,32 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>130068714</v>
+        <v>130068921</v>
       </c>
       <c r="B316" t="n">
-        <v>79180</v>
+        <v>93010</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
@@ -33700,10 +33700,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>490444</v>
+        <v>490679</v>
       </c>
       <c r="R316" t="n">
-        <v>6821345</v>
+        <v>6820958</v>
       </c>
       <c r="S316" t="n">
         <v>10</v>
@@ -33735,7 +33735,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -33745,7 +33745,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD316" t="b">
@@ -33772,32 +33772,32 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>130068717</v>
+        <v>130068591</v>
       </c>
       <c r="B317" t="n">
-        <v>79180</v>
+        <v>91692</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
@@ -33807,10 +33807,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>490489</v>
+        <v>490750</v>
       </c>
       <c r="R317" t="n">
-        <v>6821341</v>
+        <v>6820956</v>
       </c>
       <c r="S317" t="n">
         <v>10</v>
@@ -33842,7 +33842,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -33852,7 +33852,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD317" t="b">
@@ -33879,7 +33879,7 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>130068911</v>
+        <v>130068717</v>
       </c>
       <c r="B318" t="n">
         <v>79180</v>
@@ -33914,10 +33914,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>490465</v>
+        <v>490489</v>
       </c>
       <c r="R318" t="n">
-        <v>6821283</v>
+        <v>6821341</v>
       </c>
       <c r="S318" t="n">
         <v>10</v>
@@ -33949,7 +33949,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -33959,7 +33959,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD318" t="b">
@@ -33986,7 +33986,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>130068822</v>
+        <v>130068911</v>
       </c>
       <c r="B319" t="n">
         <v>79180</v>
@@ -34021,10 +34021,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>491047</v>
+        <v>490465</v>
       </c>
       <c r="R319" t="n">
-        <v>6820558</v>
+        <v>6821283</v>
       </c>
       <c r="S319" t="n">
         <v>10</v>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -34066,7 +34066,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD319" t="b">
@@ -34093,7 +34093,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>130068892</v>
+        <v>130068822</v>
       </c>
       <c r="B320" t="n">
         <v>79180</v>
@@ -34128,10 +34128,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>490511</v>
+        <v>491047</v>
       </c>
       <c r="R320" t="n">
-        <v>6821122</v>
+        <v>6820558</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -34163,7 +34163,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD320" t="b">
@@ -34200,7 +34200,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>130068808</v>
+        <v>130068892</v>
       </c>
       <c r="B321" t="n">
         <v>79180</v>
@@ -34235,10 +34235,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>491244</v>
+        <v>490511</v>
       </c>
       <c r="R321" t="n">
-        <v>6820561</v>
+        <v>6821122</v>
       </c>
       <c r="S321" t="n">
         <v>10</v>
@@ -34270,7 +34270,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -34280,7 +34280,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -34307,7 +34307,7 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>130068739</v>
+        <v>130068808</v>
       </c>
       <c r="B322" t="n">
         <v>79180</v>
@@ -34342,10 +34342,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>490569</v>
+        <v>491244</v>
       </c>
       <c r="R322" t="n">
-        <v>6821203</v>
+        <v>6820561</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -34377,7 +34377,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -34387,7 +34387,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -34414,7 +34414,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>130068879</v>
+        <v>130068739</v>
       </c>
       <c r="B323" t="n">
         <v>79180</v>
@@ -34449,10 +34449,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>490669</v>
+        <v>490569</v>
       </c>
       <c r="R323" t="n">
-        <v>6821033</v>
+        <v>6821203</v>
       </c>
       <c r="S323" t="n">
         <v>10</v>
@@ -34484,7 +34484,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -34494,7 +34494,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -34521,10 +34521,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>130068650</v>
+        <v>130068879</v>
       </c>
       <c r="B324" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -34532,21 +34532,21 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
@@ -34556,10 +34556,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>490380</v>
+        <v>490669</v>
       </c>
       <c r="R324" t="n">
-        <v>6821325</v>
+        <v>6821033</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -34591,7 +34591,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -34628,10 +34628,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>130068842</v>
+        <v>130068650</v>
       </c>
       <c r="B325" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -34639,21 +34639,21 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
@@ -34663,10 +34663,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>490953</v>
+        <v>490380</v>
       </c>
       <c r="R325" t="n">
-        <v>6820764</v>
+        <v>6821325</v>
       </c>
       <c r="S325" t="n">
         <v>10</v>
@@ -34698,7 +34698,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -34708,7 +34708,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD325" t="b">
@@ -34735,32 +34735,32 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>130068591</v>
+        <v>130068842</v>
       </c>
       <c r="B326" t="n">
-        <v>91692</v>
+        <v>79180</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
@@ -34770,10 +34770,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>490750</v>
+        <v>490953</v>
       </c>
       <c r="R326" t="n">
-        <v>6820956</v>
+        <v>6820764</v>
       </c>
       <c r="S326" t="n">
         <v>10</v>
@@ -34805,7 +34805,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -34815,7 +34815,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD326" t="b">
@@ -35056,10 +35056,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>130068888</v>
+        <v>130068635</v>
       </c>
       <c r="B329" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -35067,21 +35067,21 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
@@ -35091,10 +35091,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>490539</v>
+        <v>490388</v>
       </c>
       <c r="R329" t="n">
-        <v>6821155</v>
+        <v>6821389</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -35126,7 +35126,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD329" t="b">
@@ -35163,32 +35163,32 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>130068791</v>
+        <v>130068621</v>
       </c>
       <c r="B330" t="n">
-        <v>79180</v>
+        <v>80313</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
@@ -35198,10 +35198,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>491166</v>
+        <v>490525</v>
       </c>
       <c r="R330" t="n">
-        <v>6820674</v>
+        <v>6821278</v>
       </c>
       <c r="S330" t="n">
         <v>10</v>
@@ -35233,7 +35233,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -35243,7 +35243,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD330" t="b">
@@ -35252,6 +35252,7 @@
       <c r="AE330" t="b">
         <v>0</v>
       </c>
+      <c r="AF330" t="inlineStr"/>
       <c r="AG330" t="b">
         <v>0</v>
       </c>
@@ -35270,7 +35271,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>130068884</v>
+        <v>130068825</v>
       </c>
       <c r="B331" t="n">
         <v>79180</v>
@@ -35305,10 +35306,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>490575</v>
+        <v>491008</v>
       </c>
       <c r="R331" t="n">
-        <v>6821126</v>
+        <v>6820554</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -35340,7 +35341,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -35350,7 +35351,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -35377,7 +35378,7 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>130068731</v>
+        <v>130068908</v>
       </c>
       <c r="B332" t="n">
         <v>79180</v>
@@ -35412,10 +35413,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>490550</v>
+        <v>490464</v>
       </c>
       <c r="R332" t="n">
-        <v>6821227</v>
+        <v>6821244</v>
       </c>
       <c r="S332" t="n">
         <v>10</v>
@@ -35447,7 +35448,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -35457,7 +35458,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD332" t="b">
@@ -35484,7 +35485,7 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>130068869</v>
+        <v>130068839</v>
       </c>
       <c r="B333" t="n">
         <v>79180</v>
@@ -35519,10 +35520,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>490702</v>
+        <v>490865</v>
       </c>
       <c r="R333" t="n">
-        <v>6820970</v>
+        <v>6820655</v>
       </c>
       <c r="S333" t="n">
         <v>10</v>
@@ -35554,7 +35555,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -35564,7 +35565,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -35591,7 +35592,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>130068908</v>
+        <v>130068888</v>
       </c>
       <c r="B334" t="n">
         <v>79180</v>
@@ -35626,10 +35627,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>490464</v>
+        <v>490539</v>
       </c>
       <c r="R334" t="n">
-        <v>6821244</v>
+        <v>6821155</v>
       </c>
       <c r="S334" t="n">
         <v>10</v>
@@ -35661,7 +35662,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -35671,7 +35672,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -35698,7 +35699,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>130068839</v>
+        <v>130068791</v>
       </c>
       <c r="B335" t="n">
         <v>79180</v>
@@ -35733,10 +35734,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>490865</v>
+        <v>491166</v>
       </c>
       <c r="R335" t="n">
-        <v>6820655</v>
+        <v>6820674</v>
       </c>
       <c r="S335" t="n">
         <v>10</v>
@@ -35768,7 +35769,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -35778,7 +35779,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -35805,7 +35806,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>130068738</v>
+        <v>130068884</v>
       </c>
       <c r="B336" t="n">
         <v>79180</v>
@@ -35840,10 +35841,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>490564</v>
+        <v>490575</v>
       </c>
       <c r="R336" t="n">
-        <v>6821207</v>
+        <v>6821126</v>
       </c>
       <c r="S336" t="n">
         <v>10</v>
@@ -35875,7 +35876,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -35885,7 +35886,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -35912,7 +35913,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>130068810</v>
+        <v>130068731</v>
       </c>
       <c r="B337" t="n">
         <v>79180</v>
@@ -35947,10 +35948,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>491233</v>
+        <v>490550</v>
       </c>
       <c r="R337" t="n">
-        <v>6820538</v>
+        <v>6821227</v>
       </c>
       <c r="S337" t="n">
         <v>10</v>
@@ -35982,7 +35983,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -35992,7 +35993,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -36019,32 +36020,32 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>130068621</v>
+        <v>130068869</v>
       </c>
       <c r="B338" t="n">
-        <v>80313</v>
+        <v>79180</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
@@ -36054,10 +36055,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>490525</v>
+        <v>490702</v>
       </c>
       <c r="R338" t="n">
-        <v>6821278</v>
+        <v>6820970</v>
       </c>
       <c r="S338" t="n">
         <v>10</v>
@@ -36089,7 +36090,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -36099,7 +36100,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -36108,7 +36109,6 @@
       <c r="AE338" t="b">
         <v>0</v>
       </c>
-      <c r="AF338" t="inlineStr"/>
       <c r="AG338" t="b">
         <v>0</v>
       </c>
@@ -36127,7 +36127,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>130068825</v>
+        <v>130068738</v>
       </c>
       <c r="B339" t="n">
         <v>79180</v>
@@ -36162,10 +36162,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>491008</v>
+        <v>490564</v>
       </c>
       <c r="R339" t="n">
-        <v>6820554</v>
+        <v>6821207</v>
       </c>
       <c r="S339" t="n">
         <v>10</v>
@@ -36197,7 +36197,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -36207,7 +36207,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -36234,10 +36234,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>130068635</v>
+        <v>130068810</v>
       </c>
       <c r="B340" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -36245,21 +36245,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
@@ -36269,10 +36269,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>490388</v>
+        <v>491233</v>
       </c>
       <c r="R340" t="n">
-        <v>6821389</v>
+        <v>6820538</v>
       </c>
       <c r="S340" t="n">
         <v>10</v>
@@ -36304,7 +36304,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -36314,7 +36314,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD340" t="b">
@@ -40229,10 +40229,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>130068568</v>
+        <v>130068703</v>
       </c>
       <c r="B377" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -40240,21 +40240,21 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I377" t="inlineStr"/>
@@ -40264,10 +40264,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>490698</v>
+        <v>490436</v>
       </c>
       <c r="R377" t="n">
-        <v>6821013</v>
+        <v>6821261</v>
       </c>
       <c r="S377" t="n">
         <v>10</v>
@@ -40299,7 +40299,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -40309,7 +40309,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD377" t="b">
@@ -40336,10 +40336,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>130068572</v>
+        <v>130068733</v>
       </c>
       <c r="B378" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -40347,21 +40347,21 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I378" t="inlineStr"/>
@@ -40371,10 +40371,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>490961</v>
+        <v>490539</v>
       </c>
       <c r="R378" t="n">
-        <v>6820600</v>
+        <v>6821218</v>
       </c>
       <c r="S378" t="n">
         <v>10</v>
@@ -40406,7 +40406,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -40416,7 +40416,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD378" t="b">
@@ -40443,50 +40443,45 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>130068595</v>
+        <v>130068690</v>
       </c>
       <c r="B379" t="n">
-        <v>57016</v>
+        <v>79180</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I379" t="inlineStr"/>
-      <c r="M379" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P379" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>490535</v>
+        <v>490406</v>
       </c>
       <c r="R379" t="n">
-        <v>6821122</v>
+        <v>6821345</v>
       </c>
       <c r="S379" t="n">
         <v>10</v>
@@ -40518,7 +40513,7 @@
       </c>
       <c r="Z379" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
@@ -40528,7 +40523,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD379" t="b">
@@ -40555,7 +40550,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>130068703</v>
+        <v>130068882</v>
       </c>
       <c r="B380" t="n">
         <v>79180</v>
@@ -40590,10 +40585,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>490436</v>
+        <v>490609</v>
       </c>
       <c r="R380" t="n">
-        <v>6821261</v>
+        <v>6821100</v>
       </c>
       <c r="S380" t="n">
         <v>10</v>
@@ -40625,7 +40620,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -40635,7 +40630,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD380" t="b">
@@ -40662,45 +40657,50 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>130068733</v>
+        <v>130068595</v>
       </c>
       <c r="B381" t="n">
-        <v>79180</v>
+        <v>57016</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I381" t="inlineStr"/>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P381" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>490539</v>
+        <v>490535</v>
       </c>
       <c r="R381" t="n">
-        <v>6821218</v>
+        <v>6821122</v>
       </c>
       <c r="S381" t="n">
         <v>10</v>
@@ -40732,7 +40732,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -40742,7 +40742,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD381" t="b">
@@ -40769,10 +40769,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>130068690</v>
+        <v>130068628</v>
       </c>
       <c r="B382" t="n">
-        <v>79180</v>
+        <v>93048</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -40780,21 +40780,21 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I382" t="inlineStr"/>
@@ -40804,10 +40804,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>490406</v>
+        <v>490896</v>
       </c>
       <c r="R382" t="n">
-        <v>6821345</v>
+        <v>6820806</v>
       </c>
       <c r="S382" t="n">
         <v>10</v>
@@ -40839,7 +40839,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -40849,7 +40849,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD382" t="b">
@@ -40876,7 +40876,7 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>130068882</v>
+        <v>130068761</v>
       </c>
       <c r="B383" t="n">
         <v>79180</v>
@@ -40911,10 +40911,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>490609</v>
+        <v>490698</v>
       </c>
       <c r="R383" t="n">
-        <v>6821100</v>
+        <v>6821021</v>
       </c>
       <c r="S383" t="n">
         <v>10</v>
@@ -40946,7 +40946,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -40956,7 +40956,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD383" t="b">
@@ -40983,10 +40983,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>130068628</v>
+        <v>130068762</v>
       </c>
       <c r="B384" t="n">
-        <v>93048</v>
+        <v>79180</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -40994,21 +40994,21 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I384" t="inlineStr"/>
@@ -41018,10 +41018,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>490896</v>
+        <v>490687</v>
       </c>
       <c r="R384" t="n">
-        <v>6820806</v>
+        <v>6821018</v>
       </c>
       <c r="S384" t="n">
         <v>10</v>
@@ -41053,7 +41053,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -41063,7 +41063,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD384" t="b">
@@ -41090,7 +41090,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>130068761</v>
+        <v>130068732</v>
       </c>
       <c r="B385" t="n">
         <v>79180</v>
@@ -41125,10 +41125,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>490698</v>
+        <v>490542</v>
       </c>
       <c r="R385" t="n">
-        <v>6821021</v>
+        <v>6821224</v>
       </c>
       <c r="S385" t="n">
         <v>10</v>
@@ -41160,7 +41160,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -41170,7 +41170,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD385" t="b">
@@ -41197,10 +41197,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>130068762</v>
+        <v>130068568</v>
       </c>
       <c r="B386" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -41208,21 +41208,21 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I386" t="inlineStr"/>
@@ -41232,10 +41232,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>490687</v>
+        <v>490698</v>
       </c>
       <c r="R386" t="n">
-        <v>6821018</v>
+        <v>6821013</v>
       </c>
       <c r="S386" t="n">
         <v>10</v>
@@ -41267,7 +41267,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -41277,7 +41277,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD386" t="b">
@@ -41304,10 +41304,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>130068732</v>
+        <v>130068572</v>
       </c>
       <c r="B387" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -41315,21 +41315,21 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I387" t="inlineStr"/>
@@ -41339,10 +41339,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>490542</v>
+        <v>490961</v>
       </c>
       <c r="R387" t="n">
-        <v>6821224</v>
+        <v>6820600</v>
       </c>
       <c r="S387" t="n">
         <v>10</v>
@@ -41374,7 +41374,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -41384,7 +41384,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD387" t="b">

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -17226,10 +17226,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>130068653</v>
+        <v>130068627</v>
       </c>
       <c r="B163" t="n">
-        <v>78937</v>
+        <v>93048</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17237,21 +17237,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17261,10 +17261,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>490522</v>
+        <v>491012</v>
       </c>
       <c r="R163" t="n">
-        <v>6821366</v>
+        <v>6820821</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17296,7 +17296,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17333,10 +17333,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130068914</v>
+        <v>130068653</v>
       </c>
       <c r="B164" t="n">
-        <v>57826</v>
+        <v>78937</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17344,39 +17344,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>490384</v>
+        <v>490522</v>
       </c>
       <c r="R164" t="n">
-        <v>6821397</v>
+        <v>6821366</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17408,7 +17403,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17418,14 +17413,14 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG164" t="b">
         <v>0</v>
@@ -17445,45 +17440,50 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130068617</v>
+        <v>130068914</v>
       </c>
       <c r="B165" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>490994</v>
+        <v>490384</v>
       </c>
       <c r="R165" t="n">
-        <v>6820825</v>
+        <v>6821397</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17515,7 +17515,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17525,14 +17525,14 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG165" t="b">
         <v>0</v>
@@ -17552,32 +17552,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>130068627</v>
+        <v>130068617</v>
       </c>
       <c r="B166" t="n">
-        <v>93048</v>
+        <v>97791</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5966</v>
+        <v>221945</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17587,10 +17587,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>491012</v>
+        <v>490994</v>
       </c>
       <c r="R166" t="n">
-        <v>6820821</v>
+        <v>6820825</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17632,7 +17632,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20129,10 +20129,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>130068712</v>
+        <v>130068930</v>
       </c>
       <c r="B190" t="n">
-        <v>79180</v>
+        <v>78846</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20140,21 +20140,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20164,10 +20164,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>490440</v>
+        <v>490563</v>
       </c>
       <c r="R190" t="n">
-        <v>6821320</v>
+        <v>6821133</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20209,7 +20209,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20236,10 +20236,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>130068785</v>
+        <v>130068570</v>
       </c>
       <c r="B191" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20247,21 +20247,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20271,10 +20271,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>491178</v>
+        <v>490731</v>
       </c>
       <c r="R191" t="n">
-        <v>6820798</v>
+        <v>6820976</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20343,10 +20343,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>130068898</v>
+        <v>130068561</v>
       </c>
       <c r="B192" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20354,21 +20354,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20378,10 +20378,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>490480</v>
+        <v>490380</v>
       </c>
       <c r="R192" t="n">
-        <v>6821113</v>
+        <v>6821325</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20413,7 +20413,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20450,10 +20450,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>130068741</v>
+        <v>130068642</v>
       </c>
       <c r="B193" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20461,21 +20461,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20485,10 +20485,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>490578</v>
+        <v>491110</v>
       </c>
       <c r="R193" t="n">
-        <v>6821202</v>
+        <v>6820801</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20520,7 +20520,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20530,7 +20530,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20557,7 +20557,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>130068771</v>
+        <v>130068837</v>
       </c>
       <c r="B194" t="n">
         <v>79180</v>
@@ -20592,10 +20592,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>490799</v>
+        <v>490932</v>
       </c>
       <c r="R194" t="n">
-        <v>6820989</v>
+        <v>6820625</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20627,7 +20627,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20637,7 +20637,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20664,10 +20664,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>130068806</v>
+        <v>130068658</v>
       </c>
       <c r="B195" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20675,21 +20675,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20699,10 +20699,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>491242</v>
+        <v>490643</v>
       </c>
       <c r="R195" t="n">
-        <v>6820579</v>
+        <v>6821043</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20771,10 +20771,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>130068570</v>
+        <v>130068748</v>
       </c>
       <c r="B196" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20782,21 +20782,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20806,10 +20806,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>490731</v>
+        <v>490584</v>
       </c>
       <c r="R196" t="n">
-        <v>6820976</v>
+        <v>6821145</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20851,7 +20851,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20878,10 +20878,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>130068561</v>
+        <v>130068719</v>
       </c>
       <c r="B197" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20889,21 +20889,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20913,10 +20913,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>490380</v>
+        <v>490534</v>
       </c>
       <c r="R197" t="n">
-        <v>6821325</v>
+        <v>6821348</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20958,7 +20958,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20985,10 +20985,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>130068642</v>
+        <v>130068712</v>
       </c>
       <c r="B198" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20996,21 +20996,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21020,10 +21020,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>491110</v>
+        <v>490440</v>
       </c>
       <c r="R198" t="n">
-        <v>6820801</v>
+        <v>6821320</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21065,7 +21065,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21092,7 +21092,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>130068837</v>
+        <v>130068785</v>
       </c>
       <c r="B199" t="n">
         <v>79180</v>
@@ -21127,10 +21127,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>490932</v>
+        <v>491178</v>
       </c>
       <c r="R199" t="n">
-        <v>6820625</v>
+        <v>6820798</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21172,7 +21172,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21199,10 +21199,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>130068658</v>
+        <v>130068898</v>
       </c>
       <c r="B200" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21210,21 +21210,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21234,10 +21234,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>490643</v>
+        <v>490480</v>
       </c>
       <c r="R200" t="n">
-        <v>6821043</v>
+        <v>6821113</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21269,7 +21269,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21279,7 +21279,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21306,10 +21306,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>130068607</v>
+        <v>130068741</v>
       </c>
       <c r="B201" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21317,39 +21317,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>490376</v>
+        <v>490578</v>
       </c>
       <c r="R201" t="n">
-        <v>6821479</v>
+        <v>6821202</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21381,7 +21376,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21391,7 +21386,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21418,10 +21413,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>130068596</v>
+        <v>130068771</v>
       </c>
       <c r="B202" t="n">
-        <v>57985</v>
+        <v>79180</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21429,50 +21424,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>490604</v>
+        <v>490799</v>
       </c>
       <c r="R202" t="n">
-        <v>6821185</v>
+        <v>6820989</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21504,7 +21483,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21514,7 +21493,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21541,10 +21520,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>130068930</v>
+        <v>130068806</v>
       </c>
       <c r="B203" t="n">
-        <v>78846</v>
+        <v>79180</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21552,21 +21531,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21576,10 +21555,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>490563</v>
+        <v>491242</v>
       </c>
       <c r="R203" t="n">
-        <v>6821133</v>
+        <v>6820579</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21611,7 +21590,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -21621,7 +21600,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21648,10 +21627,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>130068748</v>
+        <v>130068607</v>
       </c>
       <c r="B204" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21659,34 +21638,39 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>490584</v>
+        <v>490376</v>
       </c>
       <c r="R204" t="n">
-        <v>6821145</v>
+        <v>6821479</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21718,7 +21702,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -21728,7 +21712,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21755,10 +21739,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>130068719</v>
+        <v>130068596</v>
       </c>
       <c r="B205" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21766,34 +21750,50 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>490534</v>
+        <v>490604</v>
       </c>
       <c r="R205" t="n">
-        <v>6821348</v>
+        <v>6821185</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21825,7 +21825,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -21835,7 +21835,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23584,10 +23584,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>130068583</v>
+        <v>130068646</v>
       </c>
       <c r="B222" t="n">
-        <v>79212</v>
+        <v>81165</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23595,21 +23595,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23619,10 +23619,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>491003</v>
+        <v>490550</v>
       </c>
       <c r="R222" t="n">
-        <v>6820778</v>
+        <v>6821161</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -23664,7 +23664,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23691,10 +23691,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>130068646</v>
+        <v>130068913</v>
       </c>
       <c r="B223" t="n">
-        <v>81165</v>
+        <v>79180</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23702,21 +23702,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23726,10 +23726,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>490550</v>
+        <v>490410</v>
       </c>
       <c r="R223" t="n">
-        <v>6821161</v>
+        <v>6821329</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23761,7 +23761,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23798,7 +23798,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>130068766</v>
+        <v>130068743</v>
       </c>
       <c r="B224" t="n">
         <v>79180</v>
@@ -23833,10 +23833,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>490705</v>
+        <v>490593</v>
       </c>
       <c r="R224" t="n">
-        <v>6821005</v>
+        <v>6821181</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23868,7 +23868,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -23878,7 +23878,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23905,7 +23905,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>130068727</v>
+        <v>130068747</v>
       </c>
       <c r="B225" t="n">
         <v>79180</v>
@@ -23940,10 +23940,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>490537</v>
+        <v>490598</v>
       </c>
       <c r="R225" t="n">
-        <v>6821254</v>
+        <v>6821145</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23975,7 +23975,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -23985,7 +23985,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24012,7 +24012,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>130068744</v>
+        <v>130068725</v>
       </c>
       <c r="B226" t="n">
         <v>79180</v>
@@ -24047,10 +24047,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>490605</v>
+        <v>490522</v>
       </c>
       <c r="R226" t="n">
-        <v>6821175</v>
+        <v>6821261</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24082,7 +24082,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24092,7 +24092,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24119,7 +24119,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>130068913</v>
+        <v>130068735</v>
       </c>
       <c r="B227" t="n">
         <v>79180</v>
@@ -24154,10 +24154,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>490410</v>
+        <v>490544</v>
       </c>
       <c r="R227" t="n">
-        <v>6821329</v>
+        <v>6821205</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24189,7 +24189,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -24199,7 +24199,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24226,7 +24226,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>130068743</v>
+        <v>130068816</v>
       </c>
       <c r="B228" t="n">
         <v>79180</v>
@@ -24261,10 +24261,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>490593</v>
+        <v>491141</v>
       </c>
       <c r="R228" t="n">
-        <v>6821181</v>
+        <v>6820499</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24296,7 +24296,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24333,7 +24333,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>130068747</v>
+        <v>130068809</v>
       </c>
       <c r="B229" t="n">
         <v>79180</v>
@@ -24368,10 +24368,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>490598</v>
+        <v>491230</v>
       </c>
       <c r="R229" t="n">
-        <v>6821145</v>
+        <v>6820560</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24403,7 +24403,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -24413,7 +24413,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24440,7 +24440,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>130068725</v>
+        <v>130068767</v>
       </c>
       <c r="B230" t="n">
         <v>79180</v>
@@ -24475,10 +24475,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>490522</v>
+        <v>490711</v>
       </c>
       <c r="R230" t="n">
-        <v>6821261</v>
+        <v>6820988</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24510,7 +24510,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -24520,7 +24520,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24547,7 +24547,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>130068735</v>
+        <v>130068820</v>
       </c>
       <c r="B231" t="n">
         <v>79180</v>
@@ -24582,10 +24582,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>490544</v>
+        <v>491083</v>
       </c>
       <c r="R231" t="n">
-        <v>6821205</v>
+        <v>6820517</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24617,7 +24617,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24654,7 +24654,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>130068816</v>
+        <v>130068813</v>
       </c>
       <c r="B232" t="n">
         <v>79180</v>
@@ -24689,10 +24689,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>491141</v>
+        <v>491226</v>
       </c>
       <c r="R232" t="n">
-        <v>6820499</v>
+        <v>6820480</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24724,7 +24724,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -24734,7 +24734,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24761,7 +24761,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>130068809</v>
+        <v>130068704</v>
       </c>
       <c r="B233" t="n">
         <v>79180</v>
@@ -24796,10 +24796,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>491230</v>
+        <v>490432</v>
       </c>
       <c r="R233" t="n">
-        <v>6820560</v>
+        <v>6821264</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24831,7 +24831,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -24841,7 +24841,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24868,7 +24868,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>130068767</v>
+        <v>130068745</v>
       </c>
       <c r="B234" t="n">
         <v>79180</v>
@@ -24903,10 +24903,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>490711</v>
+        <v>490627</v>
       </c>
       <c r="R234" t="n">
-        <v>6820988</v>
+        <v>6821161</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24938,7 +24938,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -24948,7 +24948,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -24975,7 +24975,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>130068820</v>
+        <v>130068905</v>
       </c>
       <c r="B235" t="n">
         <v>79180</v>
@@ -25010,10 +25010,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>491083</v>
+        <v>490465</v>
       </c>
       <c r="R235" t="n">
-        <v>6820517</v>
+        <v>6821218</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25045,7 +25045,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -25055,7 +25055,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -25082,7 +25082,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>130068813</v>
+        <v>130068906</v>
       </c>
       <c r="B236" t="n">
         <v>79180</v>
@@ -25117,10 +25117,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>491226</v>
+        <v>490456</v>
       </c>
       <c r="R236" t="n">
-        <v>6820480</v>
+        <v>6821215</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -25162,7 +25162,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25189,7 +25189,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>130068704</v>
+        <v>130068766</v>
       </c>
       <c r="B237" t="n">
         <v>79180</v>
@@ -25224,10 +25224,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>490432</v>
+        <v>490705</v>
       </c>
       <c r="R237" t="n">
-        <v>6821264</v>
+        <v>6821005</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25259,7 +25259,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25296,7 +25296,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>130068745</v>
+        <v>130068727</v>
       </c>
       <c r="B238" t="n">
         <v>79180</v>
@@ -25331,10 +25331,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>490627</v>
+        <v>490537</v>
       </c>
       <c r="R238" t="n">
-        <v>6821161</v>
+        <v>6821254</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25366,7 +25366,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -25403,7 +25403,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>130068905</v>
+        <v>130068744</v>
       </c>
       <c r="B239" t="n">
         <v>79180</v>
@@ -25438,10 +25438,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>490465</v>
+        <v>490605</v>
       </c>
       <c r="R239" t="n">
-        <v>6821218</v>
+        <v>6821175</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25473,7 +25473,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -25510,10 +25510,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>130068906</v>
+        <v>130068583</v>
       </c>
       <c r="B240" t="n">
-        <v>79180</v>
+        <v>79212</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -25521,21 +25521,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -25545,10 +25545,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>490456</v>
+        <v>491003</v>
       </c>
       <c r="R240" t="n">
-        <v>6821215</v>
+        <v>6820778</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25580,7 +25580,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -25590,7 +25590,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -25617,7 +25617,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>130068872</v>
+        <v>130068751</v>
       </c>
       <c r="B241" t="n">
         <v>79180</v>
@@ -25652,10 +25652,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>490677</v>
+        <v>490626</v>
       </c>
       <c r="R241" t="n">
-        <v>6820976</v>
+        <v>6821133</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25687,7 +25687,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -25697,7 +25697,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -25724,10 +25724,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>130068663</v>
+        <v>130068807</v>
       </c>
       <c r="B242" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25735,21 +25735,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25759,10 +25759,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>490449</v>
+        <v>491248</v>
       </c>
       <c r="R242" t="n">
-        <v>6821237</v>
+        <v>6820566</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -25804,7 +25804,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25831,10 +25831,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>130068927</v>
+        <v>130068794</v>
       </c>
       <c r="B243" t="n">
-        <v>78846</v>
+        <v>79180</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25842,21 +25842,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25866,10 +25866,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>490948</v>
+        <v>491171</v>
       </c>
       <c r="R243" t="n">
-        <v>6820619</v>
+        <v>6820628</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25901,7 +25901,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -25911,7 +25911,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25938,10 +25938,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>130068931</v>
+        <v>130068788</v>
       </c>
       <c r="B244" t="n">
-        <v>78846</v>
+        <v>79180</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25949,21 +25949,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25973,10 +25973,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>490510</v>
+        <v>491152</v>
       </c>
       <c r="R244" t="n">
-        <v>6821122</v>
+        <v>6820778</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -26008,7 +26008,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -26018,7 +26018,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -26045,7 +26045,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>130068834</v>
+        <v>130068709</v>
       </c>
       <c r="B245" t="n">
         <v>79180</v>
@@ -26080,10 +26080,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>490981</v>
+        <v>490438</v>
       </c>
       <c r="R245" t="n">
-        <v>6820625</v>
+        <v>6821306</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -26115,7 +26115,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -26125,7 +26125,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -26152,7 +26152,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>130068824</v>
+        <v>130068862</v>
       </c>
       <c r="B246" t="n">
         <v>79180</v>
@@ -26187,10 +26187,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>491021</v>
+        <v>490788</v>
       </c>
       <c r="R246" t="n">
-        <v>6820562</v>
+        <v>6820868</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -26232,7 +26232,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26259,7 +26259,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>130068751</v>
+        <v>130068773</v>
       </c>
       <c r="B247" t="n">
         <v>79180</v>
@@ -26294,10 +26294,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>490626</v>
+        <v>491101</v>
       </c>
       <c r="R247" t="n">
-        <v>6821133</v>
+        <v>6820784</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26329,7 +26329,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -26339,7 +26339,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -26366,7 +26366,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>130068807</v>
+        <v>130068872</v>
       </c>
       <c r="B248" t="n">
         <v>79180</v>
@@ -26401,10 +26401,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>491248</v>
+        <v>490677</v>
       </c>
       <c r="R248" t="n">
-        <v>6820566</v>
+        <v>6820976</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26436,7 +26436,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26473,10 +26473,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>130068794</v>
+        <v>130068663</v>
       </c>
       <c r="B249" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26484,21 +26484,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -26508,10 +26508,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>491171</v>
+        <v>490449</v>
       </c>
       <c r="R249" t="n">
-        <v>6820628</v>
+        <v>6821237</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26543,7 +26543,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -26553,7 +26553,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26580,10 +26580,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>130068788</v>
+        <v>130068931</v>
       </c>
       <c r="B250" t="n">
-        <v>79180</v>
+        <v>78846</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26591,21 +26591,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -26615,10 +26615,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>491152</v>
+        <v>490510</v>
       </c>
       <c r="R250" t="n">
-        <v>6820778</v>
+        <v>6821122</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -26660,7 +26660,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26687,7 +26687,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>130068709</v>
+        <v>130068834</v>
       </c>
       <c r="B251" t="n">
         <v>79180</v>
@@ -26722,10 +26722,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>490438</v>
+        <v>490981</v>
       </c>
       <c r="R251" t="n">
-        <v>6821306</v>
+        <v>6820625</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -26767,7 +26767,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26794,7 +26794,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>130068862</v>
+        <v>130068824</v>
       </c>
       <c r="B252" t="n">
         <v>79180</v>
@@ -26829,10 +26829,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>490788</v>
+        <v>491021</v>
       </c>
       <c r="R252" t="n">
-        <v>6820868</v>
+        <v>6820562</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26864,7 +26864,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -26874,7 +26874,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -26901,10 +26901,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>130068773</v>
+        <v>130068927</v>
       </c>
       <c r="B253" t="n">
-        <v>79180</v>
+        <v>78846</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26912,21 +26912,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -26936,10 +26936,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>491101</v>
+        <v>490948</v>
       </c>
       <c r="R253" t="n">
-        <v>6820784</v>
+        <v>6820619</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26971,7 +26971,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -27008,10 +27008,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>130068674</v>
+        <v>130068677</v>
       </c>
       <c r="B254" t="n">
-        <v>98920</v>
+        <v>91901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -27019,43 +27019,34 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>490606</v>
+        <v>490384</v>
       </c>
       <c r="R254" t="n">
-        <v>6821108</v>
+        <v>6821360</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -27087,7 +27078,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -27097,7 +27088,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27124,32 +27115,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>130068645</v>
+        <v>130068590</v>
       </c>
       <c r="B255" t="n">
-        <v>81165</v>
+        <v>91692</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -27159,10 +27150,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>490554</v>
+        <v>490670</v>
       </c>
       <c r="R255" t="n">
-        <v>6821209</v>
+        <v>6821056</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -27194,7 +27185,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -27204,7 +27195,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -27231,7 +27222,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>130068708</v>
+        <v>130068909</v>
       </c>
       <c r="B256" t="n">
         <v>79180</v>
@@ -27266,10 +27257,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>490439</v>
+        <v>490479</v>
       </c>
       <c r="R256" t="n">
-        <v>6821301</v>
+        <v>6821264</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -27301,7 +27292,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -27311,7 +27302,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27338,7 +27329,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>130068705</v>
+        <v>130068746</v>
       </c>
       <c r="B257" t="n">
         <v>79180</v>
@@ -27373,10 +27364,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>490431</v>
+        <v>490617</v>
       </c>
       <c r="R257" t="n">
-        <v>6821274</v>
+        <v>6821148</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27408,7 +27399,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -27418,7 +27409,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27445,32 +27436,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>130068677</v>
+        <v>130068723</v>
       </c>
       <c r="B258" t="n">
-        <v>91901</v>
+        <v>79180</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -27480,10 +27471,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>490384</v>
+        <v>490527</v>
       </c>
       <c r="R258" t="n">
-        <v>6821360</v>
+        <v>6821279</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27515,7 +27506,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -27525,7 +27516,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -27552,32 +27543,32 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>130068590</v>
+        <v>130068708</v>
       </c>
       <c r="B259" t="n">
-        <v>91692</v>
+        <v>79180</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -27587,10 +27578,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>490670</v>
+        <v>490439</v>
       </c>
       <c r="R259" t="n">
-        <v>6821056</v>
+        <v>6821301</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27622,7 +27613,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -27632,7 +27623,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -27659,10 +27650,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>130068909</v>
+        <v>130068571</v>
       </c>
       <c r="B260" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -27670,21 +27661,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -27694,10 +27685,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>490479</v>
+        <v>491234</v>
       </c>
       <c r="R260" t="n">
-        <v>6821264</v>
+        <v>6820562</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27729,7 +27720,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -27739,7 +27730,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -27766,10 +27757,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>130068746</v>
+        <v>130068566</v>
       </c>
       <c r="B261" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -27777,21 +27768,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -27801,10 +27792,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>490617</v>
+        <v>490653</v>
       </c>
       <c r="R261" t="n">
-        <v>6821148</v>
+        <v>6821056</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27836,7 +27827,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -27846,7 +27837,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -27873,10 +27864,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>130068723</v>
+        <v>130068577</v>
       </c>
       <c r="B262" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -27884,21 +27875,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -27908,10 +27899,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>490527</v>
+        <v>490510</v>
       </c>
       <c r="R262" t="n">
-        <v>6821279</v>
+        <v>6821122</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27943,7 +27934,7 @@
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -27953,7 +27944,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -27980,10 +27971,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>130068571</v>
+        <v>130068645</v>
       </c>
       <c r="B263" t="n">
-        <v>79799</v>
+        <v>81165</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -27991,21 +27982,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -28015,10 +28006,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>491234</v>
+        <v>490554</v>
       </c>
       <c r="R263" t="n">
-        <v>6820562</v>
+        <v>6821209</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -28050,7 +28041,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -28060,7 +28051,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -28087,10 +28078,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>130068566</v>
+        <v>130068705</v>
       </c>
       <c r="B264" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -28098,21 +28089,21 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -28122,10 +28113,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>490653</v>
+        <v>490431</v>
       </c>
       <c r="R264" t="n">
-        <v>6821056</v>
+        <v>6821274</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -28157,7 +28148,7 @@
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -28167,7 +28158,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -28194,10 +28185,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>130068577</v>
+        <v>130068647</v>
       </c>
       <c r="B265" t="n">
-        <v>79799</v>
+        <v>78937</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -28205,21 +28196,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -28229,10 +28220,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>490510</v>
+        <v>490333</v>
       </c>
       <c r="R265" t="n">
-        <v>6821122</v>
+        <v>6821419</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -28264,7 +28255,7 @@
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
@@ -28274,7 +28265,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -28301,7 +28292,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>130068647</v>
+        <v>130068649</v>
       </c>
       <c r="B266" t="n">
         <v>78937</v>
@@ -28336,10 +28327,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>490333</v>
+        <v>490404</v>
       </c>
       <c r="R266" t="n">
-        <v>6821419</v>
+        <v>6821355</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28371,7 +28362,7 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -28381,7 +28372,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28408,10 +28399,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>130068649</v>
+        <v>130068676</v>
       </c>
       <c r="B267" t="n">
-        <v>78937</v>
+        <v>5176</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -28419,34 +28410,39 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6446</v>
+        <v>102204</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P267" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>490404</v>
+        <v>490599</v>
       </c>
       <c r="R267" t="n">
-        <v>6821355</v>
+        <v>6821131</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28478,7 +28474,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -28488,7 +28484,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28515,38 +28511,42 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>130068676</v>
+        <v>130068674</v>
       </c>
       <c r="B268" t="n">
-        <v>5176</v>
+        <v>98920</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>102204</v>
+        <v>220787</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
@@ -28555,10 +28555,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>490599</v>
+        <v>490606</v>
       </c>
       <c r="R268" t="n">
-        <v>6821131</v>
+        <v>6821108</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28590,7 +28590,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -28600,7 +28600,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -32488,32 +32488,32 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>130068634</v>
+        <v>130068921</v>
       </c>
       <c r="B305" t="n">
-        <v>78938</v>
+        <v>93010</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -32523,10 +32523,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>490332</v>
+        <v>490679</v>
       </c>
       <c r="R305" t="n">
-        <v>6821426</v>
+        <v>6820958</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -32558,7 +32558,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -32568,7 +32568,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -32595,10 +32595,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>130068639</v>
+        <v>130068702</v>
       </c>
       <c r="B306" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -32606,21 +32606,21 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
@@ -32630,10 +32630,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>490401</v>
+        <v>490438</v>
       </c>
       <c r="R306" t="n">
-        <v>6821264</v>
+        <v>6821252</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -32675,7 +32675,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -32702,32 +32702,32 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>130068686</v>
+        <v>130068603</v>
       </c>
       <c r="B307" t="n">
-        <v>79180</v>
+        <v>80314</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -32737,10 +32737,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>490393</v>
+        <v>491182</v>
       </c>
       <c r="R307" t="n">
-        <v>6821358</v>
+        <v>6820747</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -32772,7 +32772,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -32782,7 +32782,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -32809,32 +32809,32 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>130068901</v>
+        <v>130068622</v>
       </c>
       <c r="B308" t="n">
-        <v>79180</v>
+        <v>80313</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -32844,10 +32844,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>490479</v>
+        <v>490534</v>
       </c>
       <c r="R308" t="n">
-        <v>6821177</v>
+        <v>6821209</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -32879,7 +32879,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -32889,7 +32889,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -32916,10 +32916,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>130068875</v>
+        <v>130068634</v>
       </c>
       <c r="B309" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -32927,21 +32927,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -32951,10 +32951,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>490675</v>
+        <v>490332</v>
       </c>
       <c r="R309" t="n">
-        <v>6821007</v>
+        <v>6821426</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -32986,7 +32986,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -32996,7 +32996,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -33023,10 +33023,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>130068891</v>
+        <v>130068639</v>
       </c>
       <c r="B310" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -33034,21 +33034,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -33058,10 +33058,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>490526</v>
+        <v>490401</v>
       </c>
       <c r="R310" t="n">
-        <v>6821120</v>
+        <v>6821264</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -33093,7 +33093,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -33103,7 +33103,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -33130,7 +33130,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>130068749</v>
+        <v>130068686</v>
       </c>
       <c r="B311" t="n">
         <v>79180</v>
@@ -33165,10 +33165,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>490607</v>
+        <v>490393</v>
       </c>
       <c r="R311" t="n">
-        <v>6821129</v>
+        <v>6821358</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -33200,7 +33200,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -33210,7 +33210,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -33237,7 +33237,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>130068714</v>
+        <v>130068901</v>
       </c>
       <c r="B312" t="n">
         <v>79180</v>
@@ -33272,10 +33272,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>490444</v>
+        <v>490479</v>
       </c>
       <c r="R312" t="n">
-        <v>6821345</v>
+        <v>6821177</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -33307,7 +33307,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -33317,7 +33317,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -33344,7 +33344,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>130068702</v>
+        <v>130068875</v>
       </c>
       <c r="B313" t="n">
         <v>79180</v>
@@ -33379,10 +33379,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>490438</v>
+        <v>490675</v>
       </c>
       <c r="R313" t="n">
-        <v>6821252</v>
+        <v>6821007</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -33414,7 +33414,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -33424,7 +33424,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -33451,32 +33451,32 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>130068603</v>
+        <v>130068891</v>
       </c>
       <c r="B314" t="n">
-        <v>80314</v>
+        <v>79180</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
@@ -33486,10 +33486,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>491182</v>
+        <v>490526</v>
       </c>
       <c r="R314" t="n">
-        <v>6820747</v>
+        <v>6821120</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -33521,7 +33521,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -33531,7 +33531,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD314" t="b">
@@ -33558,32 +33558,32 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>130068622</v>
+        <v>130068749</v>
       </c>
       <c r="B315" t="n">
-        <v>80313</v>
+        <v>79180</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -33593,10 +33593,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>490534</v>
+        <v>490607</v>
       </c>
       <c r="R315" t="n">
-        <v>6821209</v>
+        <v>6821129</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>
@@ -33628,7 +33628,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -33638,7 +33638,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD315" t="b">
@@ -33665,32 +33665,32 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>130068921</v>
+        <v>130068714</v>
       </c>
       <c r="B316" t="n">
-        <v>93010</v>
+        <v>79180</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
@@ -33700,10 +33700,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>490679</v>
+        <v>490444</v>
       </c>
       <c r="R316" t="n">
-        <v>6820958</v>
+        <v>6821345</v>
       </c>
       <c r="S316" t="n">
         <v>10</v>
@@ -33735,7 +33735,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -33745,7 +33745,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD316" t="b">
@@ -35056,10 +35056,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>130068635</v>
+        <v>130068888</v>
       </c>
       <c r="B329" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -35067,21 +35067,21 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
@@ -35091,10 +35091,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>490388</v>
+        <v>490539</v>
       </c>
       <c r="R329" t="n">
-        <v>6821389</v>
+        <v>6821155</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -35126,7 +35126,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD329" t="b">
@@ -35163,32 +35163,32 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>130068621</v>
+        <v>130068791</v>
       </c>
       <c r="B330" t="n">
-        <v>80313</v>
+        <v>79180</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
@@ -35198,10 +35198,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>490525</v>
+        <v>491166</v>
       </c>
       <c r="R330" t="n">
-        <v>6821278</v>
+        <v>6820674</v>
       </c>
       <c r="S330" t="n">
         <v>10</v>
@@ -35233,7 +35233,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -35243,7 +35243,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD330" t="b">
@@ -35252,7 +35252,6 @@
       <c r="AE330" t="b">
         <v>0</v>
       </c>
-      <c r="AF330" t="inlineStr"/>
       <c r="AG330" t="b">
         <v>0</v>
       </c>
@@ -35271,7 +35270,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>130068825</v>
+        <v>130068884</v>
       </c>
       <c r="B331" t="n">
         <v>79180</v>
@@ -35306,10 +35305,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>491008</v>
+        <v>490575</v>
       </c>
       <c r="R331" t="n">
-        <v>6820554</v>
+        <v>6821126</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -35341,7 +35340,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -35351,7 +35350,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -35378,7 +35377,7 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>130068908</v>
+        <v>130068731</v>
       </c>
       <c r="B332" t="n">
         <v>79180</v>
@@ -35413,10 +35412,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>490464</v>
+        <v>490550</v>
       </c>
       <c r="R332" t="n">
-        <v>6821244</v>
+        <v>6821227</v>
       </c>
       <c r="S332" t="n">
         <v>10</v>
@@ -35448,7 +35447,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -35458,7 +35457,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD332" t="b">
@@ -35485,7 +35484,7 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>130068839</v>
+        <v>130068869</v>
       </c>
       <c r="B333" t="n">
         <v>79180</v>
@@ -35520,10 +35519,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>490865</v>
+        <v>490702</v>
       </c>
       <c r="R333" t="n">
-        <v>6820655</v>
+        <v>6820970</v>
       </c>
       <c r="S333" t="n">
         <v>10</v>
@@ -35555,7 +35554,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -35565,7 +35564,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -35592,10 +35591,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>130068888</v>
+        <v>130068635</v>
       </c>
       <c r="B334" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -35603,21 +35602,21 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
@@ -35627,10 +35626,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>490539</v>
+        <v>490388</v>
       </c>
       <c r="R334" t="n">
-        <v>6821155</v>
+        <v>6821389</v>
       </c>
       <c r="S334" t="n">
         <v>10</v>
@@ -35662,7 +35661,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -35672,7 +35671,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -35699,7 +35698,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>130068791</v>
+        <v>130068908</v>
       </c>
       <c r="B335" t="n">
         <v>79180</v>
@@ -35734,10 +35733,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>491166</v>
+        <v>490464</v>
       </c>
       <c r="R335" t="n">
-        <v>6820674</v>
+        <v>6821244</v>
       </c>
       <c r="S335" t="n">
         <v>10</v>
@@ -35769,7 +35768,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -35779,7 +35778,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -35806,7 +35805,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>130068884</v>
+        <v>130068839</v>
       </c>
       <c r="B336" t="n">
         <v>79180</v>
@@ -35841,10 +35840,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>490575</v>
+        <v>490865</v>
       </c>
       <c r="R336" t="n">
-        <v>6821126</v>
+        <v>6820655</v>
       </c>
       <c r="S336" t="n">
         <v>10</v>
@@ -35876,7 +35875,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -35886,7 +35885,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -35913,7 +35912,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>130068731</v>
+        <v>130068738</v>
       </c>
       <c r="B337" t="n">
         <v>79180</v>
@@ -35948,10 +35947,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>490550</v>
+        <v>490564</v>
       </c>
       <c r="R337" t="n">
-        <v>6821227</v>
+        <v>6821207</v>
       </c>
       <c r="S337" t="n">
         <v>10</v>
@@ -35983,7 +35982,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -35993,7 +35992,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -36020,7 +36019,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>130068869</v>
+        <v>130068810</v>
       </c>
       <c r="B338" t="n">
         <v>79180</v>
@@ -36055,10 +36054,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>490702</v>
+        <v>491233</v>
       </c>
       <c r="R338" t="n">
-        <v>6820970</v>
+        <v>6820538</v>
       </c>
       <c r="S338" t="n">
         <v>10</v>
@@ -36090,7 +36089,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -36100,7 +36099,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -36127,32 +36126,32 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>130068738</v>
+        <v>130068621</v>
       </c>
       <c r="B339" t="n">
-        <v>79180</v>
+        <v>80313</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
@@ -36162,10 +36161,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>490564</v>
+        <v>490525</v>
       </c>
       <c r="R339" t="n">
-        <v>6821207</v>
+        <v>6821278</v>
       </c>
       <c r="S339" t="n">
         <v>10</v>
@@ -36197,7 +36196,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -36207,7 +36206,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -36216,6 +36215,7 @@
       <c r="AE339" t="b">
         <v>0</v>
       </c>
+      <c r="AF339" t="inlineStr"/>
       <c r="AG339" t="b">
         <v>0</v>
       </c>
@@ -36234,7 +36234,7 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>130068810</v>
+        <v>130068825</v>
       </c>
       <c r="B340" t="n">
         <v>79180</v>
@@ -36269,10 +36269,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>491233</v>
+        <v>491008</v>
       </c>
       <c r="R340" t="n">
-        <v>6820538</v>
+        <v>6820554</v>
       </c>
       <c r="S340" t="n">
         <v>10</v>
@@ -36304,7 +36304,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -36314,7 +36314,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD340" t="b">
@@ -36341,10 +36341,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>130068787</v>
+        <v>130068606</v>
       </c>
       <c r="B341" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -36352,34 +36352,42 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>491207</v>
+        <v>490394</v>
       </c>
       <c r="R341" t="n">
-        <v>6820802</v>
+        <v>6821362</v>
       </c>
       <c r="S341" t="n">
         <v>10</v>
@@ -36411,7 +36419,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -36421,7 +36429,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD341" t="b">
@@ -36448,7 +36456,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>130068695</v>
+        <v>130068787</v>
       </c>
       <c r="B342" t="n">
         <v>79180</v>
@@ -36483,10 +36491,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>490372</v>
+        <v>491207</v>
       </c>
       <c r="R342" t="n">
-        <v>6821292</v>
+        <v>6820802</v>
       </c>
       <c r="S342" t="n">
         <v>10</v>
@@ -36518,7 +36526,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -36528,7 +36536,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD342" t="b">
@@ -36555,7 +36563,7 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>130068710</v>
+        <v>130068695</v>
       </c>
       <c r="B343" t="n">
         <v>79180</v>
@@ -36590,10 +36598,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>490439</v>
+        <v>490372</v>
       </c>
       <c r="R343" t="n">
-        <v>6821312</v>
+        <v>6821292</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -36625,7 +36633,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -36635,7 +36643,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD343" t="b">
@@ -36662,7 +36670,7 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>130068823</v>
+        <v>130068710</v>
       </c>
       <c r="B344" t="n">
         <v>79180</v>
@@ -36697,10 +36705,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>491046</v>
+        <v>490439</v>
       </c>
       <c r="R344" t="n">
-        <v>6820573</v>
+        <v>6821312</v>
       </c>
       <c r="S344" t="n">
         <v>10</v>
@@ -36732,7 +36740,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -36742,7 +36750,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD344" t="b">
@@ -36769,7 +36777,7 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>130068790</v>
+        <v>130068823</v>
       </c>
       <c r="B345" t="n">
         <v>79180</v>
@@ -36804,10 +36812,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>491190</v>
+        <v>491046</v>
       </c>
       <c r="R345" t="n">
-        <v>6820717</v>
+        <v>6820573</v>
       </c>
       <c r="S345" t="n">
         <v>10</v>
@@ -36839,7 +36847,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -36849,7 +36857,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD345" t="b">
@@ -36876,7 +36884,7 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>130068849</v>
+        <v>130068790</v>
       </c>
       <c r="B346" t="n">
         <v>79180</v>
@@ -36911,10 +36919,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>491023</v>
+        <v>491190</v>
       </c>
       <c r="R346" t="n">
-        <v>6820788</v>
+        <v>6820717</v>
       </c>
       <c r="S346" t="n">
         <v>10</v>
@@ -36946,7 +36954,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -36956,7 +36964,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD346" t="b">
@@ -36983,7 +36991,7 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>130068812</v>
+        <v>130068849</v>
       </c>
       <c r="B347" t="n">
         <v>79180</v>
@@ -37018,10 +37026,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>491240</v>
+        <v>491023</v>
       </c>
       <c r="R347" t="n">
-        <v>6820517</v>
+        <v>6820788</v>
       </c>
       <c r="S347" t="n">
         <v>10</v>
@@ -37053,7 +37061,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -37063,7 +37071,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD347" t="b">
@@ -37090,7 +37098,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>130068760</v>
+        <v>130068812</v>
       </c>
       <c r="B348" t="n">
         <v>79180</v>
@@ -37125,10 +37133,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>490695</v>
+        <v>491240</v>
       </c>
       <c r="R348" t="n">
-        <v>6821031</v>
+        <v>6820517</v>
       </c>
       <c r="S348" t="n">
         <v>10</v>
@@ -37160,7 +37168,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -37170,7 +37178,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD348" t="b">
@@ -37197,7 +37205,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>130068779</v>
+        <v>130068760</v>
       </c>
       <c r="B349" t="n">
         <v>79180</v>
@@ -37232,10 +37240,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>491151</v>
+        <v>490695</v>
       </c>
       <c r="R349" t="n">
-        <v>6820805</v>
+        <v>6821031</v>
       </c>
       <c r="S349" t="n">
         <v>10</v>
@@ -37267,7 +37275,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -37277,7 +37285,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD349" t="b">
@@ -37304,7 +37312,7 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>130068894</v>
+        <v>130068779</v>
       </c>
       <c r="B350" t="n">
         <v>79180</v>
@@ -37339,10 +37347,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>490495</v>
+        <v>491151</v>
       </c>
       <c r="R350" t="n">
-        <v>6821096</v>
+        <v>6820805</v>
       </c>
       <c r="S350" t="n">
         <v>10</v>
@@ -37374,7 +37382,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -37384,7 +37392,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD350" t="b">
@@ -37411,7 +37419,7 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>130068897</v>
+        <v>130068894</v>
       </c>
       <c r="B351" t="n">
         <v>79180</v>
@@ -37446,10 +37454,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>490474</v>
+        <v>490495</v>
       </c>
       <c r="R351" t="n">
-        <v>6821107</v>
+        <v>6821096</v>
       </c>
       <c r="S351" t="n">
         <v>10</v>
@@ -37481,7 +37489,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -37491,7 +37499,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD351" t="b">
@@ -37518,10 +37526,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>130068629</v>
+        <v>130068897</v>
       </c>
       <c r="B352" t="n">
-        <v>93048</v>
+        <v>79180</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -37529,21 +37537,21 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
@@ -37553,10 +37561,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>490667</v>
+        <v>490474</v>
       </c>
       <c r="R352" t="n">
-        <v>6820977</v>
+        <v>6821107</v>
       </c>
       <c r="S352" t="n">
         <v>10</v>
@@ -37588,7 +37596,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -37598,7 +37606,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD352" t="b">
@@ -37625,7 +37633,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>130068626</v>
+        <v>130068629</v>
       </c>
       <c r="B353" t="n">
         <v>93048</v>
@@ -37660,10 +37668,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>491243</v>
+        <v>490667</v>
       </c>
       <c r="R353" t="n">
-        <v>6820605</v>
+        <v>6820977</v>
       </c>
       <c r="S353" t="n">
         <v>10</v>
@@ -37695,7 +37703,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -37705,7 +37713,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD353" t="b">
@@ -37732,10 +37740,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>130068711</v>
+        <v>130068626</v>
       </c>
       <c r="B354" t="n">
-        <v>79180</v>
+        <v>93048</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -37743,21 +37751,21 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I354" t="inlineStr"/>
@@ -37767,10 +37775,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>490435</v>
+        <v>491243</v>
       </c>
       <c r="R354" t="n">
-        <v>6821316</v>
+        <v>6820605</v>
       </c>
       <c r="S354" t="n">
         <v>10</v>
@@ -37802,7 +37810,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -37812,7 +37820,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD354" t="b">
@@ -37839,7 +37847,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>130068796</v>
+        <v>130068711</v>
       </c>
       <c r="B355" t="n">
         <v>79180</v>
@@ -37874,10 +37882,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>491176</v>
+        <v>490435</v>
       </c>
       <c r="R355" t="n">
-        <v>6820628</v>
+        <v>6821316</v>
       </c>
       <c r="S355" t="n">
         <v>10</v>
@@ -37909,7 +37917,7 @@
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
@@ -37919,7 +37927,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD355" t="b">
@@ -37946,10 +37954,10 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>130068881</v>
+        <v>130068640</v>
       </c>
       <c r="B356" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -37957,21 +37965,21 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I356" t="inlineStr"/>
@@ -37981,10 +37989,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>490610</v>
+        <v>491183</v>
       </c>
       <c r="R356" t="n">
-        <v>6821092</v>
+        <v>6820741</v>
       </c>
       <c r="S356" t="n">
         <v>10</v>
@@ -38016,7 +38024,7 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -38026,7 +38034,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD356" t="b">
@@ -38053,10 +38061,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>130068830</v>
+        <v>130068562</v>
       </c>
       <c r="B357" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -38064,21 +38072,21 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I357" t="inlineStr"/>
@@ -38088,10 +38096,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>490969</v>
+        <v>490522</v>
       </c>
       <c r="R357" t="n">
-        <v>6820589</v>
+        <v>6821366</v>
       </c>
       <c r="S357" t="n">
         <v>10</v>
@@ -38123,7 +38131,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -38133,7 +38141,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD357" t="b">
@@ -38160,10 +38168,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>130068606</v>
+        <v>130068564</v>
       </c>
       <c r="B358" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -38171,42 +38179,34 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I358" t="inlineStr"/>
-      <c r="K358" t="inlineStr"/>
-      <c r="L358" t="inlineStr"/>
-      <c r="M358" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N358" t="inlineStr"/>
       <c r="P358" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>490394</v>
+        <v>490628</v>
       </c>
       <c r="R358" t="n">
-        <v>6821362</v>
+        <v>6821065</v>
       </c>
       <c r="S358" t="n">
         <v>10</v>
@@ -38238,7 +38238,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -38248,7 +38248,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD358" t="b">
@@ -38275,50 +38275,45 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>130068632</v>
+        <v>130068796</v>
       </c>
       <c r="B359" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
-      <c r="M359" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P359" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>490598</v>
+        <v>491176</v>
       </c>
       <c r="R359" t="n">
-        <v>6821145</v>
+        <v>6820628</v>
       </c>
       <c r="S359" t="n">
         <v>10</v>
@@ -38350,7 +38345,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -38360,7 +38355,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD359" t="b">
@@ -38387,10 +38382,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>130068640</v>
+        <v>130068881</v>
       </c>
       <c r="B360" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -38398,21 +38393,21 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I360" t="inlineStr"/>
@@ -38422,10 +38417,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>491183</v>
+        <v>490610</v>
       </c>
       <c r="R360" t="n">
-        <v>6820741</v>
+        <v>6821092</v>
       </c>
       <c r="S360" t="n">
         <v>10</v>
@@ -38457,7 +38452,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -38467,7 +38462,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD360" t="b">
@@ -38494,10 +38489,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>130068562</v>
+        <v>130068830</v>
       </c>
       <c r="B361" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -38505,21 +38500,21 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I361" t="inlineStr"/>
@@ -38529,10 +38524,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>490522</v>
+        <v>490969</v>
       </c>
       <c r="R361" t="n">
-        <v>6821366</v>
+        <v>6820589</v>
       </c>
       <c r="S361" t="n">
         <v>10</v>
@@ -38564,7 +38559,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -38574,7 +38569,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD361" t="b">
@@ -38601,10 +38596,10 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>130068564</v>
+        <v>130068578</v>
       </c>
       <c r="B362" t="n">
-        <v>79799</v>
+        <v>91651</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -38612,21 +38607,21 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I362" t="inlineStr"/>
@@ -38636,10 +38631,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>490628</v>
+        <v>490566</v>
       </c>
       <c r="R362" t="n">
-        <v>6821065</v>
+        <v>6821130</v>
       </c>
       <c r="S362" t="n">
         <v>10</v>
@@ -38671,7 +38666,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -38681,7 +38676,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD362" t="b">
@@ -38708,45 +38703,50 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>130068578</v>
+        <v>130068632</v>
       </c>
       <c r="B363" t="n">
-        <v>91651</v>
+        <v>8451</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>3242</v>
+        <v>106545</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr"/>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P363" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>490566</v>
+        <v>490598</v>
       </c>
       <c r="R363" t="n">
-        <v>6821130</v>
+        <v>6821145</v>
       </c>
       <c r="S363" t="n">
         <v>10</v>
@@ -38778,7 +38778,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -38788,7 +38788,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD363" t="b">
@@ -40229,10 +40229,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>130068703</v>
+        <v>130068568</v>
       </c>
       <c r="B377" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -40240,21 +40240,21 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I377" t="inlineStr"/>
@@ -40264,10 +40264,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>490436</v>
+        <v>490698</v>
       </c>
       <c r="R377" t="n">
-        <v>6821261</v>
+        <v>6821013</v>
       </c>
       <c r="S377" t="n">
         <v>10</v>
@@ -40299,7 +40299,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -40309,7 +40309,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD377" t="b">
@@ -40336,10 +40336,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>130068733</v>
+        <v>130068572</v>
       </c>
       <c r="B378" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -40347,21 +40347,21 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I378" t="inlineStr"/>
@@ -40371,10 +40371,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>490539</v>
+        <v>490961</v>
       </c>
       <c r="R378" t="n">
-        <v>6821218</v>
+        <v>6820600</v>
       </c>
       <c r="S378" t="n">
         <v>10</v>
@@ -40406,7 +40406,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -40416,7 +40416,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD378" t="b">
@@ -40443,45 +40443,50 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>130068690</v>
+        <v>130068595</v>
       </c>
       <c r="B379" t="n">
-        <v>79180</v>
+        <v>57016</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I379" t="inlineStr"/>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P379" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>490406</v>
+        <v>490535</v>
       </c>
       <c r="R379" t="n">
-        <v>6821345</v>
+        <v>6821122</v>
       </c>
       <c r="S379" t="n">
         <v>10</v>
@@ -40513,7 +40518,7 @@
       </c>
       <c r="Z379" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
@@ -40523,7 +40528,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD379" t="b">
@@ -40550,7 +40555,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>130068882</v>
+        <v>130068703</v>
       </c>
       <c r="B380" t="n">
         <v>79180</v>
@@ -40585,10 +40590,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>490609</v>
+        <v>490436</v>
       </c>
       <c r="R380" t="n">
-        <v>6821100</v>
+        <v>6821261</v>
       </c>
       <c r="S380" t="n">
         <v>10</v>
@@ -40620,7 +40625,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -40630,7 +40635,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD380" t="b">
@@ -40657,50 +40662,45 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>130068595</v>
+        <v>130068733</v>
       </c>
       <c r="B381" t="n">
-        <v>57016</v>
+        <v>79180</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I381" t="inlineStr"/>
-      <c r="M381" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P381" t="inlineStr">
         <is>
           <t>Råbergskojan, Dlr</t>
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>490535</v>
+        <v>490539</v>
       </c>
       <c r="R381" t="n">
-        <v>6821122</v>
+        <v>6821218</v>
       </c>
       <c r="S381" t="n">
         <v>10</v>
@@ -40732,7 +40732,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -40742,7 +40742,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD381" t="b">
@@ -40769,10 +40769,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>130068628</v>
+        <v>130068690</v>
       </c>
       <c r="B382" t="n">
-        <v>93048</v>
+        <v>79180</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -40780,21 +40780,21 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I382" t="inlineStr"/>
@@ -40804,10 +40804,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>490896</v>
+        <v>490406</v>
       </c>
       <c r="R382" t="n">
-        <v>6820806</v>
+        <v>6821345</v>
       </c>
       <c r="S382" t="n">
         <v>10</v>
@@ -40839,7 +40839,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -40849,7 +40849,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD382" t="b">
@@ -40876,7 +40876,7 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>130068761</v>
+        <v>130068882</v>
       </c>
       <c r="B383" t="n">
         <v>79180</v>
@@ -40911,10 +40911,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>490698</v>
+        <v>490609</v>
       </c>
       <c r="R383" t="n">
-        <v>6821021</v>
+        <v>6821100</v>
       </c>
       <c r="S383" t="n">
         <v>10</v>
@@ -40946,7 +40946,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -40956,7 +40956,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD383" t="b">
@@ -40983,10 +40983,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>130068762</v>
+        <v>130068628</v>
       </c>
       <c r="B384" t="n">
-        <v>79180</v>
+        <v>93048</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -40994,21 +40994,21 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I384" t="inlineStr"/>
@@ -41018,10 +41018,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>490687</v>
+        <v>490896</v>
       </c>
       <c r="R384" t="n">
-        <v>6821018</v>
+        <v>6820806</v>
       </c>
       <c r="S384" t="n">
         <v>10</v>
@@ -41053,7 +41053,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -41063,7 +41063,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD384" t="b">
@@ -41090,7 +41090,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>130068732</v>
+        <v>130068761</v>
       </c>
       <c r="B385" t="n">
         <v>79180</v>
@@ -41125,10 +41125,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>490542</v>
+        <v>490698</v>
       </c>
       <c r="R385" t="n">
-        <v>6821224</v>
+        <v>6821021</v>
       </c>
       <c r="S385" t="n">
         <v>10</v>
@@ -41160,7 +41160,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -41170,7 +41170,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD385" t="b">
@@ -41197,10 +41197,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>130068568</v>
+        <v>130068762</v>
       </c>
       <c r="B386" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -41208,21 +41208,21 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I386" t="inlineStr"/>
@@ -41232,10 +41232,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>490698</v>
+        <v>490687</v>
       </c>
       <c r="R386" t="n">
-        <v>6821013</v>
+        <v>6821018</v>
       </c>
       <c r="S386" t="n">
         <v>10</v>
@@ -41267,7 +41267,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -41277,7 +41277,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD386" t="b">
@@ -41304,10 +41304,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>130068572</v>
+        <v>130068732</v>
       </c>
       <c r="B387" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -41315,21 +41315,21 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I387" t="inlineStr"/>
@@ -41339,10 +41339,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>490961</v>
+        <v>490542</v>
       </c>
       <c r="R387" t="n">
-        <v>6820600</v>
+        <v>6821224</v>
       </c>
       <c r="S387" t="n">
         <v>10</v>
@@ -41374,7 +41374,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -41384,7 +41384,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD387" t="b">
@@ -41411,10 +41411,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>130068685</v>
+        <v>130068656</v>
       </c>
       <c r="B388" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -41422,21 +41422,21 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I388" t="inlineStr"/>
@@ -41446,10 +41446,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>490423</v>
+        <v>490731</v>
       </c>
       <c r="R388" t="n">
-        <v>6821356</v>
+        <v>6820976</v>
       </c>
       <c r="S388" t="n">
         <v>10</v>
@@ -41481,7 +41481,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -41491,7 +41491,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD388" t="b">
@@ -41518,10 +41518,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>130068715</v>
+        <v>130068928</v>
       </c>
       <c r="B389" t="n">
-        <v>79180</v>
+        <v>78846</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -41529,21 +41529,21 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I389" t="inlineStr"/>
@@ -41553,10 +41553,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>490454</v>
+        <v>490893</v>
       </c>
       <c r="R389" t="n">
-        <v>6821354</v>
+        <v>6820651</v>
       </c>
       <c r="S389" t="n">
         <v>10</v>
@@ -41588,7 +41588,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -41598,7 +41598,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD389" t="b">
@@ -41625,32 +41625,32 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>130068612</v>
+        <v>130068644</v>
       </c>
       <c r="B390" t="n">
-        <v>97791</v>
+        <v>81165</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>221945</v>
+        <v>1049</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I390" t="inlineStr"/>
@@ -41660,10 +41660,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>490645</v>
+        <v>490352</v>
       </c>
       <c r="R390" t="n">
-        <v>6821063</v>
+        <v>6821426</v>
       </c>
       <c r="S390" t="n">
         <v>10</v>
@@ -41695,7 +41695,7 @@
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -41705,7 +41705,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD390" t="b">
@@ -41732,32 +41732,32 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>130068616</v>
+        <v>130068685</v>
       </c>
       <c r="B391" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I391" t="inlineStr"/>
@@ -41767,10 +41767,10 @@
         </is>
       </c>
       <c r="Q391" t="n">
-        <v>491184</v>
+        <v>490423</v>
       </c>
       <c r="R391" t="n">
-        <v>6820708</v>
+        <v>6821356</v>
       </c>
       <c r="S391" t="n">
         <v>10</v>
@@ -41802,7 +41802,7 @@
       </c>
       <c r="Z391" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA391" t="inlineStr">
@@ -41812,7 +41812,7 @@
       </c>
       <c r="AB391" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD391" t="b">
@@ -41839,10 +41839,10 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>130068644</v>
+        <v>130068774</v>
       </c>
       <c r="B392" t="n">
-        <v>81165</v>
+        <v>79180</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -41850,21 +41850,21 @@
         </is>
       </c>
       <c r="E392" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I392" t="inlineStr"/>
@@ -41874,10 +41874,10 @@
         </is>
       </c>
       <c r="Q392" t="n">
-        <v>490352</v>
+        <v>491119</v>
       </c>
       <c r="R392" t="n">
-        <v>6821426</v>
+        <v>6820790</v>
       </c>
       <c r="S392" t="n">
         <v>10</v>
@@ -41909,7 +41909,7 @@
       </c>
       <c r="Z392" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA392" t="inlineStr">
@@ -41919,7 +41919,7 @@
       </c>
       <c r="AB392" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD392" t="b">
@@ -41946,7 +41946,7 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>130068774</v>
+        <v>130068715</v>
       </c>
       <c r="B393" t="n">
         <v>79180</v>
@@ -41981,10 +41981,10 @@
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>491119</v>
+        <v>490454</v>
       </c>
       <c r="R393" t="n">
-        <v>6820790</v>
+        <v>6821354</v>
       </c>
       <c r="S393" t="n">
         <v>10</v>
@@ -42016,7 +42016,7 @@
       </c>
       <c r="Z393" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA393" t="inlineStr">
@@ -42026,7 +42026,7 @@
       </c>
       <c r="AB393" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD393" t="b">
@@ -42267,32 +42267,32 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>130068656</v>
+        <v>130068612</v>
       </c>
       <c r="B396" t="n">
-        <v>78937</v>
+        <v>97791</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I396" t="inlineStr"/>
@@ -42302,10 +42302,10 @@
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>490731</v>
+        <v>490645</v>
       </c>
       <c r="R396" t="n">
-        <v>6820976</v>
+        <v>6821063</v>
       </c>
       <c r="S396" t="n">
         <v>10</v>
@@ -42337,7 +42337,7 @@
       </c>
       <c r="Z396" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA396" t="inlineStr">
@@ -42347,7 +42347,7 @@
       </c>
       <c r="AB396" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD396" t="b">
@@ -42374,32 +42374,32 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>130068928</v>
+        <v>130068616</v>
       </c>
       <c r="B397" t="n">
-        <v>78846</v>
+        <v>97791</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I397" t="inlineStr"/>
@@ -42409,10 +42409,10 @@
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>490893</v>
+        <v>491184</v>
       </c>
       <c r="R397" t="n">
-        <v>6820651</v>
+        <v>6820708</v>
       </c>
       <c r="S397" t="n">
         <v>10</v>
@@ -42444,7 +42444,7 @@
       </c>
       <c r="Z397" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA397" t="inlineStr">
@@ -42454,7 +42454,7 @@
       </c>
       <c r="AB397" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD397" t="b">

--- a/artfynd/A 60015-2025 artfynd.xlsx
+++ b/artfynd/A 60015-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY458"/>
+  <dimension ref="A1:AZ458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362268</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386247</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068801</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068802</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068803</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068804</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068805</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387225</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387227</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068605</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362269</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362271</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386224</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386225</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386226</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2284,6 +2364,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386227</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2381,6 +2466,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387179</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2478,6 +2568,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387220</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2575,6 +2670,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387222</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2672,6 +2772,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387223</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2769,6 +2874,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387672</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2876,6 +2986,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068582</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2983,6 +3098,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068583</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3090,6 +3210,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068584</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068585</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3304,6 +3434,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068586</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3411,6 +3546,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068587</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3518,6 +3658,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068588</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3625,6 +3770,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068589</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3722,6 +3872,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362290</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3829,6 +3984,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068923</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3936,6 +4096,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068924</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4043,6 +4208,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068925</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4150,6 +4320,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068926</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4257,6 +4432,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068927</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4364,6 +4544,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068928</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4471,6 +4656,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068929</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4578,6 +4768,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068930</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4685,6 +4880,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068931</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4792,6 +4992,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068644</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4899,6 +5104,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068645</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5006,6 +5216,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068646</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5104,6 +5319,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387255</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5202,6 +5422,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387256</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5309,6 +5534,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068677</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5416,6 +5646,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068678</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5513,6 +5748,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387669</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5624,6 +5864,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127342991</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5731,6 +5976,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068625</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5838,6 +6088,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347570</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5945,6 +6200,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068609</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6052,6 +6312,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068578</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6149,6 +6414,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387217</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6256,6 +6526,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127342926</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6363,6 +6638,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127345735</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6460,6 +6740,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387205</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6557,6 +6842,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387258</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6664,6 +6954,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068917</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6771,6 +7066,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068918</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6878,6 +7178,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068919</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6985,6 +7290,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068920</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7092,6 +7402,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068921</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7199,6 +7514,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068922</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7306,6 +7626,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068590</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7413,6 +7738,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068591</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7520,6 +7850,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068915</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7627,6 +7962,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068626</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7734,6 +8074,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068627</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7841,6 +8186,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068628</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7948,6 +8298,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068629</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8045,6 +8400,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362283</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8142,6 +8502,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362284</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8239,6 +8604,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362285</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8336,6 +8706,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362286</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8433,6 +8808,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386243</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8530,6 +8910,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386244</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8627,6 +9012,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386246</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8724,6 +9114,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386248</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8821,6 +9216,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386249</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8918,6 +9318,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386251</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9015,6 +9420,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386252</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9112,6 +9522,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386254</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9209,6 +9624,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386255</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9306,6 +9726,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386256</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9403,6 +9828,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386257</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9500,6 +9930,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386258</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9597,6 +10032,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386259</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9694,6 +10134,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386261</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9791,6 +10236,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387199</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9888,6 +10338,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387200</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9985,6 +10440,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387201</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10082,6 +10542,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387247</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10179,6 +10644,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387248</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10276,6 +10746,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387249</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10373,6 +10848,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387251</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10470,6 +10950,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387252</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10567,6 +11052,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387253</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10664,6 +11154,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387680</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10761,6 +11256,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387735</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10858,6 +11358,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387736</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10965,6 +11470,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068683</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11072,6 +11582,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068685</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11179,6 +11694,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068686</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11286,6 +11806,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068687</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11393,6 +11918,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068688</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11500,6 +12030,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068689</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11607,6 +12142,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068690</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11714,6 +12254,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068691</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11821,6 +12366,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068692</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11928,6 +12478,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068693</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12035,6 +12590,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068694</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12142,6 +12702,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068695</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12249,6 +12814,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068696</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12356,6 +12926,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068698</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12463,6 +13038,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068699</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12570,6 +13150,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068700</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12677,6 +13262,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068701</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12784,6 +13374,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068702</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12891,6 +13486,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068703</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12998,6 +13598,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068704</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13105,6 +13710,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068705</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13212,6 +13822,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068707</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13319,6 +13934,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068708</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13426,6 +14046,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068709</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13533,6 +14158,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068710</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13640,6 +14270,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068711</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13747,6 +14382,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068712</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13854,6 +14494,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068713</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13961,6 +14606,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068714</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14068,6 +14718,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068715</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14175,6 +14830,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068716</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14282,6 +14942,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068717</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14389,6 +15054,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068718</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14496,6 +15166,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068719</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14603,6 +15278,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068720</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14710,6 +15390,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068721</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14817,6 +15502,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068722</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14924,6 +15614,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068723</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15031,6 +15726,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068724</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15138,6 +15838,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068725</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15245,6 +15950,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068726</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15352,6 +16062,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068727</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15459,6 +16174,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068728</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15566,6 +16286,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068729</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15673,6 +16398,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068730</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15780,6 +16510,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068731</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15887,6 +16622,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068732</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15994,6 +16734,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068733</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16101,6 +16846,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068734</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16208,6 +16958,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068735</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16315,6 +17070,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068736</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16422,6 +17182,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068737</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16529,6 +17294,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068738</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16636,6 +17406,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068739</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16743,6 +17518,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068740</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16850,6 +17630,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068741</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16957,6 +17742,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068742</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17064,6 +17854,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068743</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17171,6 +17966,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068744</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17278,6 +18078,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068745</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17385,6 +18190,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068746</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17492,6 +18302,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068747</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17599,6 +18414,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068748</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17706,6 +18526,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068749</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17813,6 +18638,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068750</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17920,6 +18750,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068751</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18027,6 +18862,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068752</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18134,6 +18974,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068753</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18241,6 +19086,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068754</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18348,6 +19198,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068755</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18455,6 +19310,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068756</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18562,6 +19422,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068757</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18669,6 +19534,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068758</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18776,6 +19646,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068759</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18883,6 +19758,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068760</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18990,6 +19870,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068761</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19097,6 +19982,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068762</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19204,6 +20094,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068764</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19311,6 +20206,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068765</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19418,6 +20318,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068766</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19525,6 +20430,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068767</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19632,6 +20542,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068768</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19739,6 +20654,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068769</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19846,6 +20766,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068770</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19953,6 +20878,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068771</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20060,6 +20990,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068773</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20167,6 +21102,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068774</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20274,6 +21214,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068776</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20381,6 +21326,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068778</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20488,6 +21438,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068779</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20595,6 +21550,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068781</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20702,6 +21662,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068782</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20809,6 +21774,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068784</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20916,6 +21886,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068785</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21023,6 +21998,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068787</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21130,6 +22110,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068788</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21237,6 +22222,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068790</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21344,6 +22334,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068791</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21451,6 +22446,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068793</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21558,6 +22558,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068794</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21665,6 +22670,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068796</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21772,6 +22782,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068797</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21879,6 +22894,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068799</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21986,6 +23006,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068800</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22093,6 +23118,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068806</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22200,6 +23230,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068807</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22307,6 +23342,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068808</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22414,6 +23454,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068809</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22521,6 +23566,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068810</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22628,6 +23678,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068811</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -22735,6 +23790,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068812</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -22842,6 +23902,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068813</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22949,6 +24014,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068814</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23056,6 +24126,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068815</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23163,6 +24238,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068816</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23270,6 +24350,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068817</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23377,6 +24462,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068818</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23484,6 +24574,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068819</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23591,6 +24686,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068820</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -23698,6 +24798,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068822</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -23805,6 +24910,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068823</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -23912,6 +25022,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068824</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24019,6 +25134,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068825</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24126,6 +25246,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068826</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24233,6 +25358,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068827</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24340,6 +25470,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068828</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24447,6 +25582,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068829</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24554,6 +25694,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068830</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -24661,6 +25806,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068831</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -24768,6 +25918,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068832</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -24875,6 +26030,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068833</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -24982,6 +26142,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068834</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25089,6 +26254,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068835</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25196,6 +26366,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068836</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25303,6 +26478,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068837</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25410,6 +26590,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068838</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25517,6 +26702,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068839</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -25624,6 +26814,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068840</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -25731,6 +26926,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068841</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -25838,6 +27038,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068842</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -25945,6 +27150,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068843</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26052,6 +27262,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068844</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26159,6 +27374,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068845</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26266,6 +27486,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068846</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26373,6 +27598,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068847</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26480,6 +27710,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068848</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -26587,6 +27822,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068849</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -26694,6 +27934,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068850</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -26801,6 +28046,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068851</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -26908,6 +28158,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068852</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27015,6 +28270,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068853</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -27122,6 +28382,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068854</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -27229,6 +28494,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068855</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -27336,6 +28606,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068856</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -27443,6 +28718,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068857</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -27550,6 +28830,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068858</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -27657,6 +28942,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068859</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -27764,6 +29054,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068860</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -27871,6 +29166,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068861</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -27978,6 +29278,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068862</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -28085,6 +29390,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068863</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -28192,6 +29502,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068864</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -28299,6 +29614,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068865</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -28406,6 +29726,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068866</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -28513,6 +29838,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068867</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -28620,6 +29950,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068868</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -28727,6 +30062,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068869</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -28834,6 +30174,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068870</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -28941,6 +30286,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068871</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -29048,6 +30398,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068872</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -29155,6 +30510,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068873</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -29262,6 +30622,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068874</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -29369,6 +30734,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068875</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -29476,6 +30846,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068876</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -29583,6 +30958,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068877</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -29690,6 +31070,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068878</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -29797,6 +31182,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068879</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -29904,6 +31294,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068881</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -30011,6 +31406,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068882</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -30118,6 +31518,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068883</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -30225,6 +31630,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068884</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -30332,6 +31742,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068885</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -30439,6 +31854,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068886</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -30546,6 +31966,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068887</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -30653,6 +32078,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068888</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -30760,6 +32190,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068889</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -30867,6 +32302,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068890</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -30974,6 +32414,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068891</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -31081,6 +32526,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068892</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -31188,6 +32638,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068893</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -31295,6 +32750,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068894</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -31402,6 +32862,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068895</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -31509,6 +32974,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068896</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -31616,6 +33086,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068897</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -31723,6 +33198,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068898</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -31830,6 +33310,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068899</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -31937,6 +33422,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068900</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -32044,6 +33534,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068901</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -32151,6 +33646,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068902</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -32258,6 +33758,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068903</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -32365,6 +33870,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068904</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -32472,6 +33982,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068905</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -32579,6 +34094,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068906</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -32686,6 +34206,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068907</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -32793,6 +34318,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068908</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -32900,6 +34430,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068909</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -33007,6 +34542,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068910</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -33114,6 +34654,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068911</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -33221,6 +34766,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068912</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -33328,6 +34878,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068913</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -33435,6 +34990,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068619</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -33542,6 +35102,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068620</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -33649,6 +35214,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068936</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -33746,6 +35316,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362267</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -33853,6 +35428,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068580</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -33950,6 +35530,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386238</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -34047,6 +35632,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387195</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -34144,6 +35734,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387196</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -34241,6 +35836,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387731</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -34348,6 +35948,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068647</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -34455,6 +36060,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068648</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -34562,6 +36172,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068649</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -34669,6 +36284,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068650</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -34776,6 +36396,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068651</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -34883,6 +36508,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068652</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -34990,6 +36620,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068653</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -35097,6 +36732,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068654</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -35204,6 +36844,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068655</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -35311,6 +36956,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068656</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -35418,6 +37068,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068657</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -35525,6 +37180,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068658</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -35632,6 +37292,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068659</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -35739,6 +37404,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068660</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -35846,6 +37516,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068661</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -35953,6 +37628,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068662</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -36060,6 +37740,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068663</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -36167,6 +37852,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068664</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -36264,6 +37954,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362273</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -36361,6 +38056,11 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387180</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -36468,6 +38168,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068560</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -36575,6 +38280,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068561</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -36682,6 +38392,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068562</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -36789,6 +38504,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068563</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -36896,6 +38616,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068564</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -37003,6 +38728,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068565</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -37110,6 +38840,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068566</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -37217,6 +38952,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068567</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -37324,6 +39064,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068568</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -37431,6 +39176,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068570</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -37538,6 +39288,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068571</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -37645,6 +39400,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068572</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -37752,6 +39512,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068573</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -37859,6 +39624,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068574</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -37966,6 +39736,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068575</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -38073,6 +39848,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068576</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -38180,6 +39960,11 @@
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068577</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -38287,6 +40072,11 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347521</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -38384,6 +40174,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362280</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -38481,6 +40276,11 @@
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387191</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -38578,6 +40378,11 @@
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387192</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -38675,6 +40480,11 @@
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387238</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -38772,6 +40582,11 @@
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387239</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -38869,6 +40684,11 @@
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387678</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -38976,6 +40796,11 @@
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068640</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -39083,6 +40908,11 @@
         </is>
       </c>
       <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068641</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -39190,6 +41020,11 @@
         </is>
       </c>
       <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068642</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -39297,6 +41132,11 @@
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068643</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -39405,6 +41245,11 @@
         </is>
       </c>
       <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068621</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -39512,6 +41357,11 @@
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068622</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -39619,6 +41469,11 @@
         </is>
       </c>
       <c r="AY371" t="inlineStr"/>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068623</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -39726,6 +41581,11 @@
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068624</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -39823,6 +41683,11 @@
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362275</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -39920,6 +41785,11 @@
         </is>
       </c>
       <c r="AY374" t="inlineStr"/>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362278</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -40017,6 +41887,11 @@
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387183</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -40114,6 +41989,11 @@
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387233</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -40221,6 +42101,11 @@
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068602</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -40328,6 +42213,11 @@
         </is>
       </c>
       <c r="AY378" t="inlineStr"/>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068603</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -40435,6 +42325,11 @@
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068604</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -40532,6 +42427,11 @@
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387206</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -40629,6 +42529,11 @@
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387685</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -40734,6 +42639,11 @@
         </is>
       </c>
       <c r="AY382" t="inlineStr"/>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387673</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -40839,6 +42749,11 @@
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387674</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -40954,6 +42869,11 @@
         </is>
       </c>
       <c r="AY384" t="inlineStr"/>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068606</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -41066,6 +42986,11 @@
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068607</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -41178,6 +43103,11 @@
         </is>
       </c>
       <c r="AY386" t="inlineStr"/>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068608</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -41290,6 +43220,11 @@
         </is>
       </c>
       <c r="AY387" t="inlineStr"/>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127342979</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -41395,6 +43330,11 @@
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387216</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -41507,6 +43447,11 @@
         </is>
       </c>
       <c r="AY389" t="inlineStr"/>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068610</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -41619,6 +43564,11 @@
         </is>
       </c>
       <c r="AY390" t="inlineStr"/>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068611</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -41731,6 +43681,11 @@
         </is>
       </c>
       <c r="AY391" t="inlineStr"/>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068914</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -41836,6 +43791,11 @@
         </is>
       </c>
       <c r="AY392" t="inlineStr"/>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386233</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -41941,6 +43901,11 @@
         </is>
       </c>
       <c r="AY393" t="inlineStr"/>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387723</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -42053,6 +44018,11 @@
         </is>
       </c>
       <c r="AY394" t="inlineStr"/>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068594</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -42165,6 +44135,11 @@
         </is>
       </c>
       <c r="AY395" t="inlineStr"/>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068595</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -42277,6 +44252,11 @@
         </is>
       </c>
       <c r="AY396" t="inlineStr"/>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068676</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -42382,6 +44362,11 @@
         </is>
       </c>
       <c r="AY397" t="inlineStr"/>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386234</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -42496,6 +44481,11 @@
         </is>
       </c>
       <c r="AY398" t="inlineStr"/>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362274</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -42605,6 +44595,11 @@
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387230</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -42714,6 +44709,11 @@
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387231</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -42837,6 +44837,11 @@
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068596</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -42943,6 +44948,11 @@
         </is>
       </c>
       <c r="AY402" t="inlineStr"/>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387668</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -43050,6 +45060,11 @@
         </is>
       </c>
       <c r="AY403" t="inlineStr"/>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387237</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -43162,6 +45177,11 @@
         </is>
       </c>
       <c r="AY404" t="inlineStr"/>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068630</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -43274,6 +45294,11 @@
         </is>
       </c>
       <c r="AY405" t="inlineStr"/>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068631</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -43386,6 +45411,11 @@
         </is>
       </c>
       <c r="AY406" t="inlineStr"/>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068632</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -43498,6 +45528,11 @@
         </is>
       </c>
       <c r="AY407" t="inlineStr"/>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068633</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -43605,6 +45640,11 @@
         </is>
       </c>
       <c r="AY408" t="inlineStr"/>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387743</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -43702,6 +45742,11 @@
         </is>
       </c>
       <c r="AY409" t="inlineStr"/>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386230</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -43799,6 +45844,11 @@
         </is>
       </c>
       <c r="AY410" t="inlineStr"/>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387182</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -43906,6 +45956,11 @@
         </is>
       </c>
       <c r="AY411" t="inlineStr"/>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127348515</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -44003,6 +46058,11 @@
         </is>
       </c>
       <c r="AY412" t="inlineStr"/>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386266</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -44100,6 +46160,11 @@
         </is>
       </c>
       <c r="AY413" t="inlineStr"/>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387202</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -44197,6 +46262,11 @@
         </is>
       </c>
       <c r="AY414" t="inlineStr"/>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387204</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -44294,6 +46364,11 @@
         </is>
       </c>
       <c r="AY415" t="inlineStr"/>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387257</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -44391,6 +46466,11 @@
         </is>
       </c>
       <c r="AY416" t="inlineStr"/>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387683</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -44489,6 +46569,11 @@
         </is>
       </c>
       <c r="AY417" t="inlineStr"/>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387737</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -44586,6 +46671,11 @@
         </is>
       </c>
       <c r="AY418" t="inlineStr"/>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387738</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -44683,6 +46773,11 @@
         </is>
       </c>
       <c r="AY419" t="inlineStr"/>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387739</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -44780,6 +46875,11 @@
         </is>
       </c>
       <c r="AY420" t="inlineStr"/>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387740</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -44877,6 +46977,11 @@
         </is>
       </c>
       <c r="AY421" t="inlineStr"/>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387741</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -44974,6 +47079,11 @@
         </is>
       </c>
       <c r="AY422" t="inlineStr"/>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387742</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -45071,6 +47181,11 @@
         </is>
       </c>
       <c r="AY423" t="inlineStr"/>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362281</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -45168,6 +47283,11 @@
         </is>
       </c>
       <c r="AY424" t="inlineStr"/>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387193</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -45270,6 +47390,11 @@
         </is>
       </c>
       <c r="AY425" t="inlineStr"/>
+      <c r="AZ425" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387240</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -45382,6 +47507,11 @@
         </is>
       </c>
       <c r="AY426" t="inlineStr"/>
+      <c r="AZ426" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127346114</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -45484,6 +47614,11 @@
         </is>
       </c>
       <c r="AY427" t="inlineStr"/>
+      <c r="AZ427" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362282</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -45598,6 +47733,11 @@
         </is>
       </c>
       <c r="AY428" t="inlineStr"/>
+      <c r="AZ428" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387241</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -45712,6 +47852,11 @@
         </is>
       </c>
       <c r="AY429" t="inlineStr"/>
+      <c r="AZ429" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387242</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -45814,6 +47959,11 @@
         </is>
       </c>
       <c r="AY430" t="inlineStr"/>
+      <c r="AZ430" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387733</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -45930,6 +48080,11 @@
         </is>
       </c>
       <c r="AY431" t="inlineStr"/>
+      <c r="AZ431" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068665</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -46046,6 +48201,11 @@
         </is>
       </c>
       <c r="AY432" t="inlineStr"/>
+      <c r="AZ432" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068666</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -46162,6 +48322,11 @@
         </is>
       </c>
       <c r="AY433" t="inlineStr"/>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068667</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -46278,6 +48443,11 @@
         </is>
       </c>
       <c r="AY434" t="inlineStr"/>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068668</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -46394,6 +48564,11 @@
         </is>
       </c>
       <c r="AY435" t="inlineStr"/>
+      <c r="AZ435" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068670</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -46510,6 +48685,11 @@
         </is>
       </c>
       <c r="AY436" t="inlineStr"/>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068671</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -46626,6 +48806,11 @@
         </is>
       </c>
       <c r="AY437" t="inlineStr"/>
+      <c r="AZ437" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068672</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -46742,6 +48927,11 @@
         </is>
       </c>
       <c r="AY438" t="inlineStr"/>
+      <c r="AZ438" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068673</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -46858,6 +49048,11 @@
         </is>
       </c>
       <c r="AY439" t="inlineStr"/>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068674</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -46965,6 +49160,11 @@
         </is>
       </c>
       <c r="AY440" t="inlineStr"/>
+      <c r="AZ440" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068618</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -47072,6 +49272,11 @@
         </is>
       </c>
       <c r="AY441" t="inlineStr"/>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068612</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -47179,6 +49384,11 @@
         </is>
       </c>
       <c r="AY442" t="inlineStr"/>
+      <c r="AZ442" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068613</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -47286,6 +49496,11 @@
         </is>
       </c>
       <c r="AY443" t="inlineStr"/>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068614</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -47393,6 +49608,11 @@
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
+      <c r="AZ444" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068615</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -47500,6 +49720,11 @@
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068616</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -47607,6 +49832,11 @@
         </is>
       </c>
       <c r="AY446" t="inlineStr"/>
+      <c r="AZ446" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068617</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -47704,6 +49934,11 @@
         </is>
       </c>
       <c r="AY447" t="inlineStr"/>
+      <c r="AZ447" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387185</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -47801,6 +50036,11 @@
         </is>
       </c>
       <c r="AY448" t="inlineStr"/>
+      <c r="AZ448" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387234</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -47898,6 +50138,11 @@
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386236</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -47995,6 +50240,11 @@
         </is>
       </c>
       <c r="AY450" t="inlineStr"/>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387186</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -48092,6 +50342,11 @@
         </is>
       </c>
       <c r="AY451" t="inlineStr"/>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387726</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -48199,6 +50454,11 @@
         </is>
       </c>
       <c r="AY452" t="inlineStr"/>
+      <c r="AZ452" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068634</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -48306,6 +50566,11 @@
         </is>
       </c>
       <c r="AY453" t="inlineStr"/>
+      <c r="AZ453" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068635</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -48413,6 +50678,11 @@
         </is>
       </c>
       <c r="AY454" t="inlineStr"/>
+      <c r="AZ454" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068636</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -48520,6 +50790,11 @@
         </is>
       </c>
       <c r="AY455" t="inlineStr"/>
+      <c r="AZ455" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068637</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -48627,6 +50902,11 @@
         </is>
       </c>
       <c r="AY456" t="inlineStr"/>
+      <c r="AZ456" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068638</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -48734,6 +51014,11 @@
         </is>
       </c>
       <c r="AY457" t="inlineStr"/>
+      <c r="AZ457" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068639</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -48831,8 +51116,472 @@
         </is>
       </c>
       <c r="AY458" t="inlineStr"/>
+      <c r="AZ458" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387243</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ458" r:id="rId457"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>